--- a/AAII_Financials/Quarterly/LNVGY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LNVGY_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="92">
   <si>
     <t>LNVGY</t>
   </si>
@@ -656,403 +656,428 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43100</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43008</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>42916</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>42825</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>42735</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>15721000</v>
+      </c>
+      <c r="E8" s="3">
+        <v>14409800</v>
+      </c>
+      <c r="F8" s="3">
         <v>12899900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>12635100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>15266600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>17089500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>16955600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>16693800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>20126500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>17868700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>16929200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>15630100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>17245400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>14518900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>13347900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>10579400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>14102800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>13522000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>12512200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>11710300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>14035100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>13379800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>11912700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>10638300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>12938500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>11760900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>10012200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>9578700</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>12168700</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>11231200</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>13119600</v>
+      </c>
+      <c r="E9" s="3">
+        <v>11888000</v>
+      </c>
+      <c r="F9" s="3">
         <v>10648000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>10491700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>12654400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>14213000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>14086700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>13829500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>16771300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>14862900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>14105500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>12942200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>14459300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>12266400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>11306500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>8717600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>11838200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>11339400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>10463800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>9815100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>11985500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>11585700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>10281100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>9094300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>11187500</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>10148400</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>8647600</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>8210200</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>10573500</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>9624000</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>2601400</v>
+      </c>
+      <c r="E10" s="3">
+        <v>2521800</v>
+      </c>
+      <c r="F10" s="3">
         <v>2251900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>2143400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>2612200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>2876500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>2868900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>2864300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>3355200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>3005800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>2823700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>2687900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>2786100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>2252500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>2041400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>1861800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>2264600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>2182600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>2048400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>1895200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>2049600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>1794100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>1631600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>1544000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>1751000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>1612500</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>1364600</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>1368500</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>1595200</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>1607200</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1084,97 +1109,105 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>546600</v>
+      </c>
+      <c r="E12" s="3">
+        <v>498200</v>
+      </c>
+      <c r="F12" s="3">
         <v>451000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>549600</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>578600</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>555700</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>511400</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>575800</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>549200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>482000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>466500</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>416700</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>398100</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>306500</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>332600</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>347200</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>341200</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>318000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>329300</v>
       </c>
-      <c r="U12" s="3">
+      <c r="W12" s="3">
         <v>371300</v>
       </c>
-      <c r="V12" s="3">
+      <c r="X12" s="3">
         <v>272800</v>
       </c>
-      <c r="W12" s="3">
+      <c r="Y12" s="3">
         <v>312300</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Z12" s="3">
         <v>309900</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="AA12" s="3">
         <v>326800</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AB12" s="3">
         <v>344400</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AC12" s="3">
         <v>310900</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AD12" s="3">
         <v>291600</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AE12" s="3">
         <v>338700</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AF12" s="3">
         <v>318400</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AG12" s="3">
         <v>348800</v>
       </c>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1262,31 +1295,37 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+        <v>-4100</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1324,35 +1363,41 @@
       <c r="V14" s="3">
         <v>0</v>
       </c>
-      <c r="W14" s="3" t="s">
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3" t="s">
         <v>10</v>
-      </c>
-      <c r="X14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="Y14" s="3">
-        <v>0</v>
       </c>
       <c r="Z14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AA14" s="3" t="s">
-        <v>10</v>
+      <c r="AA14" s="3">
+        <v>0</v>
       </c>
       <c r="AB14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD14" s="3">
+      <c r="AC14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="3">
         <v>1000</v>
       </c>
-      <c r="AE14" s="3" t="s">
+      <c r="AG14" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1440,8 +1485,14 @@
       <c r="AE15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1470,186 +1521,200 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>15108000</v>
+      </c>
+      <c r="E17" s="3">
+        <v>13891700</v>
+      </c>
+      <c r="F17" s="3">
         <v>12509900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>12344400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>14516700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>16238600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>16178400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>16105000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>19194100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>17052100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>16186500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>15151300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>16544200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>13954400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>12912000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>10413300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>13614700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>13080200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>12169500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>11436800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>13600700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>13090300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>11732400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>10537600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>12734100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>11673200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>10018300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>9504800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>12030700</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>11015800</v>
       </c>
     </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>613000</v>
+      </c>
+      <c r="E18" s="3">
+        <v>518100</v>
+      </c>
+      <c r="F18" s="3">
         <v>390000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>290700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>750000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>850900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>777200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>588800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>932400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>816600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>742700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>478800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>701200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>564500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>435900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>166100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>488100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>441800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>342700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>273500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>434400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>289500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>180300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>100700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>204400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>87700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>-6100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>73900</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>138000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>215400</v>
       </c>
     </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1681,453 +1746,485 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-74900</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-96700</v>
+      </c>
+      <c r="F20" s="3">
         <v>-92300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>-85700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>-59800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>-46500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>-24600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>-8100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-12100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-6700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-27400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>-30100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>-36300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>-33100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>-39700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>-26100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>-34700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>-66000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>-32500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>-26200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>-23500</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>-22100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>-12000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>-14100</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>-12500</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>-9300</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>-10200</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>-2500</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>10300</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AG20" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>895700</v>
+      </c>
+      <c r="E21" s="3">
+        <v>769100</v>
+      </c>
+      <c r="F21" s="3">
         <v>637400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>542500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>1040400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>1137900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>1084000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>907400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>1237700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>1123000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>1022700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>743300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>924900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>788500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>644500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>406600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>704700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>608500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>529500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>451400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>610700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>474200</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>356300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>279800</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>382000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>258700</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>158500</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>247700</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>329700</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>406500</v>
       </c>
     </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>67000</v>
+      </c>
+      <c r="E22" s="3">
+        <v>63700</v>
+      </c>
+      <c r="F22" s="3">
         <v>69700</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>74600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>85100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>94300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>62100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>60600</v>
-      </c>
-      <c r="J22" s="3">
-        <v>65100</v>
-      </c>
-      <c r="K22" s="3">
-        <v>67700</v>
       </c>
       <c r="L22" s="3">
         <v>65100</v>
       </c>
       <c r="M22" s="3">
+        <v>67700</v>
+      </c>
+      <c r="N22" s="3">
+        <v>65100</v>
+      </c>
+      <c r="O22" s="3">
         <v>68500</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>73400</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>61000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>64100</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>62800</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>63200</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>65700</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>70100</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>67100</v>
       </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>60600</v>
       </c>
-      <c r="W22" s="3">
+      <c r="Y22" s="3">
         <v>54200</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Z22" s="3">
         <v>55500</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="AA22" s="3">
         <v>49700</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AB22" s="3">
         <v>41600</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AC22" s="3">
         <v>43100</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AD22" s="3">
         <v>52900</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AE22" s="3">
         <v>56100</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AF22" s="3">
         <v>46900</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AG22" s="3">
         <v>47400</v>
       </c>
     </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>471000</v>
+      </c>
+      <c r="E23" s="3">
+        <v>357600</v>
+      </c>
+      <c r="F23" s="3">
         <v>228100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>130400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>605000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>710100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>690500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>520200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>855200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>742100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>650200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>380300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>591500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>470400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>332100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>77300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>390200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>310100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>240100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>180200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>350300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>213300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>112800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>36800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>150300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>35300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>-69300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>15200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>101300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>167800</v>
       </c>
     </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>94200</v>
+      </c>
+      <c r="E24" s="3">
+        <v>68600</v>
+      </c>
+      <c r="F24" s="3">
         <v>44700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>24800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>123100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>156200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>151000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>98800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>173500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>185100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>165100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>95100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>160000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>120800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>85300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>13900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>84700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>66400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>48200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>46700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>85500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>39800</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>27500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>-11600</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>424800</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>-117800</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>-15400</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>-88500</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>-5700</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>15800</v>
       </c>
     </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2215,186 +2312,204 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>376800</v>
+      </c>
+      <c r="E26" s="3">
+        <v>289100</v>
+      </c>
+      <c r="F26" s="3">
         <v>183400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>105600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>481900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>553800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>539500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>421400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>681700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>557100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>485200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>285200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>431400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>349600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>246800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>63400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>305500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>243600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>191900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>133600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>264800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>173500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>85300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>48400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>-274500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>153200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>-53900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>103700</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>107100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>152000</v>
       </c>
     </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>337000</v>
+      </c>
+      <c r="E27" s="3">
+        <v>249200</v>
+      </c>
+      <c r="F27" s="3">
         <v>176500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>113600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>437200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>541200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>515700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>412200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>639600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>512000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>466100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>260200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>395100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>310200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>212800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>42600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>258100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>202200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>162200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>118100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>232800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>168400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>77000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>32700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>-288800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>139000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>-72300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>106900</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>98400</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>156800</v>
       </c>
     </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2482,8 +2597,14 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2571,8 +2692,14 @@
       <c r="AE29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2660,8 +2787,14 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2749,186 +2882,204 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>74900</v>
+      </c>
+      <c r="E32" s="3">
+        <v>96700</v>
+      </c>
+      <c r="F32" s="3">
         <v>92300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>85700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>59800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>46500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>24600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>8100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>12100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>6700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>27400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>30100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>36300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>33100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>39700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>26100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>34700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>66000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>32500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>26200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>23500</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>22100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>12000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>14100</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>12500</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>9300</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>10200</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>2500</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>-10300</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>337000</v>
+      </c>
+      <c r="E33" s="3">
+        <v>249200</v>
+      </c>
+      <c r="F33" s="3">
         <v>176500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>113600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>437200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>541200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>515700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>412200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>639600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>512000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>466100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>260200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>395100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>310200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>212800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>42600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>258100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>202200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>162200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>118100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>232800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>168400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>77000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>32700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>-288800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>139000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>-72300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>106900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>98400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>156800</v>
       </c>
     </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3016,191 +3167,209 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>337000</v>
+      </c>
+      <c r="E35" s="3">
+        <v>249200</v>
+      </c>
+      <c r="F35" s="3">
         <v>176500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>113600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>437200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>541200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>515700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>412200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>639600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>512000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>466100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>260200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>395100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>310200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>212800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>42600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>258100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>202200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>162200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>118100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>232800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>168400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>77000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>32700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>-288800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>139000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>-72300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>106900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>98400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>156800</v>
       </c>
     </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43100</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43008</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>42916</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>42825</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>42735</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3232,8 +3401,10 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3265,809 +3436,865 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3466200</v>
+      </c>
+      <c r="E41" s="3">
+        <v>3737000</v>
+      </c>
+      <c r="F41" s="3">
         <v>4354800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>4250100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>5018900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>5567400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>3788100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>3930300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>3756500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>3647500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>3175800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>3068400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>4040100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>3698700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>3495600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>3551000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>3520900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>3310900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>2717400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>2662900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>3399900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>2212500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>2613100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>1848000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>1660300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>1143800</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>1387500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>2754600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>2523000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>2253100</v>
       </c>
     </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>66600</v>
+      </c>
+      <c r="E42" s="3">
+        <v>62000</v>
+      </c>
+      <c r="F42" s="3">
         <v>68400</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>71200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>61800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>60400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>57600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>92500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>72500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>83500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>82800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>59400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>51100</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>54000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>50700</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>66500</v>
       </c>
-      <c r="R42" s="3">
+      <c r="T42" s="3">
         <v>65100</v>
       </c>
-      <c r="S42" s="3">
+      <c r="U42" s="3">
         <v>65200</v>
       </c>
-      <c r="T42" s="3">
+      <c r="V42" s="3">
         <v>70600</v>
       </c>
-      <c r="U42" s="3">
+      <c r="W42" s="3">
         <v>70200</v>
       </c>
-      <c r="V42" s="3">
+      <c r="X42" s="3">
         <v>108600</v>
       </c>
-      <c r="W42" s="3">
+      <c r="Y42" s="3">
         <v>112300</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Z42" s="3">
         <v>75900</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="AA42" s="3">
         <v>84300</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AB42" s="3">
         <v>86500</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AC42" s="3">
         <v>118200</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AD42" s="3">
         <v>153600</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AE42" s="3">
         <v>196700</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AF42" s="3">
         <v>162200</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AG42" s="3">
         <v>196600</v>
       </c>
     </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>12059400</v>
+      </c>
+      <c r="E43" s="3">
+        <v>11595000</v>
+      </c>
+      <c r="F43" s="3">
         <v>10125900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>10236200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>11854000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>12346700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>14797200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>15244900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>16798400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>13698200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>13029500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>12518900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>13537100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>11207200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>10257700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>8850900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>12562500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>11648000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>11474800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>9481000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>10010500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>10509900</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>10307200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>8557600</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>9712800</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>9751000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>8075700</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>8062800</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>8914800</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>8875200</v>
       </c>
     </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>6218900</v>
+      </c>
+      <c r="E44" s="3">
+        <v>6169600</v>
+      </c>
+      <c r="F44" s="3">
         <v>5907200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>6371900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>7502100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>8417900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>8867700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>8300700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>8441600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>8727800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>7825800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>6380600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>5785800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>5242300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>5126700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>4946900</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>3998400</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>3816900</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>3573000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>3434700</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>3792300</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>4280900</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>4125100</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>3791700</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>3983300</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>3600000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>3177500</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>2794000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AF44" s="3">
         <v>2833600</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AG44" s="3">
         <v>2882800</v>
       </c>
     </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1416700</v>
+      </c>
+      <c r="E45" s="3">
+        <v>1845600</v>
+      </c>
+      <c r="F45" s="3">
         <v>1818200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>2011600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>1695300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>1725700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>1594500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>1428500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>1413800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>1414700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>1396500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>1308100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>1036400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>1102900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>1116900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>1318200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>1299100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>1275600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>1172300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>1237500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>1168400</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>1211800</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>1524900</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>1381800</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>1502200</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>1419700</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>1354900</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>1060200</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>980200</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>930100</v>
       </c>
     </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>23227800</v>
+      </c>
+      <c r="E46" s="3">
+        <v>23409200</v>
+      </c>
+      <c r="F46" s="3">
         <v>22274500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>22940900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>26132000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>28118100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>29105000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>28996900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>30482800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>27571700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>25510300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>23335400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>24450500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>21305000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>20047600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>18733400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>21446000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>20116800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>19008100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>16886200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>18479800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>18327500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>18646200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>15663300</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>16945200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>16032700</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>14149300</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>14868400</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>15413900</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>15137700</v>
       </c>
     </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1718700</v>
+      </c>
+      <c r="E47" s="3">
+        <v>1719600</v>
+      </c>
+      <c r="F47" s="3">
         <v>1637400</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>1738400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>1673800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>1554800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>1543800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>1508500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>1293600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>1193400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>1120400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>955300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>939200</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>844200</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>701700</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>611300</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>618200</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>556300</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>554700</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>599900</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>559700</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>506600</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>431900</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AA47" s="3">
         <v>408700</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AB47" s="3">
         <v>392900</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AC47" s="3">
         <v>366600</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AD47" s="3">
         <v>304700</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AE47" s="3">
         <v>288500</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AF47" s="3">
         <v>236300</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AG47" s="3">
         <v>215000</v>
       </c>
     </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2999300</v>
+      </c>
+      <c r="E48" s="3">
+        <v>3157900</v>
+      </c>
+      <c r="F48" s="3">
         <v>3123800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>3303900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>3174200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>2788700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>2846700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>2986100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>2834000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>2711600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>2657000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>2674900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>2565700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>2555100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>2472500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>2017100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>2016100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>1937900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>1936400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>1662900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>1568900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>1514700</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>1636000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>1687600</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>1663500</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>1706600</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>1716100</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>1649400</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>1588100</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>1593000</v>
       </c>
     </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>8519200</v>
+      </c>
+      <c r="E49" s="3">
+        <v>8174800</v>
+      </c>
+      <c r="F49" s="3">
         <v>8190500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>8267100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>8184600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>8048700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>7849700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>8066800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>8138300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>8238900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>8447600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>8405000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>8152100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>7980100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>7991500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>7984600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>8230900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>8196700</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>8391500</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>8324600</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>8296700</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>8286300</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>8426900</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>8514500</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>8416300</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>8448400</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>8317200</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>8349100</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AF49" s="3">
         <v>8313800</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AG49" s="3">
         <v>8560500</v>
       </c>
     </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4155,8 +4382,14 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4244,97 +4477,109 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>3039200</v>
+      </c>
+      <c r="E52" s="3">
+        <v>2795100</v>
+      </c>
+      <c r="F52" s="3">
         <v>2698100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>2669800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>2584100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>2783200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>2903300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>2952200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>2897500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>2859000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>2725300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>2620100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>2537600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>2399800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>2281700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>2781800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>2715100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>2581700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>2520900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>2514900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>2373500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>2252300</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>2170400</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>2220000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>2081500</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>2369200</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>2139600</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>2030600</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>1651600</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AG52" s="3">
         <v>1578300</v>
       </c>
     </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4422,97 +4667,109 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>39504300</v>
+      </c>
+      <c r="E54" s="3">
+        <v>39256700</v>
+      </c>
+      <c r="F54" s="3">
         <v>37924400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>38920100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>41748600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>43293500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>44248500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>44510400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>45646200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>42574700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>40460600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>37990600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>38645100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>35084200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>33495000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>32128200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>35026300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>33389400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>32411600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>29988500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>31278600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>30887400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>31311400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>28494200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>29499400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>28923600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>26626800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>27186000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>27203800</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>27084500</v>
       </c>
     </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4544,8 +4801,10 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4577,542 +4836,580 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>9234800</v>
+      </c>
+      <c r="E57" s="3">
+        <v>10872300</v>
+      </c>
+      <c r="F57" s="3">
         <v>7151300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>9772900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>7899600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>12348700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>11505300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>11035900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>12516700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>11492000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>11198200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>10220800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>9968000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>8525700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>7806100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>7509700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>8665800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>7857700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>6736700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>6429800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>7339800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>7281900</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>7919600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>6450800</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>7498200</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>7240100</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>6209100</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>5649900</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>6162700</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>5758900</v>
       </c>
     </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1199800</v>
+      </c>
+      <c r="E58" s="3">
+        <v>414300</v>
+      </c>
+      <c r="F58" s="3">
         <v>2531700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>395300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>3674300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>753100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>3067600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>3081900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>1637700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>1856900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>1853800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>1717600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>1987100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>3508300</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>3895400</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>4845600</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>3966000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>3901700</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>4094900</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>3225900</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>3675300</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>3259700</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>3470000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>1968700</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>1004200</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>1045200</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>1055400</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>905600</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AF58" s="3">
         <v>700600</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AG58" s="3">
         <v>708200</v>
       </c>
     </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>16266100</v>
+      </c>
+      <c r="E59" s="3">
+        <v>15769100</v>
+      </c>
+      <c r="F59" s="3">
         <v>15695000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>15925100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>17343400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>17673600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>18396800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>18640900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>19546000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>17995800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>16166600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>15433300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>15165700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>12541100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>11673600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>10902800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>12601600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>12280300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>12013500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>10834600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>11768900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>12050400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>11625600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>11040300</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>12086600</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>12009800</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>10788000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>11778300</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>12984600</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>11364000</v>
       </c>
     </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>26700700</v>
+      </c>
+      <c r="E60" s="3">
+        <v>27055700</v>
+      </c>
+      <c r="F60" s="3">
         <v>25378000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>26093400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>28917200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>30775300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>32969700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>32758700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>33700300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>31344700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>29218600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>27371600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>27120700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>24575100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>23375100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>23258100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>25233500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>24039700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>22845100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>20490300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>22784100</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>22592000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>23015300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>19459700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>20589000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>20295000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>18052500</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>18333800</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>19848000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>17831000</v>
       </c>
     </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>3826700</v>
+      </c>
+      <c r="E61" s="3">
+        <v>3907300</v>
+      </c>
+      <c r="F61" s="3">
         <v>3972800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>3964000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>4180700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>4185100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>2890000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>2896300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>3619300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>3627000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>3622000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>3632800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>4246500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>2873000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>2867400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>1911400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>2498400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>2452800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>2462800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>2426800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>1821200</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>1820100</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>1842200</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>2648700</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>2617700</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>2591300</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>2579200</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>2966700</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AF61" s="3">
         <v>2465200</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AG61" s="3">
         <v>2487500</v>
       </c>
     </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2863900</v>
+      </c>
+      <c r="E62" s="3">
+        <v>2715200</v>
+      </c>
+      <c r="F62" s="3">
         <v>2716600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>2815700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>2847200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>2706100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>2803700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>3460800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>3534700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>3464100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>3460000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>3375600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>3367000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>3179700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>3022200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>2899300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>2999200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>2882400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>2846900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>2974300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>2803400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>2521900</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>2115800</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>1839700</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>1916700</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>1848900</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>1817100</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>1790200</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>1856000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>3583200</v>
       </c>
     </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5200,8 +5497,14 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5289,8 +5592,14 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5378,97 +5687,109 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>33903900</v>
+      </c>
+      <c r="E66" s="3">
+        <v>34129500</v>
+      </c>
+      <c r="F66" s="3">
         <v>32515200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>33332500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>36424100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>38109200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>39068600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>39519800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>41162200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>38571700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>36400300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>34431600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>34758400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>30568500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>29159200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>27937000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>30588700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>29147100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>27899500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>25598400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>27099800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>26872400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>26971200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>23981900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>25154000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>24769900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>22489200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>23118700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>24201600</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>23923100</v>
       </c>
     </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5500,8 +5821,10 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5589,8 +5912,14 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5678,8 +6007,14 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5767,8 +6102,14 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5856,97 +6197,109 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>5159800</v>
+        <v>4555400</v>
       </c>
       <c r="E72" s="3">
-        <v>4969300</v>
+        <v>4429500</v>
       </c>
       <c r="F72" s="3">
-        <v>4824900</v>
+        <v>4651900</v>
       </c>
       <c r="G72" s="3">
-        <v>4473200</v>
+        <v>4625100</v>
       </c>
       <c r="H72" s="3">
-        <v>4356700</v>
+        <v>4590200</v>
       </c>
       <c r="I72" s="3">
+        <v>4209700</v>
+      </c>
+      <c r="J72" s="3">
+        <v>4064400</v>
+      </c>
+      <c r="K72" s="3">
         <v>3841000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>3460100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>2951300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>2796200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>2334600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>2056000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>1803600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>1825700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>1614800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>1603800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>1453200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>1586700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>1424000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>1249300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>1110200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>1242900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>1160100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>1143900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>1531400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>1684100</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>1756400</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>1610600</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>1616600</v>
       </c>
     </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6034,8 +6387,14 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6123,8 +6482,14 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6212,97 +6577,109 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>5600400</v>
+      </c>
+      <c r="E76" s="3">
+        <v>5127200</v>
+      </c>
+      <c r="F76" s="3">
         <v>5409100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>5587600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>5324600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>5184300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>5179900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>4990600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>4484000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>4003000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>4060400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>3559000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>3886800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>4515700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>4335800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>4191200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>4437600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>4242300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>4512100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>4390100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>4178800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>4015000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>4340200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>4512300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>4345400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>4153700</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>4137600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>4067300</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>3002200</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>3161400</v>
       </c>
     </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6390,191 +6767,209 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43100</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43008</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>42916</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>42825</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>42735</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>337000</v>
+      </c>
+      <c r="E81" s="3">
+        <v>249200</v>
+      </c>
+      <c r="F81" s="3">
         <v>176500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>113600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>437200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>541200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>515700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>412200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>639600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>512000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>466100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>260200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>395100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>310200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>212800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>42600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>258100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>202200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>162200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>118100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>232800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>168400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>77000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>32700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>-288800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>139000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>-72300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>106900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>98400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>156800</v>
       </c>
     </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6606,97 +7001,105 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>357700</v>
+      </c>
+      <c r="E83" s="3">
+        <v>347700</v>
+      </c>
+      <c r="F83" s="3">
         <v>339600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>337500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>350300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>333500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>331400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>326600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>317400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>313100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>307300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>294600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>260000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>257100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>248300</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>266500</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>251200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>232700</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>219300</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>204100</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>199800</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>206800</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>188000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>193300</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>190100</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>180300</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AD83" s="3">
         <v>174900</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AE83" s="3">
         <v>176400</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AF83" s="3">
         <v>181400</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AG83" s="3">
         <v>191300</v>
       </c>
     </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6784,8 +7187,14 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6873,8 +7282,14 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6962,8 +7377,14 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7051,8 +7472,14 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7140,97 +7567,109 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>364200</v>
+      </c>
+      <c r="E89" s="3">
+        <v>453800</v>
+      </c>
+      <c r="F89" s="3">
         <v>649800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>244400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>74000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>2084300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>398700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>1462500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>606300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>1560600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>447600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>601400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>1962900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>771400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>317100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>431600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>538300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>1381600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>-141600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>-478100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>1547600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>67100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>336000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>-753500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>210900</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>363600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>-577400</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>207600</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>345500</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>1558700</v>
       </c>
     </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7262,97 +7701,105 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-355700</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-345200</v>
+      </c>
+      <c r="F91" s="3">
         <v>-331500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-374200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-434400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-383400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-386200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-364500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-361800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-278500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-279300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-111400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-71600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-69600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-50200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-68600</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-71900</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-75000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-31200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-76200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-86400</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-34900</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-37200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-61300</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-55300</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-44600</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-56700</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-177300</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AF91" s="3">
         <v>-181700</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AG91" s="3">
         <v>-154700</v>
       </c>
     </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7440,8 +7887,14 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7529,97 +7982,109 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-364400</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-468700</v>
+      </c>
+      <c r="F94" s="3">
         <v>-200000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-314000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-407200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-806000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-387800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-574100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-389300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-343400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-191600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-279600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-197000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-214300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-285100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-237800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-215400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-200400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-303400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-181500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-217100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-103700</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-197400</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-173500</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-103200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-92900</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-743900</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-1323900</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>93100</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>-200800</v>
       </c>
     </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7651,97 +8116,105 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>-124500</v>
       </c>
       <c r="E96" s="3">
         <v>0</v>
       </c>
       <c r="F96" s="3">
+        <v>0</v>
+      </c>
+      <c r="G96" s="3">
+        <v>0</v>
+      </c>
+      <c r="H96" s="3">
         <v>-123400</v>
       </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
       <c r="I96" s="3">
         <v>0</v>
       </c>
       <c r="J96" s="3">
+        <v>0</v>
+      </c>
+      <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3">
         <v>-119800</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
       <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3">
         <v>100</v>
       </c>
-      <c r="N96" s="3">
+      <c r="P96" s="3">
         <v>-102000</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
       <c r="Q96" s="3">
         <v>0</v>
       </c>
       <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
         <v>-96400</v>
       </c>
-      <c r="S96" s="3">
-        <v>0</v>
-      </c>
-      <c r="T96" s="3">
-        <v>0</v>
-      </c>
       <c r="U96" s="3">
         <v>0</v>
       </c>
       <c r="V96" s="3">
+        <v>0</v>
+      </c>
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+      <c r="X96" s="3">
         <v>-91400</v>
       </c>
-      <c r="W96" s="3">
-        <v>0</v>
-      </c>
-      <c r="X96" s="3">
-        <v>0</v>
-      </c>
       <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA96" s="3">
         <v>3300</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AB96" s="3">
         <v>-92300</v>
       </c>
-      <c r="AA96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB96" s="3">
-        <v>0</v>
-      </c>
       <c r="AC96" s="3">
         <v>0</v>
       </c>
       <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-85100</v>
       </c>
-      <c r="AE96" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7829,8 +8302,14 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7918,8 +8397,14 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8007,271 +8492,295 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-323400</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-574900</v>
+      </c>
+      <c r="F100" s="3">
         <v>-283400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-729100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-301500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>625300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-8500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-750100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-110400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-717100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-179800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-1224700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-1524500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-387900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-91100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-69000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-157600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-524100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>512300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-86000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-165100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-317800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>691600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>1071600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>395000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-525700</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>-66500</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>1318500</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>-117800</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>-1014900</v>
       </c>
     </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>52800</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-28000</v>
+      </c>
+      <c r="F101" s="3">
         <v>-61600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>29900</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>86200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-124300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-144700</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>35600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>2400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-28500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>31100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>-68900</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>100100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>33800</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>3700</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>-94800</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>44700</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>-63500</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>-12800</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>8500</v>
       </c>
-      <c r="V101" s="3">
+      <c r="X101" s="3">
         <v>22000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="Y101" s="3">
         <v>-46200</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Z101" s="3">
         <v>-65000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="AA101" s="3">
         <v>43000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AB101" s="3">
         <v>13700</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AC101" s="3">
         <v>11400</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AD101" s="3">
         <v>20600</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AE101" s="3">
         <v>29300</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AF101" s="3">
         <v>-50800</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AG101" s="3">
         <v>3900</v>
       </c>
     </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-270800</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-617800</v>
+      </c>
+      <c r="F102" s="3">
         <v>104700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-768800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-548500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>1779300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-142200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>173800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>109000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>471700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>107400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-971800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>341500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>203000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-55400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>30100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>210000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>593500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>54600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>-737000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>1187300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-400600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>765100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>187700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>516500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>-243600</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>-1367100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>231600</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>270000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>346900</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/LNVGY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LNVGY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="92">
   <si>
     <t>LNVGY</t>
   </si>
@@ -1315,8 +1315,8 @@
       <c r="F14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>10</v>
+      <c r="G14" s="3">
+        <v>-16900</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>10</v>
@@ -1538,7 +1538,7 @@
         <v>12509900</v>
       </c>
       <c r="G17" s="3">
-        <v>12344400</v>
+        <v>12327500</v>
       </c>
       <c r="H17" s="3">
         <v>14516700</v>
@@ -1633,7 +1633,7 @@
         <v>390000</v>
       </c>
       <c r="G18" s="3">
-        <v>290700</v>
+        <v>307600</v>
       </c>
       <c r="H18" s="3">
         <v>750000</v>
@@ -1763,7 +1763,7 @@
         <v>-92300</v>
       </c>
       <c r="G20" s="3">
-        <v>-85700</v>
+        <v>-102600</v>
       </c>
       <c r="H20" s="3">
         <v>-59800</v>
@@ -2903,7 +2903,7 @@
         <v>92300</v>
       </c>
       <c r="G32" s="3">
-        <v>85700</v>
+        <v>102600</v>
       </c>
       <c r="H32" s="3">
         <v>59800</v>
@@ -4844,25 +4844,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>9234800</v>
+        <v>10258500</v>
       </c>
       <c r="E57" s="3">
         <v>10872300</v>
       </c>
       <c r="F57" s="3">
-        <v>7151300</v>
+        <v>9284200</v>
       </c>
       <c r="G57" s="3">
         <v>9772900</v>
       </c>
       <c r="H57" s="3">
-        <v>7899600</v>
+        <v>10837300</v>
       </c>
       <c r="I57" s="3">
         <v>12348700</v>
       </c>
       <c r="J57" s="3">
-        <v>11505300</v>
+        <v>13609600</v>
       </c>
       <c r="K57" s="3">
         <v>11035900</v>
@@ -4939,25 +4939,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1199800</v>
+        <v>176100</v>
       </c>
       <c r="E58" s="3">
         <v>414300</v>
       </c>
       <c r="F58" s="3">
-        <v>2531700</v>
+        <v>398800</v>
       </c>
       <c r="G58" s="3">
         <v>395300</v>
       </c>
       <c r="H58" s="3">
-        <v>3674300</v>
+        <v>736500</v>
       </c>
       <c r="I58" s="3">
         <v>753100</v>
       </c>
       <c r="J58" s="3">
-        <v>3067600</v>
+        <v>963300</v>
       </c>
       <c r="K58" s="3">
         <v>3081900</v>

--- a/AAII_Financials/Quarterly/LNVGY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LNVGY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="92">
   <si>
     <t>LNVGY</t>
   </si>
@@ -656,428 +656,454 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>42825</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>15447100</v>
+      </c>
+      <c r="E8" s="3">
+        <v>13833100</v>
+      </c>
+      <c r="F8" s="3">
         <v>15721000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>14409800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>12899900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>12635100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>15266600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>17089500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>16955600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>16693800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>20126500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>17868700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>16929200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>15630100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>17245400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>14518900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>13347900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>10579400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>14102800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>13522000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>12512200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>11710300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>14035100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>13379800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>11912700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>10638300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>12938500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>11760900</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>10012200</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>9578700</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>12168700</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AI8" s="3">
         <v>11231200</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>12887200</v>
+      </c>
+      <c r="E9" s="3">
+        <v>11405000</v>
+      </c>
+      <c r="F9" s="3">
         <v>13119600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>11888000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>10648000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>10491700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>12654400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>14213000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>14086700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>13829500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>16771300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>14862900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>14105500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>12942200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>14459300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>12266400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>11306500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>8717600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>11838200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>11339400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>10463800</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>9815100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>11985500</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>11585700</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>10281100</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>9094300</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>11187500</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>10148400</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>8647600</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>8210200</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AH9" s="3">
         <v>10573500</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AI9" s="3">
         <v>9624000</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>2559900</v>
+      </c>
+      <c r="E10" s="3">
+        <v>2428100</v>
+      </c>
+      <c r="F10" s="3">
         <v>2601400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>2521800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>2251900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>2143400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>2612200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>2876500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>2868900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>2864300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>3355200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>3005800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>2823700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>2687900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>2786100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>2252500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>2041400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>1861800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>2264600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>2182600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>2048400</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>1895200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>2049600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>1794100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>1631600</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>1544000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>1751000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>1612500</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>1364600</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>1368500</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>1595200</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AI10" s="3">
         <v>1607200</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1111,103 +1137,111 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>476000</v>
+      </c>
+      <c r="E12" s="3">
+        <v>531700</v>
+      </c>
+      <c r="F12" s="3">
         <v>546600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>498200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>451000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>549600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>578600</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>555700</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>511400</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>575800</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>549200</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>482000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>466500</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>416700</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>398100</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>306500</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>332600</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>347200</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>341200</v>
       </c>
-      <c r="U12" s="3">
+      <c r="W12" s="3">
         <v>318000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="X12" s="3">
         <v>329300</v>
       </c>
-      <c r="W12" s="3">
+      <c r="Y12" s="3">
         <v>371300</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Z12" s="3">
         <v>272800</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="AA12" s="3">
         <v>312300</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AB12" s="3">
         <v>309900</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AC12" s="3">
         <v>326800</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AD12" s="3">
         <v>344400</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AE12" s="3">
         <v>310900</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AF12" s="3">
         <v>291600</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AG12" s="3">
         <v>338700</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AH12" s="3">
         <v>318400</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AI12" s="3">
         <v>348800</v>
       </c>
     </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1301,8 +1335,14 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1316,22 +1356,22 @@
         <v>10</v>
       </c>
       <c r="G14" s="3">
-        <v>-16900</v>
+        <v>-4100</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>10</v>
+      <c r="I14" s="3">
+        <v>-16900</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1369,35 +1409,41 @@
       <c r="X14" s="3">
         <v>0</v>
       </c>
-      <c r="Y14" s="3" t="s">
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="3" t="s">
         <v>10</v>
-      </c>
-      <c r="Z14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AA14" s="3">
-        <v>0</v>
       </c>
       <c r="AB14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AC14" s="3" t="s">
-        <v>10</v>
+      <c r="AC14" s="3">
+        <v>0</v>
       </c>
       <c r="AD14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AE14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF14" s="3">
+      <c r="AE14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="3">
         <v>1000</v>
       </c>
-      <c r="AG14" s="3" t="s">
+      <c r="AI14" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1491,8 +1537,14 @@
       <c r="AG15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1523,198 +1575,212 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>14952600</v>
+      </c>
+      <c r="E17" s="3">
+        <v>13340300</v>
+      </c>
+      <c r="F17" s="3">
         <v>15108000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>13891700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>12509900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>12327500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>14516700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>16238600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>16178400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>16105000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>19194100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>17052100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>16186500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>15151300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>16544200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>13954400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>12912000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>10413300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>13614700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>13080200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>12169500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>11436800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>13600700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>13090300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>11732400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>10537600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>12734100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>11673200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>10018300</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>9504800</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>12030700</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AI17" s="3">
         <v>11015800</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>494500</v>
+      </c>
+      <c r="E18" s="3">
+        <v>492800</v>
+      </c>
+      <c r="F18" s="3">
         <v>613000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>518100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>390000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>307600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>750000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>850900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>777200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>588800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>932400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>816600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>742700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>478800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>701200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>564500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>435900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>166100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>488100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>441800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>342700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>273500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>434400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>289500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>180300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>100700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>204400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>87700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>-6100</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>73900</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>138000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AI18" s="3">
         <v>215400</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1748,483 +1814,515 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-111900</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-109400</v>
+      </c>
+      <c r="F20" s="3">
         <v>-74900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>-96700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>-92300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>-102600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>-59800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>-46500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-24600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-8100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-12100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>-6700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>-27400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>-30100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>-36300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>-33100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>-39700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>-26100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>-34700</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>-66000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>-32500</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>-26200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>-23500</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>-22100</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>-12000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>-14100</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>-12500</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>-9300</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>-10200</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AG20" s="3">
         <v>-2500</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AH20" s="3">
         <v>10300</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AI20" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3">
+      <c r="D21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E21" s="3">
+        <v>751600</v>
+      </c>
+      <c r="F21" s="3">
         <v>895700</v>
       </c>
-      <c r="E21" s="3">
-        <v>769100</v>
-      </c>
-      <c r="F21" s="3">
-        <v>637400</v>
-      </c>
       <c r="G21" s="3">
+        <v>1108700</v>
+      </c>
+      <c r="H21" s="3">
+        <v>-715300</v>
+      </c>
+      <c r="I21" s="3">
         <v>542500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>1040400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>1137900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>1084000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>907400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>1237700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>1123000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>1022700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>743300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>924900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>788500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>644500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>406600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>704700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>608500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>529500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>451400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>610700</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>474200</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>356300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>279800</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>382000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>258700</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>158500</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>247700</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>329700</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AI21" s="3">
         <v>406500</v>
       </c>
     </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>69600</v>
+      </c>
+      <c r="E22" s="3">
+        <v>74800</v>
+      </c>
+      <c r="F22" s="3">
         <v>67000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>63700</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>69700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>74600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>85100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>94300</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>62100</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>60600</v>
-      </c>
-      <c r="L22" s="3">
-        <v>65100</v>
-      </c>
-      <c r="M22" s="3">
-        <v>67700</v>
       </c>
       <c r="N22" s="3">
         <v>65100</v>
       </c>
       <c r="O22" s="3">
+        <v>67700</v>
+      </c>
+      <c r="P22" s="3">
+        <v>65100</v>
+      </c>
+      <c r="Q22" s="3">
         <v>68500</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>73400</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>61000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>64100</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>62800</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>63200</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>65700</v>
       </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>70100</v>
       </c>
-      <c r="W22" s="3">
+      <c r="Y22" s="3">
         <v>67100</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Z22" s="3">
         <v>60600</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="AA22" s="3">
         <v>54200</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AB22" s="3">
         <v>55500</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AC22" s="3">
         <v>49700</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AD22" s="3">
         <v>41600</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AE22" s="3">
         <v>43100</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AF22" s="3">
         <v>52900</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AG22" s="3">
         <v>56100</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AH22" s="3">
         <v>46900</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AI22" s="3">
         <v>47400</v>
       </c>
     </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>313000</v>
+      </c>
+      <c r="E23" s="3">
+        <v>308700</v>
+      </c>
+      <c r="F23" s="3">
         <v>471000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>357600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>228100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>130400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>605000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>710100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>690500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>520200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>855200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>742100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>650200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>380300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>591500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>470400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>332100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>77300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>390200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>310100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>240100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>180200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>350300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>213300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>112800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>36800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>150300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>35300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>-69300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>15200</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>101300</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AI23" s="3">
         <v>167800</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>59500</v>
+      </c>
+      <c r="E24" s="3">
+        <v>55600</v>
+      </c>
+      <c r="F24" s="3">
         <v>94200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>68600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>44700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>24800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>123100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>156200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>151000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>98800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>173500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>185100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>165100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>95100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>160000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>120800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>85300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>13900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>84700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>66400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>48200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>46700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>85500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>39800</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>27500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>-11600</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>424800</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>-117800</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>-15400</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>-88500</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AH24" s="3">
         <v>-5700</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AI24" s="3">
         <v>15800</v>
       </c>
     </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2318,198 +2416,216 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>253500</v>
+      </c>
+      <c r="E26" s="3">
+        <v>253000</v>
+      </c>
+      <c r="F26" s="3">
         <v>376800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>289100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>183400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>105600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>481900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>553800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>539500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>421400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>681700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>557100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>485200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>285200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>431400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>349600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>246800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>63400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>305500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>243600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>191900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>133600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>264800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>173500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>85300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>48400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>-274500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>153200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>-53900</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>103700</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>107100</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AI26" s="3">
         <v>152000</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>243400</v>
+      </c>
+      <c r="E27" s="3">
+        <v>247700</v>
+      </c>
+      <c r="F27" s="3">
         <v>337000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>249200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>176500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>113600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>437200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>541200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>515700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>412200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>639600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>512000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>466100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>260200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>395100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>310200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>212800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>42600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>258100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>202200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>162200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>118100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>232800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>168400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>77000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>32700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>-288800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>139000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>-72300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>106900</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>98400</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AI27" s="3">
         <v>156800</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2603,8 +2719,14 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2698,8 +2820,14 @@
       <c r="AG29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2793,8 +2921,14 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2888,198 +3022,216 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>111900</v>
+      </c>
+      <c r="E32" s="3">
+        <v>109400</v>
+      </c>
+      <c r="F32" s="3">
         <v>74900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>96700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>92300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>102600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>59800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>46500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>24600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>8100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>12100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>6700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>27400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>30100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>36300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>33100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>39700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>26100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>34700</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>66000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>32500</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>26200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>23500</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>22100</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>12000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>14100</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>12500</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>9300</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>10200</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>2500</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AH32" s="3">
         <v>-10300</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AI32" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>243400</v>
+      </c>
+      <c r="E33" s="3">
+        <v>247700</v>
+      </c>
+      <c r="F33" s="3">
         <v>337000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>249200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>176500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>113600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>437200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>541200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>515700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>412200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>639600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>512000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>466100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>260200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>395100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>310200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>212800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>42600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>258100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>202200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>162200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>118100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>232800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>168400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>77000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>32700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>-288800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>139000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>-72300</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>106900</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>98400</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AI33" s="3">
         <v>156800</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3173,203 +3325,221 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>243400</v>
+      </c>
+      <c r="E35" s="3">
+        <v>247700</v>
+      </c>
+      <c r="F35" s="3">
         <v>337000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>249200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>176500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>113600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>437200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>541200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>515700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>412200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>639600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>512000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>466100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>260200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>395100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>310200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>212800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>42600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>258100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>202200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>162200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>118100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>232800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>168400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>77000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>32700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>-288800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>139000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>-72300</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>106900</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>98400</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AI35" s="3">
         <v>156800</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>42825</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3403,8 +3573,10 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3438,863 +3610,919 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3911100</v>
+      </c>
+      <c r="E41" s="3">
+        <v>3559800</v>
+      </c>
+      <c r="F41" s="3">
         <v>3466200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>3737000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>4354800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>4250100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>5018900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>5567400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>3788100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>3930300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>3756500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>3647500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>3175800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>3068400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>4040100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>3698700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>3495600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>3551000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>3520900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>3310900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>2717400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>2662900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>3399900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>2212500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>2613100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>1848000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>1660300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>1143800</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>1387500</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>2754600</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>2523000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AI41" s="3">
         <v>2253100</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>62000</v>
+      </c>
+      <c r="E42" s="3">
+        <v>65600</v>
+      </c>
+      <c r="F42" s="3">
         <v>66600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>62000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>68400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>71200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>61800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>60400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>57600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>92500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>72500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>83500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>82800</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>59400</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>51100</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>54000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="T42" s="3">
         <v>50700</v>
       </c>
-      <c r="S42" s="3">
+      <c r="U42" s="3">
         <v>66500</v>
       </c>
-      <c r="T42" s="3">
+      <c r="V42" s="3">
         <v>65100</v>
       </c>
-      <c r="U42" s="3">
+      <c r="W42" s="3">
         <v>65200</v>
       </c>
-      <c r="V42" s="3">
+      <c r="X42" s="3">
         <v>70600</v>
       </c>
-      <c r="W42" s="3">
+      <c r="Y42" s="3">
         <v>70200</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Z42" s="3">
         <v>108600</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="AA42" s="3">
         <v>112300</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AB42" s="3">
         <v>75900</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AC42" s="3">
         <v>84300</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AD42" s="3">
         <v>86500</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AE42" s="3">
         <v>118200</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AF42" s="3">
         <v>153600</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AG42" s="3">
         <v>196700</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AH42" s="3">
         <v>162200</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AI42" s="3">
         <v>196600</v>
       </c>
     </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>11384500</v>
+      </c>
+      <c r="E43" s="3">
+        <v>10936700</v>
+      </c>
+      <c r="F43" s="3">
         <v>12059400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>11595000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>10125900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>10236200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>11854000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>12346700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>14797200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>15244900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>16798400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>13698200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>13029500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>12518900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>13537100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>11207200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>10257700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>8850900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>12562500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>11648000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>11474800</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>9481000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>10010500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>10509900</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>10307200</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>8557600</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>9712800</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>9751000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>8075700</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>8062800</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AH43" s="3">
         <v>8914800</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AI43" s="3">
         <v>8875200</v>
       </c>
     </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>7777600</v>
+      </c>
+      <c r="E44" s="3">
+        <v>6702700</v>
+      </c>
+      <c r="F44" s="3">
         <v>6218900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>6169600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>5907200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>6371900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>7502100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>8417900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>8867700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>8300700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>8441600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>8727800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>7825800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>6380600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>5785800</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>5242300</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>5126700</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>4946900</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>3998400</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>3816900</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>3573000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>3434700</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>3792300</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>4280900</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>4125100</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>3791700</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>3983300</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>3600000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AF44" s="3">
         <v>3177500</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AG44" s="3">
         <v>2794000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AH44" s="3">
         <v>2833600</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AI44" s="3">
         <v>2882800</v>
       </c>
     </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1422100</v>
+      </c>
+      <c r="E45" s="3">
+        <v>1422400</v>
+      </c>
+      <c r="F45" s="3">
         <v>1416700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>1845600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>1818200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>2011600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>1695300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>1725700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>1594500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>1428500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>1413800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>1414700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>1396500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>1308100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>1036400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>1102900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>1116900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>1318200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>1299100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>1275600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>1172300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>1237500</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>1168400</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>1211800</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>1524900</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>1381800</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>1502200</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>1419700</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>1354900</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>1060200</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AH45" s="3">
         <v>980200</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AI45" s="3">
         <v>930100</v>
       </c>
     </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>24557300</v>
+      </c>
+      <c r="E46" s="3">
+        <v>22687200</v>
+      </c>
+      <c r="F46" s="3">
         <v>23227800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>23409200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>22274500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>22940900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>26132000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>28118100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>29105000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>28996900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>30482800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>27571700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>25510300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>23335400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>24450500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>21305000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>20047600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>18733400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>21446000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>20116800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>19008100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>16886200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>18479800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>18327500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>18646200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>15663300</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>16945200</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>16032700</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>14149300</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>14868400</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>15413900</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AI46" s="3">
         <v>15137700</v>
       </c>
     </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1772500</v>
+      </c>
+      <c r="E47" s="3">
+        <v>1768400</v>
+      </c>
+      <c r="F47" s="3">
         <v>1718700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>1719600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>1637400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>1738400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>1673800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>1554800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>1543800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>1508500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>1293600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>1193400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>1120400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>955300</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>939200</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>844200</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>701700</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>611300</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>618200</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>556300</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>554700</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>599900</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>559700</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AA47" s="3">
         <v>506600</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AB47" s="3">
         <v>431900</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AC47" s="3">
         <v>408700</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AD47" s="3">
         <v>392900</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AE47" s="3">
         <v>366600</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AF47" s="3">
         <v>304700</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AG47" s="3">
         <v>288500</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AH47" s="3">
         <v>236300</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AI47" s="3">
         <v>215000</v>
       </c>
     </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2831000</v>
+      </c>
+      <c r="E48" s="3">
+        <v>2919100</v>
+      </c>
+      <c r="F48" s="3">
         <v>2999300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>3157900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>3123800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>3303900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>3174200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>2788700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>2846700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>2986100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>2834000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>2711600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>2657000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>2674900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>2565700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>2555100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>2472500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>2017100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>2016100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>1937900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>1936400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>1662900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>1568900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>1514700</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>1636000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>1687600</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>1663500</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>1706600</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>1716100</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>1649400</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AH48" s="3">
         <v>1588100</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AI48" s="3">
         <v>1593000</v>
       </c>
     </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>8198800</v>
+      </c>
+      <c r="E49" s="3">
+        <v>8345400</v>
+      </c>
+      <c r="F49" s="3">
         <v>8519200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>8174800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>8190500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>8267100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>8184600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>8048700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>7849700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>8066800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>8138300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>8238900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>8447600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>8405000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>8152100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>7980100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>7991500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>7984600</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>8230900</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>8196700</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>8391500</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>8324600</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>8296700</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>8286300</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>8426900</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>8514500</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>8416300</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>8448400</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AF49" s="3">
         <v>8317200</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AG49" s="3">
         <v>8349100</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AH49" s="3">
         <v>8313800</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AI49" s="3">
         <v>8560500</v>
       </c>
     </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4388,8 +4616,14 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4483,103 +4717,115 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>3125000</v>
+      </c>
+      <c r="E52" s="3">
+        <v>3030800</v>
+      </c>
+      <c r="F52" s="3">
         <v>3039200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>2795100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>2698100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>2669800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>2584100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>2783200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>2903300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>2952200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>2897500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>2859000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>2725300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>2620100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>2537600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>2399800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>2281700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>2781800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>2715100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>2581700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>2520900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>2514900</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>2373500</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>2252300</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>2170400</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>2220000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>2081500</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>2369200</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>2139600</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AG52" s="3">
         <v>2030600</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AH52" s="3">
         <v>1651600</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AI52" s="3">
         <v>1578300</v>
       </c>
     </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4673,103 +4919,115 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>40484700</v>
+      </c>
+      <c r="E54" s="3">
+        <v>38751000</v>
+      </c>
+      <c r="F54" s="3">
         <v>39504300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>39256700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>37924400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>38920100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>41748600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>43293500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>44248500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>44510400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>45646200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>42574700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>40460600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>37990600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>38645100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>35084200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>33495000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>32128200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>35026300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>33389400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>32411600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>29988500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>31278600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>30887400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>31311400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>28494200</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>29499400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>28923600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>26626800</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>27186000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>27203800</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AI54" s="3">
         <v>27084500</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4803,8 +5061,10 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4838,578 +5098,616 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>11924600</v>
+      </c>
+      <c r="E57" s="3">
+        <v>10505400</v>
+      </c>
+      <c r="F57" s="3">
         <v>10258500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>10872300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>9284200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>9772900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>10837300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>12348700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>13609600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>11035900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>12516700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>11492000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>11198200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>10220800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>9968000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>8525700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>7806100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>7509700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>8665800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>7857700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>6736700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>6429800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>7339800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>7281900</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>7919600</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>6450800</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>7498200</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>7240100</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>6209100</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>5649900</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>6162700</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AI57" s="3">
         <v>5758900</v>
       </c>
     </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1100500</v>
+      </c>
+      <c r="E58" s="3">
+        <v>152000</v>
+      </c>
+      <c r="F58" s="3">
         <v>176100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>414300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>398800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>395300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>736500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>753100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>963300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>3081900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>1637700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>1856900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>1853800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>1717600</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>1987100</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>3508300</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>3895400</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>4845600</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>3966000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>3901700</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>4094900</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>3225900</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>3675300</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>3259700</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>3470000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>1968700</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>1004200</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>1045200</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AF58" s="3">
         <v>1055400</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AG58" s="3">
         <v>905600</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AH58" s="3">
         <v>700600</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AI58" s="3">
         <v>708200</v>
       </c>
     </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>15813900</v>
+      </c>
+      <c r="E59" s="3">
+        <v>15401700</v>
+      </c>
+      <c r="F59" s="3">
         <v>16266100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>15769100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>15695000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>15925100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>17343400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>17673600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>18396800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>18640900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>19546000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>17995800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>16166600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>15433300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>15165700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>12541100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>11673600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>10902800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>12601600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>12280300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>12013500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>10834600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>11768900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>12050400</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>11625600</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>11040300</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>12086600</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>12009800</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>10788000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>11778300</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>12984600</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AI59" s="3">
         <v>11364000</v>
       </c>
     </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>28839000</v>
+      </c>
+      <c r="E60" s="3">
+        <v>26059200</v>
+      </c>
+      <c r="F60" s="3">
         <v>26700700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>27055700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>25378000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>26093400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>28917200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>30775300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>32969700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>32758700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>33700300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>31344700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>29218600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>27371600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>27120700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>24575100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>23375100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>23258100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>25233500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>24039700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>22845100</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>20490300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>22784100</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>22592000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>23015300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>19459700</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>20589000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>20295000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>18052500</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>18333800</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>19848000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AI60" s="3">
         <v>17831000</v>
       </c>
     </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2833100</v>
+      </c>
+      <c r="E61" s="3">
+        <v>3809700</v>
+      </c>
+      <c r="F61" s="3">
         <v>3826700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>3907300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>3972800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>3964000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>4180700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>4185100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>2890000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>2896300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>3619300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>3627000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>3622000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>3632800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>4246500</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>2873000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>2867400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>1911400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>2498400</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>2452800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>2462800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>2426800</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>1821200</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>1820100</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>1842200</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>2648700</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>2617700</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>2591300</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AF61" s="3">
         <v>2579200</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AG61" s="3">
         <v>2966700</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AH61" s="3">
         <v>2465200</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AI61" s="3">
         <v>2487500</v>
       </c>
     </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2747200</v>
+      </c>
+      <c r="E62" s="3">
+        <v>2800900</v>
+      </c>
+      <c r="F62" s="3">
         <v>2863900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>2715200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>2716600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>2815700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>2847200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>2706100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>2803700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>3460800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>3534700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>3464100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>3460000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>3375600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>3367000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>3179700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>3022200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>2899300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>2999200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>2882400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>2846900</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>2974300</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>2803400</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>2521900</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>2115800</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>1839700</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>1916700</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>1848900</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>1817100</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>1790200</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AH62" s="3">
         <v>1856000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AI62" s="3">
         <v>3583200</v>
       </c>
     </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5503,8 +5801,14 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5598,8 +5902,14 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5693,103 +6003,115 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>34922100</v>
+      </c>
+      <c r="E66" s="3">
+        <v>33168400</v>
+      </c>
+      <c r="F66" s="3">
         <v>33903900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>34129500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>32515200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>33332500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>36424100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>38109200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>39068600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>39519800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>41162200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>38571700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>36400300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>34431600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>34758400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>30568500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>29159200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>27937000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>30588700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>29147100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>27899500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>25598400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>27099800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>26872400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>26971200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>23981900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>25154000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>24769900</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>22489200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>23118700</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>24201600</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AI66" s="3">
         <v>23923100</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5823,8 +6145,10 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5918,8 +6242,14 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6013,8 +6343,14 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6108,8 +6444,14 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6203,103 +6545,115 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>4867300</v>
+      </c>
+      <c r="E72" s="3">
+        <v>4741200</v>
+      </c>
+      <c r="F72" s="3">
         <v>4555400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>4429500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>4651900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>4625100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>4590200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>4209700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>4064400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>3841000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>3460100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>2951300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>2796200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>2334600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>2056000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>1803600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>1825700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>1614800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>1603800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>1453200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>1586700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>1424000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>1249300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>1110200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>1242900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>1160100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>1143900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>1531400</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>1684100</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>1756400</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>1610600</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AI72" s="3">
         <v>1616600</v>
       </c>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6393,8 +6747,14 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6488,8 +6848,14 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6583,103 +6949,115 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>5562600</v>
+      </c>
+      <c r="E76" s="3">
+        <v>5582600</v>
+      </c>
+      <c r="F76" s="3">
         <v>5600400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>5127200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>5409100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>5587600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>5324600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>5184300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>5179900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>4990600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>4484000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>4003000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>4060400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>3559000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>3886800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>4515700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>4335800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>4191200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>4437600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>4242300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>4512100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>4390100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>4178800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>4015000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>4340200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>4512300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>4345400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>4153700</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>4137600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>4067300</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>3002200</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AI76" s="3">
         <v>3161400</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6773,203 +7151,221 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>42825</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>243400</v>
+      </c>
+      <c r="E81" s="3">
+        <v>247700</v>
+      </c>
+      <c r="F81" s="3">
         <v>337000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>249200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>176500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>113600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>437200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>541200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>515700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>412200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>639600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>512000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>466100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>260200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>395100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>310200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>212800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>42600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>258100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>202200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>162200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>118100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>232800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>168400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>77000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>32700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>-288800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>139000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>-72300</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>106900</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>98400</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AI81" s="3">
         <v>156800</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7003,103 +7399,111 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
+      <c r="D83" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E83" s="3">
+        <v>368200</v>
+      </c>
+      <c r="F83" s="3">
         <v>357700</v>
       </c>
-      <c r="E83" s="3">
-        <v>347700</v>
-      </c>
-      <c r="F83" s="3">
-        <v>339600</v>
-      </c>
       <c r="G83" s="3">
+        <v>687300</v>
+      </c>
+      <c r="H83" s="3">
+        <v>-1013100</v>
+      </c>
+      <c r="I83" s="3">
         <v>337500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>350300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>333500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>331400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>326600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>317400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>313100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>307300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>294600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>260000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>257100</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>248300</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>266500</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>251200</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>232700</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>219300</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>204100</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>199800</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>206800</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>188000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>193300</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AD83" s="3">
         <v>190100</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AE83" s="3">
         <v>180300</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AF83" s="3">
         <v>174900</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AG83" s="3">
         <v>176400</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AH83" s="3">
         <v>181400</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AI83" s="3">
         <v>191300</v>
       </c>
     </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7193,8 +7597,14 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7288,8 +7698,14 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7383,8 +7799,14 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7478,8 +7900,14 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7573,103 +8001,115 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
+      <c r="D89" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E89" s="3">
+        <v>543300</v>
+      </c>
+      <c r="F89" s="3">
         <v>364200</v>
       </c>
-      <c r="E89" s="3">
-        <v>453800</v>
-      </c>
-      <c r="F89" s="3">
-        <v>649800</v>
-      </c>
       <c r="G89" s="3">
+        <v>1103600</v>
+      </c>
+      <c r="H89" s="3">
+        <v>-2151600</v>
+      </c>
+      <c r="I89" s="3">
         <v>244400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>74000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>2084300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>398700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>1462500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>606300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>1560600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>447600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>601400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>1962900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>771400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>317100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>431600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>538300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>1381600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>-141600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>-478100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>1547600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>67100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>336000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>-753500</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>210900</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>363600</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>-577400</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>207600</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>345500</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AI89" s="3">
         <v>1558700</v>
       </c>
     </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7703,103 +8143,111 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-253500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-355700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-345200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-331500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-374200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-434400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-383400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
+        <v>-383400</v>
+      </c>
+      <c r="L91" s="3">
         <v>-386200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-364500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-361800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-278500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-279300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-111400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-71600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-69600</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-50200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-68600</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-71900</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-75000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-31200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-76200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-86400</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-34900</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-37200</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-61300</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-55300</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-44600</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AF91" s="3">
         <v>-56700</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AG91" s="3">
         <v>-177300</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AH91" s="3">
         <v>-181700</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AI91" s="3">
         <v>-154700</v>
       </c>
     </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7893,8 +8341,14 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7988,103 +8442,115 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
+      <c r="D94" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-250300</v>
+      </c>
+      <c r="F94" s="3">
         <v>-364400</v>
       </c>
-      <c r="E94" s="3">
-        <v>-468700</v>
-      </c>
-      <c r="F94" s="3">
-        <v>-200000</v>
-      </c>
       <c r="G94" s="3">
+        <v>-668700</v>
+      </c>
+      <c r="H94" s="3">
+        <v>1715000</v>
+      </c>
+      <c r="I94" s="3">
         <v>-314000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-407200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-806000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-387800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-574100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-389300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-343400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-191600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-279600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-197000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-214300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-285100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-237800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-215400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-200400</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-303400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-181500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-217100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-103700</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-197400</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-173500</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-103200</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-92900</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>-743900</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>-1323900</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AH94" s="3">
         <v>93100</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AI94" s="3">
         <v>-200800</v>
       </c>
     </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8118,103 +8584,111 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>0</v>
+      </c>
+      <c r="E96" s="3">
+        <v>0</v>
+      </c>
+      <c r="F96" s="3">
         <v>-124500</v>
       </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
       <c r="G96" s="3">
-        <v>0</v>
+        <v>-458800</v>
       </c>
       <c r="H96" s="3">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3">
+        <v>0</v>
+      </c>
+      <c r="J96" s="3">
         <v>-123400</v>
       </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
-      </c>
       <c r="K96" s="3">
         <v>0</v>
       </c>
       <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3">
         <v>-119800</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
       <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3">
         <v>100</v>
       </c>
-      <c r="P96" s="3">
+      <c r="R96" s="3">
         <v>-102000</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
-      <c r="R96" s="3">
-        <v>0</v>
-      </c>
       <c r="S96" s="3">
         <v>0</v>
       </c>
       <c r="T96" s="3">
+        <v>0</v>
+      </c>
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
         <v>-96400</v>
       </c>
-      <c r="U96" s="3">
-        <v>0</v>
-      </c>
-      <c r="V96" s="3">
-        <v>0</v>
-      </c>
       <c r="W96" s="3">
         <v>0</v>
       </c>
       <c r="X96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-91400</v>
       </c>
-      <c r="Y96" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z96" s="3">
-        <v>0</v>
-      </c>
       <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC96" s="3">
         <v>3300</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AD96" s="3">
         <v>-92300</v>
       </c>
-      <c r="AC96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD96" s="3">
-        <v>0</v>
-      </c>
       <c r="AE96" s="3">
         <v>0</v>
       </c>
       <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-85100</v>
       </c>
-      <c r="AG96" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8308,8 +8782,14 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8403,8 +8883,14 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8498,289 +8984,313 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
+      <c r="D100" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-154500</v>
+      </c>
+      <c r="F100" s="3">
         <v>-323400</v>
       </c>
-      <c r="E100" s="3">
-        <v>-574900</v>
-      </c>
-      <c r="F100" s="3">
-        <v>-283400</v>
-      </c>
       <c r="G100" s="3">
+        <v>-858200</v>
+      </c>
+      <c r="H100" s="3">
+        <v>130400</v>
+      </c>
+      <c r="I100" s="3">
         <v>-729100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-301500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>625300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-8500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-750100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-110400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-717100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-179800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-1224700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-1524500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-387900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-91100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-69000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-157600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-524100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>512300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-86000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>-165100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>-317800</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>691600</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>1071600</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>395000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>-525700</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>-66500</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>1318500</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AH100" s="3">
         <v>-117800</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AI100" s="3">
         <v>-1014900</v>
       </c>
     </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
+      <c r="D101" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-44800</v>
+      </c>
+      <c r="F101" s="3">
         <v>52800</v>
       </c>
-      <c r="E101" s="3">
-        <v>-28000</v>
-      </c>
-      <c r="F101" s="3">
-        <v>-61600</v>
-      </c>
       <c r="G101" s="3">
+        <v>-89700</v>
+      </c>
+      <c r="H101" s="3">
+        <v>91200</v>
+      </c>
+      <c r="I101" s="3">
         <v>29900</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>86200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-124300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-144700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>35600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>2400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>-28500</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>31100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>-68900</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>100100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>33800</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>3700</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>-94800</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>44700</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>-63500</v>
       </c>
-      <c r="V101" s="3">
+      <c r="X101" s="3">
         <v>-12800</v>
       </c>
-      <c r="W101" s="3">
+      <c r="Y101" s="3">
         <v>8500</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Z101" s="3">
         <v>22000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="AA101" s="3">
         <v>-46200</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AB101" s="3">
         <v>-65000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AC101" s="3">
         <v>43000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AD101" s="3">
         <v>13700</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AE101" s="3">
         <v>11400</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AF101" s="3">
         <v>20600</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AG101" s="3">
         <v>29300</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AH101" s="3">
         <v>-50800</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AI101" s="3">
         <v>3900</v>
       </c>
     </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3">
+      <c r="D102" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E102" s="3">
+        <v>93700</v>
+      </c>
+      <c r="F102" s="3">
         <v>-270800</v>
       </c>
-      <c r="E102" s="3">
-        <v>-617800</v>
-      </c>
-      <c r="F102" s="3">
-        <v>104700</v>
-      </c>
       <c r="G102" s="3">
+        <v>-513100</v>
+      </c>
+      <c r="H102" s="3">
+        <v>-215100</v>
+      </c>
+      <c r="I102" s="3">
         <v>-768800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-548500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>1779300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-142200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>173800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>109000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>471700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>107400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-971800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>341500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>203000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-55400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>30100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>210000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>593500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>54600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-737000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>1187300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>-400600</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>765100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>187700</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>516500</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>-243600</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>-1367100</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>231600</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>270000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AI102" s="3">
         <v>346900</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/LNVGY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LNVGY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="92">
   <si>
     <t>LNVGY</t>
   </si>
@@ -656,454 +656,467 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42916</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42825</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42735</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3">
-        <v>15447100</v>
-      </c>
-      <c r="E8" s="3">
-        <v>13833100</v>
-      </c>
-      <c r="F8" s="3">
-        <v>15721000</v>
-      </c>
-      <c r="G8" s="3">
-        <v>14409800</v>
-      </c>
-      <c r="H8" s="3">
-        <v>12899900</v>
-      </c>
-      <c r="I8" s="3">
-        <v>12635100</v>
-      </c>
-      <c r="J8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K8" s="3">
         <v>15266600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>17089500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>16955600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>16693800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>20126500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>17868700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>16929200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>15630100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>17245400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>14518900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>13347900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>10579400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>14102800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>13522000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>12512200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>11710300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>14035100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>13379800</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>11912700</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>10638300</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>12938500</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>11760900</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>10012200</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>9578700</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>12168700</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>11231200</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="3">
-        <v>12887200</v>
-      </c>
-      <c r="E9" s="3">
-        <v>11405000</v>
-      </c>
-      <c r="F9" s="3">
-        <v>13119600</v>
-      </c>
-      <c r="G9" s="3">
-        <v>11888000</v>
-      </c>
-      <c r="H9" s="3">
-        <v>10648000</v>
-      </c>
-      <c r="I9" s="3">
-        <v>10491700</v>
-      </c>
-      <c r="J9" s="3">
+      <c r="D9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K9" s="3">
         <v>12654400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>14213000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>14086700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>13829500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>16771300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>14862900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>14105500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>12942200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>14459300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>12266400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>11306500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>8717600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>11838200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>11339400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>10463800</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>9815100</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>11985500</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>11585700</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>10281100</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>9094300</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>11187500</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>10148400</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>8647600</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>8210200</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>10573500</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>9624000</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="3">
-        <v>2559900</v>
-      </c>
-      <c r="E10" s="3">
-        <v>2428100</v>
-      </c>
-      <c r="F10" s="3">
-        <v>2601400</v>
-      </c>
-      <c r="G10" s="3">
-        <v>2521800</v>
-      </c>
-      <c r="H10" s="3">
-        <v>2251900</v>
-      </c>
-      <c r="I10" s="3">
-        <v>2143400</v>
-      </c>
-      <c r="J10" s="3">
+      <c r="D10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K10" s="3">
         <v>2612200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2876500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2868900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2864300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>3355200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>3005800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2823700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2687900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2786100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2252500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>2041400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1861800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>2264600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>2182600</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>2048400</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1895200</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>2049600</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1794100</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1631600</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1544000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1751000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1612500</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1364600</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1368500</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1595200</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>1607200</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1139,109 +1152,113 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3">
-        <v>476000</v>
-      </c>
-      <c r="E12" s="3">
-        <v>531700</v>
-      </c>
-      <c r="F12" s="3">
-        <v>546600</v>
-      </c>
-      <c r="G12" s="3">
-        <v>498200</v>
-      </c>
-      <c r="H12" s="3">
-        <v>451000</v>
-      </c>
-      <c r="I12" s="3">
-        <v>549600</v>
-      </c>
-      <c r="J12" s="3">
+      <c r="D12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K12" s="3">
         <v>578600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>555700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>511400</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>575800</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>549200</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>482000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>466500</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>416700</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>398100</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>306500</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>332600</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>347200</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>341200</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>318000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>329300</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>371300</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>272800</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>312300</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>309900</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>326800</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>344400</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>310900</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>291600</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>338700</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>318400</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>348800</v>
       </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1341,28 +1358,31 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E14" s="3">
-        <v>-4100</v>
+      <c r="E14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G14" s="3">
-        <v>-4100</v>
+      <c r="G14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="I14" s="3">
-        <v>-16900</v>
+      <c r="I14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>10</v>
@@ -1373,8 +1393,8 @@
       <c r="L14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -1415,17 +1435,17 @@
       <c r="Z14" s="3">
         <v>0</v>
       </c>
-      <c r="AA14" s="3" t="s">
-        <v>10</v>
+      <c r="AA14" s="3">
+        <v>0</v>
       </c>
       <c r="AB14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD14" s="3" t="s">
-        <v>10</v>
+      <c r="AC14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD14" s="3">
+        <v>0</v>
       </c>
       <c r="AE14" s="3" t="s">
         <v>10</v>
@@ -1433,40 +1453,43 @@
       <c r="AF14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AG14" s="3">
-        <v>0</v>
+      <c r="AG14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI14" s="3">
         <v>1000</v>
       </c>
-      <c r="AI14" s="3" t="s">
+      <c r="AJ14" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3">
-        <v>0</v>
-      </c>
-      <c r="E15" s="3">
-        <v>0</v>
-      </c>
-      <c r="F15" s="3">
-        <v>0</v>
-      </c>
-      <c r="G15" s="3">
-        <v>0</v>
-      </c>
-      <c r="H15" s="3">
-        <v>0</v>
-      </c>
-      <c r="I15" s="3">
-        <v>0</v>
-      </c>
-      <c r="J15" s="3">
-        <v>0</v>
+      <c r="D15" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1543,8 +1566,11 @@
       <c r="AI15" s="3">
         <v>0</v>
       </c>
+      <c r="AJ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1577,210 +1603,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3">
-        <v>14952600</v>
-      </c>
-      <c r="E17" s="3">
-        <v>13340300</v>
-      </c>
-      <c r="F17" s="3">
-        <v>15108000</v>
-      </c>
-      <c r="G17" s="3">
-        <v>13891700</v>
-      </c>
-      <c r="H17" s="3">
-        <v>12509900</v>
-      </c>
-      <c r="I17" s="3">
-        <v>12327500</v>
-      </c>
-      <c r="J17" s="3">
+      <c r="D17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K17" s="3">
         <v>14516700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>16238600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>16178400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>16105000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>19194100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>17052100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>16186500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>15151300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>16544200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>13954400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>12912000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>10413300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>13614700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>13080200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>12169500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>11436800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>13600700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>13090300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>11732400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>10537600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>12734100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>11673200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>10018300</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>9504800</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>12030700</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>11015800</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3">
-        <v>494500</v>
-      </c>
-      <c r="E18" s="3">
-        <v>492800</v>
-      </c>
-      <c r="F18" s="3">
-        <v>613000</v>
-      </c>
-      <c r="G18" s="3">
-        <v>518100</v>
-      </c>
-      <c r="H18" s="3">
-        <v>390000</v>
-      </c>
-      <c r="I18" s="3">
-        <v>307600</v>
-      </c>
-      <c r="J18" s="3">
+      <c r="D18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K18" s="3">
         <v>750000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>850900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>777200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>588800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>932400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>816600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>742700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>478800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>701200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>564500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>435900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>166100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>488100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>441800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>342700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>273500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>434400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>289500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>180300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>100700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>204400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>87700</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-6100</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>73900</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>138000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>215400</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1816,513 +1849,529 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>-111900</v>
-      </c>
-      <c r="E20" s="3">
-        <v>-109400</v>
-      </c>
-      <c r="F20" s="3">
-        <v>-74900</v>
-      </c>
-      <c r="G20" s="3">
-        <v>-96700</v>
-      </c>
-      <c r="H20" s="3">
-        <v>-92300</v>
-      </c>
-      <c r="I20" s="3">
-        <v>-102600</v>
-      </c>
-      <c r="J20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K20" s="3">
         <v>-59800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-46500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-24600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-8100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-12100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-6700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-27400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-30100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-36300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-33100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-39700</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-26100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-34700</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-66000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-32500</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-26200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-23500</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-22100</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-12000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-14100</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-12500</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-9300</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-10200</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-2500</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>10300</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E21" s="3">
-        <v>751600</v>
-      </c>
-      <c r="F21" s="3">
-        <v>895700</v>
-      </c>
-      <c r="G21" s="3">
-        <v>1108700</v>
-      </c>
-      <c r="H21" s="3">
-        <v>-715300</v>
-      </c>
-      <c r="I21" s="3">
-        <v>542500</v>
-      </c>
-      <c r="J21" s="3">
+      <c r="E21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K21" s="3">
         <v>1040400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1137900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1084000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>907400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1237700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1123000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1022700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>743300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>924900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>788500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>644500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>406600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>704700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>608500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>529500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>451400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>610700</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>474200</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>356300</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>279800</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>382000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>258700</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>158500</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>247700</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>329700</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>406500</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>69600</v>
-      </c>
-      <c r="E22" s="3">
-        <v>74800</v>
-      </c>
-      <c r="F22" s="3">
-        <v>67000</v>
-      </c>
-      <c r="G22" s="3">
-        <v>63700</v>
-      </c>
-      <c r="H22" s="3">
-        <v>69700</v>
-      </c>
-      <c r="I22" s="3">
-        <v>74600</v>
-      </c>
-      <c r="J22" s="3">
+      <c r="D22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K22" s="3">
         <v>85100</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>94300</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>62100</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>60600</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>65100</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>67700</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>65100</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>68500</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>73400</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>61000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>64100</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>62800</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>63200</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>65700</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>70100</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>67100</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>60600</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>54200</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>55500</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>49700</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>41600</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>43100</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>52900</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>56100</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>46900</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>47400</v>
       </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3">
-        <v>313000</v>
-      </c>
-      <c r="E23" s="3">
-        <v>308700</v>
-      </c>
-      <c r="F23" s="3">
-        <v>471000</v>
-      </c>
-      <c r="G23" s="3">
-        <v>357600</v>
-      </c>
-      <c r="H23" s="3">
-        <v>228100</v>
-      </c>
-      <c r="I23" s="3">
-        <v>130400</v>
-      </c>
-      <c r="J23" s="3">
+      <c r="D23" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K23" s="3">
         <v>605000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>710100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>690500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>520200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>855200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>742100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>650200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>380300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>591500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>470400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>332100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>77300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>390200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>310100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>240100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>180200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>350300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>213300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>112800</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>36800</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>150300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>35300</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-69300</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>15200</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>101300</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>167800</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>59500</v>
-      </c>
-      <c r="E24" s="3">
-        <v>55600</v>
-      </c>
-      <c r="F24" s="3">
-        <v>94200</v>
-      </c>
-      <c r="G24" s="3">
-        <v>68600</v>
-      </c>
-      <c r="H24" s="3">
-        <v>44700</v>
-      </c>
-      <c r="I24" s="3">
-        <v>24800</v>
-      </c>
-      <c r="J24" s="3">
+      <c r="D24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K24" s="3">
         <v>123100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>156200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>151000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>98800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>173500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>185100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>165100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>95100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>160000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>120800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>85300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>13900</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>84700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>66400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>48200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>46700</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>85500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>39800</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>27500</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-11600</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>424800</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-117800</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-15400</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-88500</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>-5700</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>15800</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2422,210 +2471,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3">
-        <v>253500</v>
-      </c>
-      <c r="E26" s="3">
-        <v>253000</v>
-      </c>
-      <c r="F26" s="3">
-        <v>376800</v>
-      </c>
-      <c r="G26" s="3">
-        <v>289100</v>
-      </c>
-      <c r="H26" s="3">
-        <v>183400</v>
-      </c>
-      <c r="I26" s="3">
-        <v>105600</v>
-      </c>
-      <c r="J26" s="3">
+      <c r="D26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K26" s="3">
         <v>481900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>553800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>539500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>421400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>681700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>557100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>485200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>285200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>431400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>349600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>246800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>63400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>305500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>243600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>191900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>133600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>264800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>173500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>85300</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>48400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-274500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>153200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-53900</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>103700</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>107100</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>152000</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3">
-        <v>243400</v>
-      </c>
-      <c r="E27" s="3">
-        <v>247700</v>
-      </c>
-      <c r="F27" s="3">
-        <v>337000</v>
-      </c>
-      <c r="G27" s="3">
-        <v>249200</v>
-      </c>
-      <c r="H27" s="3">
-        <v>176500</v>
-      </c>
-      <c r="I27" s="3">
-        <v>113600</v>
-      </c>
-      <c r="J27" s="3">
+      <c r="D27" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K27" s="3">
         <v>437200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>541200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>515700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>412200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>639600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>512000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>466100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>260200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>395100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>310200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>212800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>42600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>258100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>202200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>162200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>118100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>232800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>168400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>77000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>32700</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-288800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>139000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-72300</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>106900</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>98400</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>156800</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2725,31 +2783,34 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3">
-        <v>0</v>
-      </c>
-      <c r="E29" s="3">
-        <v>0</v>
-      </c>
-      <c r="F29" s="3">
-        <v>0</v>
-      </c>
-      <c r="G29" s="3">
-        <v>0</v>
-      </c>
-      <c r="H29" s="3">
-        <v>0</v>
-      </c>
-      <c r="I29" s="3">
-        <v>0</v>
-      </c>
-      <c r="J29" s="3">
-        <v>0</v>
+      <c r="D29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="K29" s="3">
         <v>0</v>
@@ -2826,8 +2887,11 @@
       <c r="AI29" s="3">
         <v>0</v>
       </c>
+      <c r="AJ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2927,8 +2991,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3028,210 +3095,219 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>111900</v>
-      </c>
-      <c r="E32" s="3">
-        <v>109400</v>
-      </c>
-      <c r="F32" s="3">
-        <v>74900</v>
-      </c>
-      <c r="G32" s="3">
-        <v>96700</v>
-      </c>
-      <c r="H32" s="3">
-        <v>92300</v>
-      </c>
-      <c r="I32" s="3">
-        <v>102600</v>
-      </c>
-      <c r="J32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K32" s="3">
         <v>59800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>46500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>24600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>8100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>12100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>6700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>27400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>30100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>36300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>33100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>39700</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>26100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>34700</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>66000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>32500</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>26200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>23500</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>22100</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>12000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>14100</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>12500</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>9300</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>10200</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>2500</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-10300</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3">
-        <v>243400</v>
-      </c>
-      <c r="E33" s="3">
-        <v>247700</v>
-      </c>
-      <c r="F33" s="3">
-        <v>337000</v>
-      </c>
-      <c r="G33" s="3">
-        <v>249200</v>
-      </c>
-      <c r="H33" s="3">
-        <v>176500</v>
-      </c>
-      <c r="I33" s="3">
-        <v>113600</v>
-      </c>
-      <c r="J33" s="3">
+      <c r="D33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K33" s="3">
         <v>437200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>541200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>515700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>412200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>639600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>512000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>466100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>260200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>395100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>310200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>212800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>42600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>258100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>202200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>162200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>118100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>232800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>168400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>77000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>32700</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-288800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>139000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-72300</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>106900</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>98400</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>156800</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3331,215 +3407,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3">
-        <v>243400</v>
-      </c>
-      <c r="E35" s="3">
-        <v>247700</v>
-      </c>
-      <c r="F35" s="3">
-        <v>337000</v>
-      </c>
-      <c r="G35" s="3">
-        <v>249200</v>
-      </c>
-      <c r="H35" s="3">
-        <v>176500</v>
-      </c>
-      <c r="I35" s="3">
-        <v>113600</v>
-      </c>
-      <c r="J35" s="3">
+      <c r="D35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K35" s="3">
         <v>437200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>541200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>515700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>412200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>639600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>512000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>466100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>260200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>395100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>310200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>212800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>42600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>258100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>202200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>162200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>118100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>232800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>168400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>77000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>32700</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-288800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>139000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-72300</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>106900</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>98400</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>156800</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42916</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42825</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42735</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3575,8 +3660,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3612,917 +3698,945 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>4178900</v>
+      </c>
+      <c r="E41" s="3">
         <v>3911100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3559800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3466200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3737000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>4354800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>4250100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>5018900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>5567400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>3788100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>3930300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>3756500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>3647500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>3175800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>3068400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>4040100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>3698700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>3495600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>3551000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>3520900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>3310900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>2717400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>2662900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>3399900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>2212500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>2613100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1848000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1660300</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1143800</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1387500</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>2754600</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>2523000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>2253100</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>62000</v>
+        <v>114500</v>
       </c>
       <c r="E42" s="3">
-        <v>65600</v>
+        <v>113600</v>
       </c>
       <c r="F42" s="3">
-        <v>66600</v>
+        <v>60400</v>
       </c>
       <c r="G42" s="3">
-        <v>62000</v>
+        <v>100800</v>
       </c>
       <c r="H42" s="3">
-        <v>68400</v>
+        <v>118000</v>
       </c>
       <c r="I42" s="3">
-        <v>71200</v>
+        <v>249900</v>
       </c>
       <c r="J42" s="3">
+        <v>198000</v>
+      </c>
+      <c r="K42" s="3">
         <v>61800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>60400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>57600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>92500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>72500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>83500</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>82800</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>59400</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>51100</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>54000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>50700</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>66500</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>65100</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>65200</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>70600</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>70200</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>108600</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>112300</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>75900</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>84300</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>86500</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>118200</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>153600</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>196700</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>162200</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>196600</v>
       </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>13431900</v>
+      </c>
+      <c r="E43" s="3">
         <v>11384500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>10936700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>12059400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>11595000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>10125900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>10236200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>11854000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>12346700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>14797200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>15244900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>16798400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>13698200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>13029500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>12518900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>13537100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>11207200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>10257700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>8850900</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>12562500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>11648000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>11474800</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>9481000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>10010500</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>10509900</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>10307200</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>8557600</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>9712800</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>9751000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>8075700</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>8062800</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>8914800</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>8875200</v>
       </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>9118800</v>
+      </c>
+      <c r="E44" s="3">
         <v>7777600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>6702700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>6218900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>6169600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>5907200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>6371900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>7502100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>8417900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>8867700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>8300700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>8441600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>8727800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>7825800</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>6380600</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>5785800</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>5242300</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>5126700</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>4946900</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>3998400</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>3816900</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>3573000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>3434700</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>3792300</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>4280900</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>4125100</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>3791700</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>3983300</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>3600000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>3177500</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>2794000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>2833600</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>2882800</v>
       </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>1422100</v>
+        <v>29900</v>
       </c>
       <c r="E45" s="3">
-        <v>1422400</v>
+        <v>94400</v>
       </c>
       <c r="F45" s="3">
-        <v>1416700</v>
+        <v>127600</v>
       </c>
       <c r="G45" s="3">
-        <v>1845600</v>
+        <v>15400</v>
       </c>
       <c r="H45" s="3">
-        <v>1818200</v>
+        <v>107200</v>
       </c>
       <c r="I45" s="3">
-        <v>2011600</v>
+        <v>98900</v>
       </c>
       <c r="J45" s="3">
+        <v>97800</v>
+      </c>
+      <c r="K45" s="3">
         <v>1695300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1725700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1594500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1428500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1413800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1414700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1396500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1308100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1036400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1102900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1116900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1318200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1299100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1275600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1172300</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1237500</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1168400</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1211800</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1524900</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1381800</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1502200</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1419700</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>1354900</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>1060200</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>980200</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>930100</v>
       </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>28206500</v>
+      </c>
+      <c r="E46" s="3">
         <v>24557300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>22687200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>23227800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>23409200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>22274500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>22940900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>26132000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>28118100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>29105000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>28996900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>30482800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>27571700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>25510300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>23335400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>24450500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>21305000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>20047600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>18733400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>21446000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>20116800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>19008100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>16886200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>18479800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>18327500</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>18646200</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>15663300</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>16945200</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>16032700</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>14149300</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>14868400</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>15413900</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>15137700</v>
       </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1843100</v>
+      </c>
+      <c r="E47" s="3">
         <v>1772500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1768400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1718700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1719600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1637400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1738400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1673800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1554800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1543800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1508500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1293600</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1193400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1120400</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>955300</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>939200</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>844200</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>701700</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>611300</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>618200</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>556300</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>554700</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>599900</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>559700</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>506600</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>431900</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>408700</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>392900</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>366600</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>304700</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>288500</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>236300</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>215000</v>
       </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2893100</v>
+      </c>
+      <c r="E48" s="3">
         <v>2831000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2919100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2999300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3157900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3123800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3303900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>3174200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2788700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2846700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2986100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2834000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2711600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2657000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2674900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>2565700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>2555100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>2472500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>2017100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>2016100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1937900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1936400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1662900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>1568900</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>1514700</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>1636000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>1687600</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>1663500</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>1706600</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>1716100</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>1649400</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>1588100</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>1593000</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>8257700</v>
+      </c>
+      <c r="E49" s="3">
         <v>8198800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>8345400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>8519200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>8174800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>8190500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>8267100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>8184600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>8048700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>7849700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>8066800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>8138300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>8238900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>8447600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>8405000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>8152100</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>7980100</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>7991500</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>7984600</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>8230900</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>8196700</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>8391500</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>8324600</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>8296700</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>8286300</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>8426900</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>8514500</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>8416300</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>8448400</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>8317200</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>8349100</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>8313800</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>8560500</v>
       </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4622,8 +4736,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4723,109 +4840,115 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>3125000</v>
+        <v>467300</v>
       </c>
       <c r="E52" s="3">
-        <v>3030800</v>
+        <v>420100</v>
       </c>
       <c r="F52" s="3">
-        <v>3039200</v>
+        <v>397500</v>
       </c>
       <c r="G52" s="3">
-        <v>2795100</v>
+        <v>408000</v>
       </c>
       <c r="H52" s="3">
-        <v>2698100</v>
+        <v>284700</v>
       </c>
       <c r="I52" s="3">
-        <v>2669800</v>
+        <v>210200</v>
       </c>
       <c r="J52" s="3">
+        <v>202500</v>
+      </c>
+      <c r="K52" s="3">
         <v>2584100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2783200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2903300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2952200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>2897500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2859000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>2725300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>2620100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>2537600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>2399800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>2281700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>2781800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>2715100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>2581700</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>2520900</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>2514900</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>2373500</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>2252300</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>2170400</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>2220000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>2081500</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>2369200</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>2139600</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>2030600</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>1651600</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>1578300</v>
       </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4925,109 +5048,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>44464300</v>
+      </c>
+      <c r="E54" s="3">
         <v>40484700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>38751000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>39504300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>39256700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>37924400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>38920100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>41748600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>43293500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>44248500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>44510400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>45646200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>42574700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>40460600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>37990600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>38645100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>35084200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>33495000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>32128200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>35026300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>33389400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>32411600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>29988500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>31278600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>30887400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>31311400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>28494200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>29499400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>28923600</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>26626800</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>27186000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>27203800</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>27084500</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5063,8 +5192,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5100,614 +5230,633 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>14229400</v>
+      </c>
+      <c r="E57" s="3">
         <v>11924600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>10505400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>10258500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>10872300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>9284200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>9772900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>10837300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>12348700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>13609600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>11035900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>12516700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>11492000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>11198200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>10220800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>9968000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>8525700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>7806100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>7509700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>8665800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>7857700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>6736700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>6429800</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>7339800</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>7281900</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>7919600</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>6450800</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>7498200</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>7240100</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>6209100</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>5649900</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>6162700</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>5758900</v>
       </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1120100</v>
+      </c>
+      <c r="E58" s="3">
         <v>1100500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>152000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>176100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>414300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>398800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>395300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>736500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>753100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>963300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>3081900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1637700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1856900</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1853800</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1717600</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1987100</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>3508300</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>3895400</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>4845600</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>3966000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>3901700</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>4094900</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>3225900</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>3675300</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>3259700</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>3470000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1968700</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1004200</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1045200</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1055400</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>905600</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>700600</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>708200</v>
       </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>15813900</v>
+        <v>13446700</v>
       </c>
       <c r="E59" s="3">
-        <v>15401700</v>
+        <v>12443900</v>
       </c>
       <c r="F59" s="3">
-        <v>16266100</v>
+        <v>12074400</v>
       </c>
       <c r="G59" s="3">
-        <v>15769100</v>
+        <v>13078100</v>
       </c>
       <c r="H59" s="3">
-        <v>15695000</v>
+        <v>12621300</v>
       </c>
       <c r="I59" s="3">
-        <v>15925100</v>
+        <v>12570400</v>
       </c>
       <c r="J59" s="3">
+        <v>12361500</v>
+      </c>
+      <c r="K59" s="3">
         <v>17343400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>17673600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>18396800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>18640900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>19546000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>17995800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>16166600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>15433300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>15165700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>12541100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>11673600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>10902800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>12601600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>12280300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>12013500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>10834600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>11768900</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>12050400</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>11625600</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>11040300</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>12086600</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>12009800</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>10788000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>11778300</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>12984600</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>11364000</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>32682100</v>
+      </c>
+      <c r="E60" s="3">
         <v>28839000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>26059200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>26700700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>27055700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>25378000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>26093400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>28917200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>30775300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>32969700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>32758700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>33700300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>31344700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>29218600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>27371600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>27120700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>24575100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>23375100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>23258100</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>25233500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>24039700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>22845100</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>20490300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>22784100</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>22592000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>23015300</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>19459700</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>20589000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>20295000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>18052500</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>18333800</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>19848000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>17831000</v>
       </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2830700</v>
+      </c>
+      <c r="E61" s="3">
         <v>2833100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>3809700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>3826700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>3907300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>3972800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>3964000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>4180700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>4185100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2890000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2896300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3619300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>3627000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>3622000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>3632800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>4246500</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2873000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2867400</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1911400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>2498400</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>2452800</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>2462800</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>2426800</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1821200</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1820100</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1842200</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>2648700</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>2617700</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>2591300</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>2579200</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>2966700</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>2465200</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>2487500</v>
       </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>2747200</v>
+        <v>520500</v>
       </c>
       <c r="E62" s="3">
-        <v>2800900</v>
+        <v>504600</v>
       </c>
       <c r="F62" s="3">
-        <v>2863900</v>
+        <v>574400</v>
       </c>
       <c r="G62" s="3">
-        <v>2715200</v>
+        <v>616000</v>
       </c>
       <c r="H62" s="3">
-        <v>2716600</v>
+        <v>584800</v>
       </c>
       <c r="I62" s="3">
-        <v>2815700</v>
+        <v>591500</v>
       </c>
       <c r="J62" s="3">
+        <v>642700</v>
+      </c>
+      <c r="K62" s="3">
         <v>2847200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2706100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2803700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3460800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3534700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>3464100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>3460000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>3375600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>3367000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>3179700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>3022200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>2899300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>2999200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>2882400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>2846900</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>2974300</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>2803400</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>2521900</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>2115800</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>1839700</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>1916700</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>1848900</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>1817100</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>1790200</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>1856000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>3583200</v>
       </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5807,8 +5956,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5908,8 +6060,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6009,109 +6164,115 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>34922100</v>
+        <v>38372800</v>
       </c>
       <c r="E66" s="3">
-        <v>33168400</v>
+        <v>34419300</v>
       </c>
       <c r="F66" s="3">
-        <v>33903900</v>
+        <v>32669800</v>
       </c>
       <c r="G66" s="3">
-        <v>34129500</v>
+        <v>33391300</v>
       </c>
       <c r="H66" s="3">
-        <v>32515200</v>
+        <v>33678200</v>
       </c>
       <c r="I66" s="3">
-        <v>33332500</v>
+        <v>32067400</v>
       </c>
       <c r="J66" s="3">
+        <v>32873000</v>
+      </c>
+      <c r="K66" s="3">
         <v>36424100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>38109200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>39068600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>39519800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>41162200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>38571700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>36400300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>34431600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>34758400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>30568500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>29159200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>27937000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>30588700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>29147100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>27899500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>25598400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>27099800</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>26872400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>26971200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>23981900</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>25154000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>24769900</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>22489200</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>23118700</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>24201600</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>23923100</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6147,8 +6308,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6248,8 +6410,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6349,8 +6514,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6450,8 +6618,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6551,109 +6722,115 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>4867300</v>
+        <v>5319200</v>
       </c>
       <c r="E72" s="3">
-        <v>4741200</v>
+        <v>5435400</v>
       </c>
       <c r="F72" s="3">
-        <v>4555400</v>
+        <v>5207100</v>
       </c>
       <c r="G72" s="3">
-        <v>4429500</v>
+        <v>4969500</v>
       </c>
       <c r="H72" s="3">
-        <v>4651900</v>
+        <v>4753600</v>
       </c>
       <c r="I72" s="3">
-        <v>4625100</v>
+        <v>4963400</v>
       </c>
       <c r="J72" s="3">
+        <v>4805900</v>
+      </c>
+      <c r="K72" s="3">
         <v>4590200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>4209700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>4064400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>3841000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>3460100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>2951300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>2796200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>2334600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>2056000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>1803600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>1825700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>1614800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>1603800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>1453200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>1586700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>1424000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>1249300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>1110200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>1242900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>1160100</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>1143900</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>1531400</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>1684100</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>1756400</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>1610600</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>1616600</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6753,8 +6930,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6854,8 +7034,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6955,109 +7138,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>5562600</v>
+        <v>4930000</v>
       </c>
       <c r="E76" s="3">
-        <v>5582600</v>
+        <v>5015200</v>
       </c>
       <c r="F76" s="3">
-        <v>5600400</v>
+        <v>5035200</v>
       </c>
       <c r="G76" s="3">
-        <v>5127200</v>
+        <v>5053100</v>
       </c>
       <c r="H76" s="3">
-        <v>5409100</v>
+        <v>4579800</v>
       </c>
       <c r="I76" s="3">
-        <v>5587600</v>
+        <v>4861800</v>
       </c>
       <c r="J76" s="3">
+        <v>5040200</v>
+      </c>
+      <c r="K76" s="3">
         <v>5324600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>5184300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>5179900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>4990600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>4484000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>4003000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>4060400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>3559000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>3886800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>4515700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>4335800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>4191200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>4437600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>4242300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>4512100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>4390100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>4178800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>4015000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>4340200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>4512300</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>4345400</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>4153700</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>4137600</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>4067300</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>3002200</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>3161400</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7157,215 +7346,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42916</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42825</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42735</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3">
-        <v>243400</v>
-      </c>
-      <c r="E81" s="3">
-        <v>247700</v>
-      </c>
-      <c r="F81" s="3">
-        <v>337000</v>
-      </c>
-      <c r="G81" s="3">
-        <v>249200</v>
-      </c>
-      <c r="H81" s="3">
-        <v>176500</v>
-      </c>
-      <c r="I81" s="3">
-        <v>113600</v>
-      </c>
-      <c r="J81" s="3">
+      <c r="D81" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I81" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J81" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K81" s="3">
         <v>437200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>541200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>515700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>412200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>639600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>512000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>466100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>260200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>395100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>310200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>212800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>42600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>258100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>202200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>162200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>118100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>232800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>168400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>77000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>32700</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-288800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>139000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-72300</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>106900</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>98400</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>156800</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7401,109 +7599,113 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>10</v>
+      <c r="D83" s="3">
+        <v>140600</v>
       </c>
       <c r="E83" s="3">
-        <v>368200</v>
+        <v>143000</v>
       </c>
       <c r="F83" s="3">
-        <v>357700</v>
+        <v>143800</v>
       </c>
       <c r="G83" s="3">
-        <v>687300</v>
+        <v>135000</v>
       </c>
       <c r="H83" s="3">
-        <v>-1013100</v>
+        <v>123600</v>
       </c>
       <c r="I83" s="3">
-        <v>337500</v>
+        <v>126300</v>
       </c>
       <c r="J83" s="3">
+        <v>129300</v>
+      </c>
+      <c r="K83" s="3">
         <v>350300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>333500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>331400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>326600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>317400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>313100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>307300</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>294600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>260000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>257100</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>248300</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>266500</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>251200</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>232700</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>219300</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>204100</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>199800</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>206800</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>188000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>193300</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>190100</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>180300</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>174900</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>176400</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>181400</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>191300</v>
       </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7603,8 +7805,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7704,8 +7909,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7805,8 +8013,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7906,8 +8117,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8007,109 +8221,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>10</v>
+      <c r="D89" s="3">
+        <v>986700</v>
       </c>
       <c r="E89" s="3">
+        <v>791400</v>
+      </c>
+      <c r="F89" s="3">
         <v>543300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>364200</v>
       </c>
-      <c r="G89" s="3">
-        <v>1103600</v>
-      </c>
       <c r="H89" s="3">
-        <v>-2151600</v>
+        <v>453800</v>
       </c>
       <c r="I89" s="3">
+        <v>649800</v>
+      </c>
+      <c r="J89" s="3">
         <v>244400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>74000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2084300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>398700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1462500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>606300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1560600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>447600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>601400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1962900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>771400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>317100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>431600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>538300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1381600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-141600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-478100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1547600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>67100</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>336000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-753500</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>210900</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>363600</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-577400</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>207600</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>345500</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>1558700</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8145,109 +8365,113 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-253500</v>
+        <v>-152200</v>
       </c>
       <c r="E91" s="3">
-        <v>-355700</v>
+        <v>-154500</v>
       </c>
       <c r="F91" s="3">
-        <v>-345200</v>
+        <v>-204400</v>
       </c>
       <c r="G91" s="3">
-        <v>-331500</v>
+        <v>-158900</v>
       </c>
       <c r="H91" s="3">
-        <v>-374200</v>
+        <v>-191600</v>
       </c>
       <c r="I91" s="3">
-        <v>-434400</v>
+        <v>-174800</v>
       </c>
       <c r="J91" s="3">
-        <v>-383400</v>
+        <v>-278900</v>
       </c>
       <c r="K91" s="3">
         <v>-383400</v>
       </c>
       <c r="L91" s="3">
+        <v>-383400</v>
+      </c>
+      <c r="M91" s="3">
         <v>-386200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-364500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-361800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-278500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-279300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-111400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-71600</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-69600</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-50200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-68600</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-71900</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-75000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-31200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-76200</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-86400</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-34900</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-37200</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-61300</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-55300</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-44600</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-56700</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-177300</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-181700</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-154700</v>
       </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8347,8 +8571,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8448,109 +8675,115 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>10</v>
+      <c r="D94" s="3">
+        <v>-204900</v>
       </c>
       <c r="E94" s="3">
+        <v>-319800</v>
+      </c>
+      <c r="F94" s="3">
         <v>-250300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-364400</v>
       </c>
-      <c r="G94" s="3">
-        <v>-668700</v>
-      </c>
       <c r="H94" s="3">
-        <v>1715000</v>
+        <v>-468700</v>
       </c>
       <c r="I94" s="3">
+        <v>-200000</v>
+      </c>
+      <c r="J94" s="3">
         <v>-314000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-407200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-806000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-387800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-574100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-389300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-343400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-191600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-279600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-197000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-214300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-285100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-237800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-215400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-200400</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-303400</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-181500</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-217100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-103700</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-197400</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-173500</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-103200</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-92900</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-743900</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-1323900</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>93100</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-200800</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8586,35 +8819,36 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
+        <v>474300</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="F96" s="3">
-        <v>-124500</v>
+        <v>0</v>
       </c>
       <c r="G96" s="3">
-        <v>-458800</v>
+        <v>124500</v>
       </c>
       <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
+        <v>458800</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="J96" s="3">
+        <v>0</v>
+      </c>
+      <c r="K96" s="3">
         <v>-123400</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
       <c r="L96" s="3">
         <v>0</v>
       </c>
@@ -8622,23 +8856,23 @@
         <v>0</v>
       </c>
       <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3">
         <v>-119800</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
       <c r="P96" s="3">
         <v>0</v>
       </c>
       <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3">
         <v>100</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-102000</v>
       </c>
-      <c r="S96" s="3">
-        <v>0</v>
-      </c>
       <c r="T96" s="3">
         <v>0</v>
       </c>
@@ -8646,11 +8880,11 @@
         <v>0</v>
       </c>
       <c r="V96" s="3">
+        <v>0</v>
+      </c>
+      <c r="W96" s="3">
         <v>-96400</v>
       </c>
-      <c r="W96" s="3">
-        <v>0</v>
-      </c>
       <c r="X96" s="3">
         <v>0</v>
       </c>
@@ -8658,23 +8892,23 @@
         <v>0</v>
       </c>
       <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-91400</v>
       </c>
-      <c r="AA96" s="3">
-        <v>0</v>
-      </c>
       <c r="AB96" s="3">
         <v>0</v>
       </c>
       <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD96" s="3">
         <v>3300</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-92300</v>
       </c>
-      <c r="AE96" s="3">
-        <v>0</v>
-      </c>
       <c r="AF96" s="3">
         <v>0</v>
       </c>
@@ -8682,13 +8916,16 @@
         <v>0</v>
       </c>
       <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI96" s="3">
         <v>-85100</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8788,8 +9025,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8889,8 +9129,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8990,307 +9233,319 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>10</v>
+      <c r="D100" s="3">
+        <v>-627000</v>
       </c>
       <c r="E100" s="3">
+        <v>-47200</v>
+      </c>
+      <c r="F100" s="3">
         <v>-154500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-323400</v>
       </c>
-      <c r="G100" s="3">
-        <v>-858200</v>
-      </c>
       <c r="H100" s="3">
-        <v>130400</v>
+        <v>-574900</v>
       </c>
       <c r="I100" s="3">
+        <v>-283400</v>
+      </c>
+      <c r="J100" s="3">
         <v>-729100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-301500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>625300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-8500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-750100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-110400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-717100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-179800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1224700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1524500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-387900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-91100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-69000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-157600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-524100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>512300</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-86000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-165100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-317800</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>691600</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>1071600</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>395000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-525700</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-66500</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>1318500</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-117800</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-1014900</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>10</v>
+      <c r="D101" s="3">
+        <v>-28000</v>
       </c>
       <c r="E101" s="3">
-        <v>-44800</v>
+        <v>-61600</v>
       </c>
       <c r="F101" s="3">
-        <v>52800</v>
+        <v>29900</v>
       </c>
       <c r="G101" s="3">
-        <v>-89700</v>
+        <v>86200</v>
       </c>
       <c r="H101" s="3">
-        <v>91200</v>
+        <v>-124300</v>
       </c>
       <c r="I101" s="3">
-        <v>29900</v>
+        <v>-144700</v>
       </c>
       <c r="J101" s="3">
+        <v>35600</v>
+      </c>
+      <c r="K101" s="3">
         <v>86200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-124300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-144700</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>35600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>2400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-28500</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>31100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-68900</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>100100</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>33800</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>3700</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-94800</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>44700</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-63500</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-12800</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>8500</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>22000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-46200</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-65000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>43000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>13700</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>11400</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>20600</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>29300</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-50800</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>3900</v>
       </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3" t="s">
-        <v>10</v>
+      <c r="D102" s="3">
+        <v>267800</v>
       </c>
       <c r="E102" s="3">
+        <v>351300</v>
+      </c>
+      <c r="F102" s="3">
         <v>93700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-270800</v>
       </c>
-      <c r="G102" s="3">
-        <v>-513100</v>
-      </c>
       <c r="H102" s="3">
-        <v>-215100</v>
+        <v>-617800</v>
       </c>
       <c r="I102" s="3">
+        <v>104700</v>
+      </c>
+      <c r="J102" s="3">
         <v>-768800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-548500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1779300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-142200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>173800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>109000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>471700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>107400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-971800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>341500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>203000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-55400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>30100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>210000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>593500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>54600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-737000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>1187300</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-400600</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>765100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>187700</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>516500</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-243600</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-1367100</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>231600</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>270000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>346900</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/LNVGY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LNVGY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="92">
   <si>
     <t>LNVGY</t>
   </si>
@@ -656,155 +656,158 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43100</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43008</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42916</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42825</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -829,86 +832,89 @@
       <c r="J8" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K8" s="3">
+      <c r="K8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L8" s="3">
         <v>15266600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>17089500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>16955600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>16693800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>20126500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>17868700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>16929200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>15630100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>17245400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>14518900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>13347900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>10579400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>14102800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>13522000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>12512200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>11710300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>14035100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>13379800</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>11912700</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>10638300</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>12938500</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>11760900</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>10012200</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>9578700</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>12168700</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>11231200</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -933,86 +939,89 @@
       <c r="J9" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K9" s="3">
+      <c r="K9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L9" s="3">
         <v>12654400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>14213000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>14086700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>13829500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>16771300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>14862900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>14105500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>12942200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>14459300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>12266400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>11306500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>8717600</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>11838200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>11339400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>10463800</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>9815100</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>11985500</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>11585700</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>10281100</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>9094300</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>11187500</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>10148400</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>8647600</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>8210200</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>10573500</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>9624000</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -1037,86 +1046,89 @@
       <c r="J10" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K10" s="3">
+      <c r="K10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L10" s="3">
         <v>2612200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2876500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2868900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2864300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>3355200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>3005800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2823700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2687900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2786100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>2252500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>2041400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1861800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>2264600</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>2182600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>2048400</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1895200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>2049600</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1794100</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1631600</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1544000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1751000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1612500</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1364600</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1368500</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>1595200</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>1607200</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1153,8 +1165,9 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1179,86 +1192,89 @@
       <c r="J12" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K12" s="3">
+      <c r="K12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L12" s="3">
         <v>578600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>555700</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>511400</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>575800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>549200</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>482000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>466500</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>416700</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>398100</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>306500</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>332600</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>347200</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>341200</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>318000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>329300</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>371300</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>272800</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>312300</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>309900</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>326800</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>344400</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>310900</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>291600</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>338700</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>318400</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>348800</v>
       </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1361,8 +1377,11 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1396,8 +1415,8 @@
       <c r="M14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
+      <c r="N14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="O14" s="3">
         <v>0</v>
@@ -1438,17 +1457,17 @@
       <c r="AA14" s="3">
         <v>0</v>
       </c>
-      <c r="AB14" s="3" t="s">
-        <v>10</v>
+      <c r="AB14" s="3">
+        <v>0</v>
       </c>
       <c r="AC14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AD14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE14" s="3" t="s">
-        <v>10</v>
+      <c r="AD14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE14" s="3">
+        <v>0</v>
       </c>
       <c r="AF14" s="3" t="s">
         <v>10</v>
@@ -1456,17 +1475,20 @@
       <c r="AG14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AH14" s="3">
-        <v>0</v>
+      <c r="AH14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ14" s="3">
         <v>1000</v>
       </c>
-      <c r="AJ14" s="3" t="s">
+      <c r="AK14" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1491,8 +1513,8 @@
       <c r="J15" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
+      <c r="K15" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="L15" s="3">
         <v>0</v>
@@ -1569,8 +1591,11 @@
       <c r="AJ15" s="3">
         <v>0</v>
       </c>
+      <c r="AK15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1604,8 +1629,9 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1630,86 +1656,89 @@
       <c r="J17" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K17" s="3">
+      <c r="K17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L17" s="3">
         <v>14516700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>16238600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>16178400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>16105000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>19194100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>17052100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>16186500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>15151300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>16544200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>13954400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>12912000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>10413300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>13614700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>13080200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>12169500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>11436800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>13600700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>13090300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>11732400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>10537600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>12734100</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>11673200</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>10018300</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>9504800</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>12030700</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>11015800</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1734,86 +1763,89 @@
       <c r="J18" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K18" s="3">
+      <c r="K18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L18" s="3">
         <v>750000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>850900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>777200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>588800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>932400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>816600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>742700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>478800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>701200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>564500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>435900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>166100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>488100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>441800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>342700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>273500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>434400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>289500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>180300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>100700</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>204400</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>87700</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-6100</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>73900</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>138000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>215400</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1850,8 +1882,9 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1876,86 +1909,89 @@
       <c r="J20" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K20" s="3">
+      <c r="K20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L20" s="3">
         <v>-59800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-46500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-24600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-8100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-12100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-6700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-27400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-30100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-36300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-33100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-39700</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-26100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-34700</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-66000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-32500</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-26200</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-23500</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-22100</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-12000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-14100</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-12500</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-9300</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-10200</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-2500</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>10300</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1980,86 +2016,89 @@
       <c r="J21" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K21" s="3">
+      <c r="K21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L21" s="3">
         <v>1040400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1137900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1084000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>907400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1237700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1123000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1022700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>743300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>924900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>788500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>644500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>406600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>704700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>608500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>529500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>451400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>610700</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>474200</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>356300</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>279800</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>382000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>258700</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>158500</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>247700</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>329700</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>406500</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2084,86 +2123,89 @@
       <c r="J22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K22" s="3">
+      <c r="K22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L22" s="3">
         <v>85100</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>94300</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>62100</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>60600</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>65100</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>67700</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>65100</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>68500</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>73400</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>61000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>64100</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>62800</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>63200</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>65700</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>70100</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>67100</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>60600</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>54200</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>55500</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>49700</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>41600</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>43100</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>52900</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>56100</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>46900</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>47400</v>
       </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2188,86 +2230,89 @@
       <c r="J23" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K23" s="3">
+      <c r="K23" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L23" s="3">
         <v>605000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>710100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>690500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>520200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>855200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>742100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>650200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>380300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>591500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>470400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>332100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>77300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>390200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>310100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>240100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>180200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>350300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>213300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>112800</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>36800</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>150300</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>35300</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-69300</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>15200</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>101300</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>167800</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2292,86 +2337,89 @@
       <c r="J24" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K24" s="3">
+      <c r="K24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L24" s="3">
         <v>123100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>156200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>151000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>98800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>173500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>185100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>165100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>95100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>160000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>120800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>85300</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>13900</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>84700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>66400</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>48200</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>46700</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>85500</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>39800</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>27500</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-11600</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>424800</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-117800</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-15400</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>-88500</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>-5700</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>15800</v>
       </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2474,8 +2522,11 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2500,86 +2551,89 @@
       <c r="J26" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K26" s="3">
+      <c r="K26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L26" s="3">
         <v>481900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>553800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>539500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>421400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>681700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>557100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>485200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>285200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>431400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>349600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>246800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>63400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>305500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>243600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>191900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>133600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>264800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>173500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>85300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>48400</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-274500</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>153200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-53900</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>103700</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>107100</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>152000</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2604,86 +2658,89 @@
       <c r="J27" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K27" s="3">
+      <c r="K27" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L27" s="3">
         <v>437200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>541200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>515700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>412200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>639600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>512000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>466100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>260200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>395100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>310200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>212800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>42600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>258100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>202200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>162200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>118100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>232800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>168400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>77000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>32700</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-288800</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>139000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-72300</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>106900</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>98400</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>156800</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2786,8 +2843,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2812,8 +2872,8 @@
       <c r="J29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K29" s="3">
-        <v>0</v>
+      <c r="K29" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="L29" s="3">
         <v>0</v>
@@ -2890,8 +2950,11 @@
       <c r="AJ29" s="3">
         <v>0</v>
       </c>
+      <c r="AK29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2994,8 +3057,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3098,8 +3164,11 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3124,86 +3193,89 @@
       <c r="J32" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K32" s="3">
+      <c r="K32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L32" s="3">
         <v>59800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>46500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>24600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>8100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>12100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>6700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>27400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>30100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>36300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>33100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>39700</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>26100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>34700</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>66000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>32500</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>26200</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>23500</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>22100</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>12000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>14100</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>12500</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>9300</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>10200</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>2500</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-10300</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -3228,86 +3300,89 @@
       <c r="J33" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K33" s="3">
+      <c r="K33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L33" s="3">
         <v>437200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>541200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>515700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>412200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>639600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>512000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>466100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>260200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>395100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>310200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>212800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>42600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>258100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>202200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>162200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>118100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>232800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>168400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>77000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>32700</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-288800</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>139000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-72300</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>106900</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>98400</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>156800</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3410,8 +3485,11 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3436,195 +3514,201 @@
       <c r="J35" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K35" s="3">
+      <c r="K35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L35" s="3">
         <v>437200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>541200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>515700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>412200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>639600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>512000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>466100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>260200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>395100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>310200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>212800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>42600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>258100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>202200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>162200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>118100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>232800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>168400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>77000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>32700</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-288800</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>139000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-72300</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>106900</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>98400</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>156800</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43100</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43008</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42916</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42825</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3661,8 +3745,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3699,944 +3784,972 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3934400</v>
+      </c>
+      <c r="E41" s="3">
         <v>4178900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3911100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3559800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3466200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3737000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>4354800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>4250100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>5018900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>5567400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>3788100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>3930300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>3756500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>3647500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>3175800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>3068400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>4040100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>3698700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>3495600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>3551000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>3520900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>3310900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>2717400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>2662900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>3399900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>2212500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>2613100</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1848000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1660300</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1143800</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1387500</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>2754600</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>2523000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>2253100</v>
       </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>189200</v>
+      </c>
+      <c r="E42" s="3">
         <v>114500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>113600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>60400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>100800</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>118000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>249900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>198000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>61800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>60400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>57600</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>92500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>72500</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>83500</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>82800</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>59400</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>51100</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>54000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>50700</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>66500</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>65100</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>65200</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>70600</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>70200</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>108600</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>112300</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>75900</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>84300</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>86500</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>118200</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>153600</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>196700</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>162200</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>196600</v>
       </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>13809500</v>
+      </c>
+      <c r="E43" s="3">
         <v>13431900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>11384500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>10936700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>12059400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>11595000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>10125900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>10236200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>11854000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>12346700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>14797200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>15244900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>16798400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>13698200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>13029500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>12518900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>13537100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>11207200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>10257700</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>8850900</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>12562500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>11648000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>11474800</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>9481000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>10010500</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>10509900</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>10307200</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>8557600</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>9712800</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>9751000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>8075700</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>8062800</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>8914800</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>8875200</v>
       </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>9147700</v>
+      </c>
+      <c r="E44" s="3">
         <v>9118800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>7777600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>6702700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>6218900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>6169600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>5907200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>6371900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>7502100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>8417900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>8867700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>8300700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>8441600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>8727800</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>7825800</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>6380600</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>5785800</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>5242300</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>5126700</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>4946900</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>3998400</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>3816900</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>3573000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>3434700</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>3792300</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>4280900</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>4125100</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>3791700</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>3983300</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>3600000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>3177500</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>2794000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>2833600</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>2882800</v>
       </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>185600</v>
+      </c>
+      <c r="E45" s="3">
         <v>29900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>94400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>127600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>15400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>107200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>98900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>97800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1695300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1725700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1594500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1428500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1413800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1414700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1396500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1308100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1036400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1102900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1116900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1318200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1299100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1275600</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1172300</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1237500</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1168400</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1211800</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1524900</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1381800</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1502200</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>1419700</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>1354900</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>1060200</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>980200</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>930100</v>
       </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>28574500</v>
+      </c>
+      <c r="E46" s="3">
         <v>28206500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>24557300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>22687200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>23227800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>23409200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>22274500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>22940900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>26132000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>28118100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>29105000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>28996900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>30482800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>27571700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>25510300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>23335400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>24450500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>21305000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>20047600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>18733400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>21446000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>20116800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>19008100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>16886200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>18479800</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>18327500</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>18646200</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>15663300</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>16945200</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>16032700</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>14149300</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>14868400</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>15413900</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>15137700</v>
       </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1757000</v>
+      </c>
+      <c r="E47" s="3">
         <v>1843100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1772500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1768400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1718700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1719600</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1637400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1738400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1673800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1554800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1543800</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1508500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1293600</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1193400</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1120400</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>955300</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>939200</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>844200</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>701700</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>611300</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>618200</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>556300</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>554700</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>599900</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>559700</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>506600</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>431900</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>408700</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>392900</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>366600</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>304700</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>288500</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>236300</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>215000</v>
       </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2754300</v>
+      </c>
+      <c r="E48" s="3">
         <v>2893100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2831000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2919100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2999300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3157900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3123800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>3303900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>3174200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2788700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2846700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2986100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2834000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2711600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2657000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>2674900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>2565700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>2555100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>2472500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>2017100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>2016100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1937900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1936400</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>1662900</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>1568900</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>1514700</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>1636000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>1687600</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>1663500</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>1706600</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>1716100</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>1649400</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>1588100</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>1593000</v>
       </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>8026400</v>
+      </c>
+      <c r="E49" s="3">
         <v>8257700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>8198800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>8345400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>8519200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>8174800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>8190500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>8267100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>8184600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>8048700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>7849700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>8066800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>8138300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>8238900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>8447600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>8405000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>8152100</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>7980100</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>7991500</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>7984600</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>8230900</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>8196700</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>8391500</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>8324600</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>8296700</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>8286300</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>8426900</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>8514500</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>8416300</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>8448400</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>8317200</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>8349100</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>8313800</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>8560500</v>
       </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4739,8 +4852,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4843,112 +4959,118 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>417500</v>
+      </c>
+      <c r="E52" s="3">
         <v>467300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>420100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>397500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>408000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>284700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>210200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>202500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2584100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2783200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2903300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>2952200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2897500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>2859000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>2725300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>2620100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>2537600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>2399800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>2281700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>2781800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>2715100</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>2581700</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>2520900</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>2514900</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>2373500</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>2252300</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>2170400</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>2220000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>2081500</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>2369200</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>2139600</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>2030600</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>1651600</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>1578300</v>
       </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5051,112 +5173,118 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>44722300</v>
+      </c>
+      <c r="E54" s="3">
         <v>44464300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>40484700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>38751000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>39504300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>39256700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>37924400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>38920100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>41748600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>43293500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>44248500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>44510400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>45646200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>42574700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>40460600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>37990600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>38645100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>35084200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>33495000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>32128200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>35026300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>33389400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>32411600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>29988500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>31278600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>30887400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>31311400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>28494200</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>29499400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>28923600</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>26626800</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>27186000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>27203800</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>27084500</v>
       </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5193,8 +5321,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5231,632 +5360,651 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>13883800</v>
+      </c>
+      <c r="E57" s="3">
         <v>14229400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>11924600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>10505400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>10258500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>10872300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>9284200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>9772900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>10837300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>12348700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>13609600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>11035900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>12516700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>11492000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>11198200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>10220800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>9968000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>8525700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>7806100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>7509700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>8665800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>7857700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>6736700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>6429800</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>7339800</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>7281900</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>7919600</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>6450800</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>7498200</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>7240100</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>6209100</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>5649900</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>6162700</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>5758900</v>
       </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1147100</v>
+      </c>
+      <c r="E58" s="3">
         <v>1120100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1100500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>152000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>176100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>414300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>398800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>395300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>736500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>753100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>963300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>3081900</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1637700</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1856900</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1853800</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1717600</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1987100</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>3508300</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>3895400</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>4845600</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>3966000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>3901700</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>4094900</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>3225900</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>3675300</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>3259700</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>3470000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1968700</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1004200</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1045200</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>1055400</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>905600</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>700600</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>708200</v>
       </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>13630400</v>
+      </c>
+      <c r="E59" s="3">
         <v>13446700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>12443900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>12074400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>13078100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>12621300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>12570400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>12361500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>17343400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>17673600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>18396800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>18640900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>19546000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>17995800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>16166600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>15433300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>15165700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>12541100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>11673600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>10902800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>12601600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>12280300</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>12013500</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>10834600</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>11768900</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>12050400</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>11625600</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>11040300</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>12086600</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>12009800</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>10788000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>11778300</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>12984600</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>11364000</v>
       </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>32904100</v>
+      </c>
+      <c r="E60" s="3">
         <v>32682100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>28839000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>26059200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>26700700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>27055700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>25378000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>26093400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>28917200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>30775300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>32969700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>32758700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>33700300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>31344700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>29218600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>27371600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>27120700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>24575100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>23375100</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>23258100</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>25233500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>24039700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>22845100</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>20490300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>22784100</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>22592000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>23015300</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>19459700</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>20589000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>20295000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>18052500</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>18333800</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>19848000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>17831000</v>
       </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2834200</v>
+      </c>
+      <c r="E61" s="3">
         <v>2830700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2833100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>3809700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>3826700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>3907300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>3972800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>3964000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>4180700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>4185100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2890000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2896300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>3619300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>3627000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>3622000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>3632800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>4246500</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2873000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2867400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1911400</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>2498400</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>2452800</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>2462800</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>2426800</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1821200</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1820100</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1842200</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>2648700</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>2617700</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>2591300</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>2579200</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>2966700</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>2465200</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>2487500</v>
       </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>471000</v>
+      </c>
+      <c r="E62" s="3">
         <v>520500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>504600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>574400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>616000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>584800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>591500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>642700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2847200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2706100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2803700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3460800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>3534700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>3464100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>3460000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>3375600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>3367000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>3179700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>3022200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>2899300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>2999200</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>2882400</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>2846900</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>2974300</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>2803400</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>2521900</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>2115800</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>1839700</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>1916700</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>1848900</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>1817100</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>1790200</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>1856000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>3583200</v>
       </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5959,8 +6107,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6063,8 +6214,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6167,112 +6321,118 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>38581400</v>
+      </c>
+      <c r="E66" s="3">
         <v>38372800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>34419300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>32669800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>33391300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>33678200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>32067400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>32873000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>36424100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>38109200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>39068600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>39519800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>41162200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>38571700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>36400300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>34431600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>34758400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>30568500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>29159200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>27937000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>30588700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>29147100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>27899500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>25598400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>27099800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>26872400</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>26971200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>23981900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>25154000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>24769900</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>22489200</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>23118700</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>24201600</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>23923100</v>
       </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6309,8 +6469,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6413,8 +6574,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6517,8 +6681,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6621,8 +6788,11 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6725,112 +6895,118 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>5875400</v>
+      </c>
+      <c r="E72" s="3">
         <v>5319200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>5435400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>5207100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>4969500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>4753600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>4963400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>4805900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>4590200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>4209700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>4064400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>3841000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>3460100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>2951300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>2796200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>2334600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>2056000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>1803600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>1825700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>1614800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>1603800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>1453200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>1586700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>1424000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>1249300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>1110200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>1242900</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>1160100</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>1143900</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>1531400</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>1684100</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>1756400</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>1610600</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>1616600</v>
       </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6933,8 +7109,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7037,8 +7216,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7141,112 +7323,118 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>5028700</v>
+      </c>
+      <c r="E76" s="3">
         <v>4930000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>5015200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>5035200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>5053100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4579800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>4861800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>5040200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>5324600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>5184300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>5179900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>4990600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>4484000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>4003000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>4060400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>3559000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>3886800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>4515700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>4335800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>4191200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>4437600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>4242300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>4512100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>4390100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>4178800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>4015000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>4340200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>4512300</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>4345400</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>4153700</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>4137600</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>4067300</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>3002200</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>3161400</v>
       </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7349,117 +7537,123 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43100</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43008</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42916</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42825</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -7484,86 +7678,89 @@
       <c r="J81" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K81" s="3">
+      <c r="K81" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L81" s="3">
         <v>437200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>541200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>515700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>412200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>639600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>512000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>466100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>260200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>395100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>310200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>212800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>42600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>258100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>202200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>162200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>118100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>232800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>168400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>77000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>32700</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-288800</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>139000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-72300</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>106900</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>98400</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>156800</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7600,112 +7797,116 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>141000</v>
+      </c>
+      <c r="E83" s="3">
         <v>140600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>143000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>143800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>135000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>123600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>126300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>129300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>350300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>333500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>331400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>326600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>317400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>313100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>307300</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>294600</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>260000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>257100</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>248300</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>266500</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>251200</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>232700</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>219300</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>204100</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>199800</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>206800</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>188000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>193300</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>190100</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>180300</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>174900</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>176400</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>181400</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>191300</v>
       </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7808,8 +8009,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7912,8 +8116,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8016,8 +8223,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8120,8 +8330,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8224,112 +8437,118 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>344100</v>
+      </c>
+      <c r="E89" s="3">
         <v>986700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>791400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>543300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>364200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>453800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>649800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>244400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>74000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>2084300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>398700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1462500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>606300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1560600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>447600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>601400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1962900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>771400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>317100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>431600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>538300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1381600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-141600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-478100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1547600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>67100</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>336000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-753500</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>210900</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>363600</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-577400</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>207600</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>345500</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>1558700</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8366,112 +8585,116 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-174300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-152200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-154500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-204400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-158900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-191600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-174800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-278900</v>
-      </c>
-      <c r="K91" s="3">
-        <v>-383400</v>
       </c>
       <c r="L91" s="3">
         <v>-383400</v>
       </c>
       <c r="M91" s="3">
+        <v>-383400</v>
+      </c>
+      <c r="N91" s="3">
         <v>-386200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-364500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-361800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-278500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-279300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-111400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-71600</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-69600</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-50200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-68600</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-71900</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-75000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-31200</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-76200</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-86400</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-34900</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-37200</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-61300</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-55300</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-44600</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-56700</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-177300</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-181700</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-154700</v>
       </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8574,8 +8797,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8678,112 +8904,118 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-335200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-204900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-319800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-250300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-364400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-468700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-200000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-314000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-407200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-806000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-387800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-574100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-389300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-343400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-191600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-279600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-197000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-214300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-285100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-237800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-215400</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-200400</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-303400</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-181500</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-217100</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-103700</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-197400</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-173500</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-103200</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-92900</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-743900</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-1323900</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>93100</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-200800</v>
       </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8820,38 +9052,39 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>134000</v>
+      </c>
+      <c r="E96" s="3">
         <v>474300</v>
       </c>
-      <c r="E96" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
+      <c r="F96" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="G96" s="3">
+        <v>0</v>
+      </c>
+      <c r="H96" s="3">
         <v>124500</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>458800</v>
       </c>
-      <c r="I96" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="J96" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3">
         <v>-123400</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
       <c r="M96" s="3">
         <v>0</v>
       </c>
@@ -8859,23 +9092,23 @@
         <v>0</v>
       </c>
       <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
         <v>-119800</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
       <c r="Q96" s="3">
         <v>0</v>
       </c>
       <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3">
         <v>100</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-102000</v>
       </c>
-      <c r="T96" s="3">
-        <v>0</v>
-      </c>
       <c r="U96" s="3">
         <v>0</v>
       </c>
@@ -8883,11 +9116,11 @@
         <v>0</v>
       </c>
       <c r="W96" s="3">
+        <v>0</v>
+      </c>
+      <c r="X96" s="3">
         <v>-96400</v>
       </c>
-      <c r="X96" s="3">
-        <v>0</v>
-      </c>
       <c r="Y96" s="3">
         <v>0</v>
       </c>
@@ -8895,23 +9128,23 @@
         <v>0</v>
       </c>
       <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-91400</v>
       </c>
-      <c r="AB96" s="3">
-        <v>0</v>
-      </c>
       <c r="AC96" s="3">
         <v>0</v>
       </c>
       <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE96" s="3">
         <v>3300</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-92300</v>
       </c>
-      <c r="AF96" s="3">
-        <v>0</v>
-      </c>
       <c r="AG96" s="3">
         <v>0</v>
       </c>
@@ -8919,13 +9152,16 @@
         <v>0</v>
       </c>
       <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ96" s="3">
         <v>-85100</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9028,8 +9264,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9132,8 +9371,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9236,316 +9478,328 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-99100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-627000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-47200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-154500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-323400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-574900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-283400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-729100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-301500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>625300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-8500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-750100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-110400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-717100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-179800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1224700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1524500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-387900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-91100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-69000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-157600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-524100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>512300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-86000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-165100</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-317800</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>691600</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>1071600</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>395000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-525700</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-66500</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>1318500</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-117800</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-1014900</v>
       </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>52800</v>
+      </c>
+      <c r="E101" s="3">
         <v>-28000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-61600</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>29900</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>86200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-124300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-144700</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>35600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>86200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-124300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-144700</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>35600</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>2400</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-28500</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>31100</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-68900</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>100100</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>33800</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>3700</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-94800</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>44700</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-63500</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-12800</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>8500</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>22000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-46200</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-65000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>43000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>13700</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>11400</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>20600</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>29300</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-50800</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>3900</v>
       </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-244500</v>
+      </c>
+      <c r="E102" s="3">
         <v>267800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>351300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>93700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-270800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-617800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>104700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-768800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-548500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1779300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-142200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>173800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>109000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>471700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>107400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-971800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>341500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>203000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-55400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>30100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>210000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>593500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>54600</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-737000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>1187300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-400600</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>765100</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>187700</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>516500</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-243600</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-1367100</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>231600</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>270000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>346900</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/LNVGY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LNVGY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="92">
   <si>
     <t>LNVGY</t>
   </si>
@@ -656,158 +656,166 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AM102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43373</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>43190</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>43100</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>43008</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AJ7" s="2">
         <v>42916</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AK7" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AL7" s="2">
         <v>42735</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AM7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -835,86 +843,92 @@
       <c r="K8" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L8" s="3">
+      <c r="L8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N8" s="3">
         <v>15266600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>17089500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>16955600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>16693800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>20126500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>17868700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>16929200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>15630100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>17245400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>14518900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>13347900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>10579400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>14102800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>13522000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>12512200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>11710300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>14035100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>13379800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>11912700</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>10638300</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>12938500</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AI8" s="3">
         <v>11760900</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AJ8" s="3">
         <v>10012200</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AK8" s="3">
         <v>9578700</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AL8" s="3">
         <v>12168700</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AM8" s="3">
         <v>11231200</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -942,86 +956,92 @@
       <c r="K9" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L9" s="3">
+      <c r="L9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N9" s="3">
         <v>12654400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>14213000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>14086700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>13829500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>16771300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>14862900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>14105500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>12942200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>14459300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>12266400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>11306500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>8717600</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>11838200</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>11339400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>10463800</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>9815100</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>11985500</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>11585700</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>10281100</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>9094300</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AH9" s="3">
         <v>11187500</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AI9" s="3">
         <v>10148400</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AJ9" s="3">
         <v>8647600</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AK9" s="3">
         <v>8210200</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AL9" s="3">
         <v>10573500</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AM9" s="3">
         <v>9624000</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -1049,86 +1069,92 @@
       <c r="K10" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L10" s="3">
+      <c r="L10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N10" s="3">
         <v>2612200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>2876500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>2868900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>2864300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>3355200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>3005800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>2823700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>2687900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>2786100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>2252500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>2041400</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>1861800</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>2264600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>2182600</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>2048400</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>1895200</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>2049600</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>1794100</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>1631600</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>1544000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>1751000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AI10" s="3">
         <v>1612500</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AJ10" s="3">
         <v>1364600</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AK10" s="3">
         <v>1368500</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AL10" s="3">
         <v>1595200</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AM10" s="3">
         <v>1607200</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1166,8 +1192,10 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1195,86 +1223,92 @@
       <c r="K12" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L12" s="3">
+      <c r="L12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N12" s="3">
         <v>578600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>555700</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>511400</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>575800</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>549200</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>482000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>466500</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>416700</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>398100</v>
       </c>
-      <c r="U12" s="3">
+      <c r="W12" s="3">
         <v>306500</v>
       </c>
-      <c r="V12" s="3">
+      <c r="X12" s="3">
         <v>332600</v>
       </c>
-      <c r="W12" s="3">
+      <c r="Y12" s="3">
         <v>347200</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Z12" s="3">
         <v>341200</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="AA12" s="3">
         <v>318000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AB12" s="3">
         <v>329300</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AC12" s="3">
         <v>371300</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AD12" s="3">
         <v>272800</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AE12" s="3">
         <v>312300</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AF12" s="3">
         <v>309900</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AG12" s="3">
         <v>326800</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AH12" s="3">
         <v>344400</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AI12" s="3">
         <v>310900</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AJ12" s="3">
         <v>291600</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AK12" s="3">
         <v>338700</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AL12" s="3">
         <v>318400</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AM12" s="3">
         <v>348800</v>
       </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1380,8 +1414,14 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1418,11 +1458,11 @@
       <c r="N14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
@@ -1460,35 +1500,41 @@
       <c r="AB14" s="3">
         <v>0</v>
       </c>
-      <c r="AC14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AD14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AE14" s="3">
-        <v>0</v>
+      <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AF14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AG14" s="3" t="s">
-        <v>10</v>
+      <c r="AG14" s="3">
+        <v>0</v>
       </c>
       <c r="AH14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AI14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ14" s="3">
+      <c r="AI14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AJ14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AK14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL14" s="3">
         <v>1000</v>
       </c>
-      <c r="AK14" s="3" t="s">
+      <c r="AM14" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1516,11 +1562,11 @@
       <c r="K15" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
-      <c r="M15" s="3">
-        <v>0</v>
+      <c r="L15" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="N15" s="3">
         <v>0</v>
@@ -1594,8 +1640,14 @@
       <c r="AK15" s="3">
         <v>0</v>
       </c>
+      <c r="AL15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1630,8 +1682,10 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1659,86 +1713,92 @@
       <c r="K17" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L17" s="3">
+      <c r="L17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N17" s="3">
         <v>14516700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>16238600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>16178400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>16105000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>19194100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>17052100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>16186500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>15151300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>16544200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>13954400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>12912000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>10413300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>13614700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>13080200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>12169500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>11436800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>13600700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>13090300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>11732400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>10537600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>12734100</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AI17" s="3">
         <v>11673200</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AJ17" s="3">
         <v>10018300</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AK17" s="3">
         <v>9504800</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AL17" s="3">
         <v>12030700</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AM17" s="3">
         <v>11015800</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1766,86 +1826,92 @@
       <c r="K18" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L18" s="3">
+      <c r="L18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N18" s="3">
         <v>750000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>850900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>777200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>588800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>932400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>816600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>742700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>478800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>701200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>564500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>435900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>166100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>488100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>441800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>342700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>273500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>434400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>289500</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>180300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>100700</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>204400</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AI18" s="3">
         <v>87700</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AJ18" s="3">
         <v>-6100</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AK18" s="3">
         <v>73900</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AL18" s="3">
         <v>138000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AM18" s="3">
         <v>215400</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1883,8 +1949,10 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1912,86 +1980,92 @@
       <c r="K20" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L20" s="3">
+      <c r="L20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N20" s="3">
         <v>-59800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>-46500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>-24600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>-8100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>-12100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>-6700</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>-27400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>-30100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>-36300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>-33100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>-39700</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>-26100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>-34700</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>-66000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>-32500</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>-26200</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>-23500</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>-22100</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>-12000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AG20" s="3">
         <v>-14100</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AH20" s="3">
         <v>-12500</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AI20" s="3">
         <v>-9300</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AJ20" s="3">
         <v>-10200</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AK20" s="3">
         <v>-2500</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AL20" s="3">
         <v>10300</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AM20" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -2019,86 +2093,92 @@
       <c r="K21" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L21" s="3">
+      <c r="L21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N21" s="3">
         <v>1040400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>1137900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>1084000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>907400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>1237700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>1123000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>1022700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>743300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>924900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>788500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>644500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>406600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>704700</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>608500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>529500</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>451400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>610700</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>474200</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>356300</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>279800</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>382000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AI21" s="3">
         <v>258700</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AJ21" s="3">
         <v>158500</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AK21" s="3">
         <v>247700</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AL21" s="3">
         <v>329700</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AM21" s="3">
         <v>406500</v>
       </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2126,86 +2206,92 @@
       <c r="K22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L22" s="3">
+      <c r="L22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N22" s="3">
         <v>85100</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>94300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>62100</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>60600</v>
-      </c>
-      <c r="P22" s="3">
-        <v>65100</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>67700</v>
       </c>
       <c r="R22" s="3">
         <v>65100</v>
       </c>
       <c r="S22" s="3">
+        <v>67700</v>
+      </c>
+      <c r="T22" s="3">
+        <v>65100</v>
+      </c>
+      <c r="U22" s="3">
         <v>68500</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>73400</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>61000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>64100</v>
       </c>
-      <c r="W22" s="3">
+      <c r="Y22" s="3">
         <v>62800</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Z22" s="3">
         <v>63200</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="AA22" s="3">
         <v>65700</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AB22" s="3">
         <v>70100</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AC22" s="3">
         <v>67100</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AD22" s="3">
         <v>60600</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AE22" s="3">
         <v>54200</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AF22" s="3">
         <v>55500</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AG22" s="3">
         <v>49700</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AH22" s="3">
         <v>41600</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AI22" s="3">
         <v>43100</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AJ22" s="3">
         <v>52900</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AK22" s="3">
         <v>56100</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AL22" s="3">
         <v>46900</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AM22" s="3">
         <v>47400</v>
       </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2233,86 +2319,92 @@
       <c r="K23" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L23" s="3">
+      <c r="L23" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M23" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N23" s="3">
         <v>605000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>710100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>690500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>520200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>855200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>742100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>650200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>380300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>591500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>470400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>332100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>77300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>390200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>310100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>240100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>180200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>350300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>213300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>112800</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>36800</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>150300</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AI23" s="3">
         <v>35300</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AJ23" s="3">
         <v>-69300</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AK23" s="3">
         <v>15200</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AL23" s="3">
         <v>101300</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AM23" s="3">
         <v>167800</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2340,86 +2432,92 @@
       <c r="K24" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L24" s="3">
+      <c r="L24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N24" s="3">
         <v>123100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>156200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>151000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>98800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>173500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>185100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>165100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>95100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>160000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>120800</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>85300</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>13900</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>84700</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>66400</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>48200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>46700</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>85500</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>39800</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>27500</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>-11600</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AH24" s="3">
         <v>424800</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AI24" s="3">
         <v>-117800</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AJ24" s="3">
         <v>-15400</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AK24" s="3">
         <v>-88500</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AL24" s="3">
         <v>-5700</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AM24" s="3">
         <v>15800</v>
       </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2525,8 +2623,14 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2554,86 +2658,92 @@
       <c r="K26" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L26" s="3">
+      <c r="L26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N26" s="3">
         <v>481900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>553800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>539500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>421400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>681700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>557100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>485200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>285200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>431400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>349600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>246800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>63400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>305500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>243600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>191900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>133600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>264800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>173500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>85300</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>48400</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>-274500</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AI26" s="3">
         <v>153200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AJ26" s="3">
         <v>-53900</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AK26" s="3">
         <v>103700</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AL26" s="3">
         <v>107100</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AM26" s="3">
         <v>152000</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2661,86 +2771,92 @@
       <c r="K27" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L27" s="3">
+      <c r="L27" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M27" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N27" s="3">
         <v>437200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>541200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>515700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>412200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>639600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>512000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>466100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>260200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>395100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>310200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>212800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>42600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>258100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>202200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>162200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>118100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>232800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>168400</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>77000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>32700</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>-288800</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AI27" s="3">
         <v>139000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AJ27" s="3">
         <v>-72300</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AK27" s="3">
         <v>106900</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AL27" s="3">
         <v>98400</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AM27" s="3">
         <v>156800</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2846,8 +2962,14 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2875,11 +2997,11 @@
       <c r="K29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L29" s="3">
-        <v>0</v>
-      </c>
-      <c r="M29" s="3">
-        <v>0</v>
+      <c r="L29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M29" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="N29" s="3">
         <v>0</v>
@@ -2953,8 +3075,14 @@
       <c r="AK29" s="3">
         <v>0</v>
       </c>
+      <c r="AL29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3060,8 +3188,14 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3167,8 +3301,14 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3196,86 +3336,92 @@
       <c r="K32" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L32" s="3">
+      <c r="L32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N32" s="3">
         <v>59800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>46500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>24600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>8100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>12100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>6700</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>27400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>30100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>36300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>33100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>39700</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>26100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>34700</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>66000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>32500</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>26200</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>23500</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>22100</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>12000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>14100</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AH32" s="3">
         <v>12500</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AI32" s="3">
         <v>9300</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AJ32" s="3">
         <v>10200</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AK32" s="3">
         <v>2500</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AL32" s="3">
         <v>-10300</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AM32" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -3303,86 +3449,92 @@
       <c r="K33" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L33" s="3">
+      <c r="L33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N33" s="3">
         <v>437200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>541200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>515700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>412200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>639600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>512000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>466100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>260200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>395100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>310200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>212800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>42600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>258100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>202200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>162200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>118100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>232800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>168400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>77000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>32700</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>-288800</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AI33" s="3">
         <v>139000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AJ33" s="3">
         <v>-72300</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AK33" s="3">
         <v>106900</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AL33" s="3">
         <v>98400</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AM33" s="3">
         <v>156800</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3488,8 +3640,14 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3517,198 +3675,210 @@
       <c r="K35" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L35" s="3">
+      <c r="L35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N35" s="3">
         <v>437200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>541200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>515700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>412200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>639600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>512000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>466100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>260200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>395100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>310200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>212800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>42600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>258100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>202200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>162200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>118100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>232800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>168400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>77000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>32700</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>-288800</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AI35" s="3">
         <v>139000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AJ35" s="3">
         <v>-72300</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AK35" s="3">
         <v>106900</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AL35" s="3">
         <v>98400</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AM35" s="3">
         <v>156800</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43373</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>43190</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>43100</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>43008</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AJ38" s="2">
         <v>42916</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AK38" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AL38" s="2">
         <v>42735</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AM38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3746,8 +3916,10 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3785,971 +3957,1027 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D41" s="3">
+      <c r="D41" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E41" s="3">
+        <v>4728100</v>
+      </c>
+      <c r="F41" s="3">
         <v>3934400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>4178900</v>
       </c>
-      <c r="F41" s="3">
-        <v>3911100</v>
-      </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I41" s="3">
         <v>3559800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>3466200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>3737000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>4354800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>4250100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>5018900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>5567400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>3788100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>3930300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>3756500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>3647500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>3175800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>3068400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>4040100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>3698700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>3495600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>3551000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>3520900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>3310900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>2717400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>2662900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>3399900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>2212500</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>2613100</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>1848000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>1660300</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AI41" s="3">
         <v>1143800</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AJ41" s="3">
         <v>1387500</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AK41" s="3">
         <v>2754600</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AL41" s="3">
         <v>2523000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AM41" s="3">
         <v>2253100</v>
       </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
+        <v>58200</v>
+      </c>
+      <c r="F42" s="3">
         <v>189200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>114500</v>
       </c>
-      <c r="F42" s="3">
-        <v>113600</v>
-      </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
         <v>60400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>100800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>118000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>249900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>198000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>61800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>60400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>57600</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>92500</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>72500</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>83500</v>
       </c>
-      <c r="R42" s="3">
+      <c r="T42" s="3">
         <v>82800</v>
       </c>
-      <c r="S42" s="3">
+      <c r="U42" s="3">
         <v>59400</v>
       </c>
-      <c r="T42" s="3">
+      <c r="V42" s="3">
         <v>51100</v>
       </c>
-      <c r="U42" s="3">
+      <c r="W42" s="3">
         <v>54000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="X42" s="3">
         <v>50700</v>
       </c>
-      <c r="W42" s="3">
+      <c r="Y42" s="3">
         <v>66500</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Z42" s="3">
         <v>65100</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="AA42" s="3">
         <v>65200</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AB42" s="3">
         <v>70600</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AC42" s="3">
         <v>70200</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AD42" s="3">
         <v>108600</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AE42" s="3">
         <v>112300</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AF42" s="3">
         <v>75900</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AG42" s="3">
         <v>84300</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AH42" s="3">
         <v>86500</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AI42" s="3">
         <v>118200</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AJ42" s="3">
         <v>153600</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AK42" s="3">
         <v>196700</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AL42" s="3">
         <v>162200</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AM42" s="3">
         <v>196600</v>
       </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
+      <c r="D43" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E43" s="3">
+        <v>13760700</v>
+      </c>
+      <c r="F43" s="3">
         <v>13809500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>13431900</v>
       </c>
-      <c r="F43" s="3">
-        <v>11384500</v>
-      </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I43" s="3">
         <v>10936700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>12059400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>11595000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>10125900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>10236200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>11854000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>12346700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>14797200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>15244900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>16798400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>13698200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>13029500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>12518900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>13537100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>11207200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>10257700</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>8850900</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>12562500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>11648000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>11474800</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>9481000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>10010500</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>10509900</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>10307200</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>8557600</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AH43" s="3">
         <v>9712800</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AI43" s="3">
         <v>9751000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AJ43" s="3">
         <v>8075700</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AK43" s="3">
         <v>8062800</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AL43" s="3">
         <v>8914800</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AM43" s="3">
         <v>8875200</v>
       </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
+      <c r="D44" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E44" s="3">
+        <v>7923800</v>
+      </c>
+      <c r="F44" s="3">
         <v>9147700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>9118800</v>
       </c>
-      <c r="F44" s="3">
-        <v>7777600</v>
-      </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I44" s="3">
         <v>6702700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>6218900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>6169600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>5907200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>6371900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>7502100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>8417900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>8867700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>8300700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>8441600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>8727800</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>7825800</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>6380600</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>5785800</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>5242300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>5126700</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>4946900</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>3998400</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>3816900</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>3573000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>3434700</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>3792300</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>4280900</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AF44" s="3">
         <v>4125100</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AG44" s="3">
         <v>3791700</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AH44" s="3">
         <v>3983300</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AI44" s="3">
         <v>3600000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AJ44" s="3">
         <v>3177500</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AK44" s="3">
         <v>2794000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AL44" s="3">
         <v>2833600</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AM44" s="3">
         <v>2882800</v>
       </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E45" s="3">
+        <v>110800</v>
+      </c>
+      <c r="F45" s="3">
         <v>185600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>29900</v>
       </c>
-      <c r="F45" s="3">
-        <v>94400</v>
-      </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I45" s="3">
         <v>127600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>15400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>107200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>98900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>97800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>1695300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>1725700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>1594500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>1428500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>1413800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>1414700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>1396500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>1308100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>1036400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>1102900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>1116900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>1318200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>1299100</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>1275600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>1172300</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>1237500</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>1168400</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>1211800</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>1524900</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>1381800</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AH45" s="3">
         <v>1502200</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AI45" s="3">
         <v>1419700</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AJ45" s="3">
         <v>1354900</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AK45" s="3">
         <v>1060200</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AL45" s="3">
         <v>980200</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AM45" s="3">
         <v>930100</v>
       </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D46" s="3">
+      <c r="D46" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E46" s="3">
+        <v>27904100</v>
+      </c>
+      <c r="F46" s="3">
         <v>28574500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>28206500</v>
       </c>
-      <c r="F46" s="3">
-        <v>24557300</v>
-      </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I46" s="3">
         <v>22687200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>23227800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>23409200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>22274500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>22940900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>26132000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>28118100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>29105000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>28996900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>30482800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>27571700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>25510300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>23335400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>24450500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>21305000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>20047600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>18733400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>21446000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>20116800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>19008100</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>16886200</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>18479800</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>18327500</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>18646200</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>15663300</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>16945200</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AI46" s="3">
         <v>16032700</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AJ46" s="3">
         <v>14149300</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AK46" s="3">
         <v>14868400</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AL46" s="3">
         <v>15413900</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AM46" s="3">
         <v>15137700</v>
       </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
+      <c r="D47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E47" s="3">
+        <v>1825500</v>
+      </c>
+      <c r="F47" s="3">
         <v>1757000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>1843100</v>
       </c>
-      <c r="F47" s="3">
-        <v>1772500</v>
-      </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I47" s="3">
         <v>1768400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>1718700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>1719600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>1637400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>1738400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>1673800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>1554800</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>1543800</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>1508500</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>1293600</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>1193400</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>1120400</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>955300</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>939200</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>844200</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>701700</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>611300</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>618200</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AA47" s="3">
         <v>556300</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AB47" s="3">
         <v>554700</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AC47" s="3">
         <v>599900</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AD47" s="3">
         <v>559700</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AE47" s="3">
         <v>506600</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AF47" s="3">
         <v>431900</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AG47" s="3">
         <v>408700</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AH47" s="3">
         <v>392900</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AI47" s="3">
         <v>366600</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AJ47" s="3">
         <v>304700</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AK47" s="3">
         <v>288500</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AL47" s="3">
         <v>236300</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AM47" s="3">
         <v>215000</v>
       </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3">
+      <c r="D48" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E48" s="3">
+        <v>2900900</v>
+      </c>
+      <c r="F48" s="3">
         <v>2754300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>2893100</v>
       </c>
-      <c r="F48" s="3">
-        <v>2831000</v>
-      </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I48" s="3">
         <v>2919100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>2999300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>3157900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>3123800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>3303900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>3174200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>2788700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>2846700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>2986100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>2834000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>2711600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>2657000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>2674900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>2565700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>2555100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>2472500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>2017100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>2016100</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>1937900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>1936400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>1662900</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>1568900</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>1514700</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>1636000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>1687600</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AH48" s="3">
         <v>1663500</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AI48" s="3">
         <v>1706600</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AJ48" s="3">
         <v>1716100</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AK48" s="3">
         <v>1649400</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AL48" s="3">
         <v>1588100</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AM48" s="3">
         <v>1593000</v>
       </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="3">
+      <c r="D49" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E49" s="3">
+        <v>8233000</v>
+      </c>
+      <c r="F49" s="3">
         <v>8026400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>8257700</v>
       </c>
-      <c r="F49" s="3">
-        <v>8198800</v>
-      </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I49" s="3">
         <v>8345400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>8519200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>8174800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>8190500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>8267100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>8184600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>8048700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>7849700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>8066800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>8138300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>8238900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>8447600</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>8405000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>8152100</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>7980100</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>7991500</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>7984600</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>8230900</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>8196700</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>8391500</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>8324600</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>8296700</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>8286300</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AF49" s="3">
         <v>8426900</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AG49" s="3">
         <v>8514500</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AH49" s="3">
         <v>8416300</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AI49" s="3">
         <v>8448400</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AJ49" s="3">
         <v>8317200</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AK49" s="3">
         <v>8349100</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AL49" s="3">
         <v>8313800</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AM49" s="3">
         <v>8560500</v>
       </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4855,8 +5083,14 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4962,115 +5196,127 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
+      <c r="D52" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E52" s="3">
+        <v>311400</v>
+      </c>
+      <c r="F52" s="3">
         <v>417500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>467300</v>
       </c>
-      <c r="F52" s="3">
-        <v>420100</v>
-      </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I52" s="3">
         <v>397500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>408000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>284700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>210200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>202500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>2584100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>2783200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>2903300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>2952200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>2897500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>2859000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>2725300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>2620100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>2537600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>2399800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>2281700</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>2781800</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>2715100</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>2581700</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>2520900</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>2514900</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>2373500</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>2252300</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>2170400</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AG52" s="3">
         <v>2220000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AH52" s="3">
         <v>2081500</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AI52" s="3">
         <v>2369200</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AJ52" s="3">
         <v>2139600</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AK52" s="3">
         <v>2030600</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AL52" s="3">
         <v>1651600</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AM52" s="3">
         <v>1578300</v>
       </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5176,115 +5422,127 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D54" s="3">
+      <c r="D54" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E54" s="3">
+        <v>44230800</v>
+      </c>
+      <c r="F54" s="3">
         <v>44722300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>44464300</v>
       </c>
-      <c r="F54" s="3">
-        <v>40484700</v>
-      </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I54" s="3">
         <v>38751000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>39504300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>39256700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>37924400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>38920100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>41748600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>43293500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>44248500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>44510400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>45646200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>42574700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>40460600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>37990600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>38645100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>35084200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>33495000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>32128200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>35026300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>33389400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>32411600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>29988500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>31278600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>30887400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>31311400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>28494200</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>29499400</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AI54" s="3">
         <v>28923600</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AJ54" s="3">
         <v>26626800</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AK54" s="3">
         <v>27186000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AL54" s="3">
         <v>27203800</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AM54" s="3">
         <v>27084500</v>
       </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5322,8 +5580,10 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5361,650 +5621,688 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
+      <c r="D57" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E57" s="3">
+        <v>11978900</v>
+      </c>
+      <c r="F57" s="3">
         <v>13883800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>14229400</v>
       </c>
-      <c r="F57" s="3">
-        <v>11924600</v>
-      </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I57" s="3">
         <v>10505400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>10258500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>10872300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>9284200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>9772900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>10837300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>12348700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>13609600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>11035900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>12516700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>11492000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>11198200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>10220800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>9968000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>8525700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>7806100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>7509700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>8665800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>7857700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>6736700</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>6429800</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>7339800</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>7281900</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>7919600</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>6450800</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>7498200</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AI57" s="3">
         <v>7240100</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AJ57" s="3">
         <v>6209100</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AK57" s="3">
         <v>5649900</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AL57" s="3">
         <v>6162700</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AM57" s="3">
         <v>5758900</v>
       </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3">
+      <c r="D58" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E58" s="3">
+        <v>1125300</v>
+      </c>
+      <c r="F58" s="3">
         <v>1147100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>1120100</v>
       </c>
-      <c r="F58" s="3">
-        <v>1100500</v>
-      </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I58" s="3">
         <v>152000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>176100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>414300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>398800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>395300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>736500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>753100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>963300</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>3081900</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>1637700</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>1856900</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>1853800</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>1717600</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>1987100</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>3508300</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>3895400</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>4845600</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>3966000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>3901700</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>4094900</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>3225900</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>3675300</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>3259700</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AF58" s="3">
         <v>3470000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AG58" s="3">
         <v>1968700</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AH58" s="3">
         <v>1004200</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AI58" s="3">
         <v>1045200</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AJ58" s="3">
         <v>1055400</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AK58" s="3">
         <v>905600</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AL58" s="3">
         <v>700600</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AM58" s="3">
         <v>708200</v>
       </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E59" s="3">
+        <v>12498600</v>
+      </c>
+      <c r="F59" s="3">
         <v>13630400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>13446700</v>
       </c>
-      <c r="F59" s="3">
-        <v>12443900</v>
-      </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I59" s="3">
         <v>12074400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>13078100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>12621300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>12570400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>12361500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>17343400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>17673600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>18396800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>18640900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>19546000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>17995800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>16166600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>15433300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>15165700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>12541100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>11673600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>10902800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>12601600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>12280300</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>12013500</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>10834600</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>11768900</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>12050400</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>11625600</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>11040300</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>12086600</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AI59" s="3">
         <v>12009800</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AJ59" s="3">
         <v>10788000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AK59" s="3">
         <v>11778300</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AL59" s="3">
         <v>12984600</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AM59" s="3">
         <v>11364000</v>
       </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D60" s="3">
+      <c r="D60" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E60" s="3">
+        <v>29994100</v>
+      </c>
+      <c r="F60" s="3">
         <v>32904100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>32682100</v>
       </c>
-      <c r="F60" s="3">
-        <v>28839000</v>
-      </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I60" s="3">
         <v>26059200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>26700700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>27055700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>25378000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>26093400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>28917200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>30775300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>32969700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>32758700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>33700300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>31344700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>29218600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>27371600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>27120700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>24575100</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>23375100</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>23258100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>25233500</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>24039700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>22845100</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>20490300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>22784100</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>22592000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>23015300</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>19459700</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>20589000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AI60" s="3">
         <v>20295000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AJ60" s="3">
         <v>18052500</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AK60" s="3">
         <v>18333800</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AL60" s="3">
         <v>19848000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AM60" s="3">
         <v>17831000</v>
       </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>0</v>
+      </c>
+      <c r="E61" s="3">
+        <v>4607600</v>
+      </c>
+      <c r="F61" s="3">
         <v>2834200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>2830700</v>
       </c>
-      <c r="F61" s="3">
-        <v>2833100</v>
-      </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
+        <v>0</v>
+      </c>
+      <c r="I61" s="3">
         <v>3809700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>3826700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>3907300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>3972800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>3964000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>4180700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>4185100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>2890000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>2896300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>3619300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>3627000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>3622000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>3632800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>4246500</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>2873000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>2867400</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>1911400</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>2498400</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>2452800</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>2462800</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>2426800</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>1821200</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>1820100</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AF61" s="3">
         <v>1842200</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AG61" s="3">
         <v>2648700</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AH61" s="3">
         <v>2617700</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AI61" s="3">
         <v>2591300</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AJ61" s="3">
         <v>2579200</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AK61" s="3">
         <v>2966700</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AL61" s="3">
         <v>2465200</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AM61" s="3">
         <v>2487500</v>
       </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
+      <c r="D62" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E62" s="3">
+        <v>750800</v>
+      </c>
+      <c r="F62" s="3">
         <v>471000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>520500</v>
       </c>
-      <c r="F62" s="3">
-        <v>504600</v>
-      </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I62" s="3">
         <v>574400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>616000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>584800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>591500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>642700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>2847200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>2706100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>2803700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>3460800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>3534700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>3464100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>3460000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>3375600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>3367000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>3179700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>3022200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>2899300</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>2999200</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>2882400</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>2846900</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>2974300</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>2803400</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>2521900</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>2115800</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>1839700</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AH62" s="3">
         <v>1916700</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AI62" s="3">
         <v>1848900</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AJ62" s="3">
         <v>1817100</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AK62" s="3">
         <v>1790200</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AL62" s="3">
         <v>1856000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AM62" s="3">
         <v>3583200</v>
       </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6110,8 +6408,14 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6217,8 +6521,14 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6324,115 +6634,127 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D66" s="3">
+      <c r="D66" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E66" s="3">
+        <v>37570900</v>
+      </c>
+      <c r="F66" s="3">
         <v>38581400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>38372800</v>
       </c>
-      <c r="F66" s="3">
-        <v>34419300</v>
-      </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I66" s="3">
         <v>32669800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>33391300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>33678200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>32067400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>32873000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>36424100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>38109200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>39068600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>39519800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>41162200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>38571700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>36400300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>34431600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>34758400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>30568500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>29159200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>27937000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>30588700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>29147100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>27899500</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>25598400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>27099800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>26872400</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>26971200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>23981900</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>25154000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AI66" s="3">
         <v>24769900</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AJ66" s="3">
         <v>22489200</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AK66" s="3">
         <v>23118700</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AL66" s="3">
         <v>24201600</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AM66" s="3">
         <v>23923100</v>
       </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6470,8 +6792,10 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6577,8 +6901,14 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6684,8 +7014,14 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6791,8 +7127,14 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6898,115 +7240,127 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3">
+      <c r="D72" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E72" s="3">
+        <v>5971600</v>
+      </c>
+      <c r="F72" s="3">
         <v>5875400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>5319200</v>
       </c>
-      <c r="F72" s="3">
-        <v>5435400</v>
-      </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I72" s="3">
         <v>5207100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>4969500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>4753600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>4963400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>4805900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>4590200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>4209700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>4064400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>3841000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>3460100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>2951300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>2796200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>2334600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>2056000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>1803600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>1825700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>1614800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>1603800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>1453200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>1586700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>1424000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>1249300</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>1110200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>1242900</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>1160100</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>1143900</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AI72" s="3">
         <v>1531400</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AJ72" s="3">
         <v>1684100</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AK72" s="3">
         <v>1756400</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AL72" s="3">
         <v>1610600</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AM72" s="3">
         <v>1616600</v>
       </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7112,8 +7466,14 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7219,8 +7579,14 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7326,115 +7692,127 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D76" s="3">
+      <c r="D76" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E76" s="3">
+        <v>5521600</v>
+      </c>
+      <c r="F76" s="3">
         <v>5028700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>4930000</v>
       </c>
-      <c r="F76" s="3">
-        <v>5015200</v>
-      </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I76" s="3">
         <v>5035200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>5053100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>4579800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>4861800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>5040200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>5324600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>5184300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>5179900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>4990600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>4484000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>4003000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>4060400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>3559000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>3886800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>4515700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>4335800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>4191200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>4437600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>4242300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>4512100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>4390100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>4178800</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>4015000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>4340200</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>4512300</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>4345400</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AI76" s="3">
         <v>4153700</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AJ76" s="3">
         <v>4137600</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AK76" s="3">
         <v>4067300</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AL76" s="3">
         <v>3002200</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AM76" s="3">
         <v>3161400</v>
       </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7540,120 +7918,132 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43373</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>43190</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>43100</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>43008</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AJ80" s="2">
         <v>42916</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AK80" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AL80" s="2">
         <v>42735</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AM80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -7681,86 +8071,92 @@
       <c r="K81" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L81" s="3">
+      <c r="L81" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M81" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N81" s="3">
         <v>437200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>541200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>515700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>412200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>639600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>512000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>466100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>260200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>395100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>310200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>212800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>42600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>258100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>202200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>162200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>118100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>232800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>168400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>77000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>32700</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>-288800</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AI81" s="3">
         <v>139000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AJ81" s="3">
         <v>-72300</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AK81" s="3">
         <v>106900</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AL81" s="3">
         <v>98400</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AM81" s="3">
         <v>156800</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7798,115 +8194,123 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
+      <c r="D83" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E83" s="3">
+        <v>155800</v>
+      </c>
+      <c r="F83" s="3">
         <v>141000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>140600</v>
       </c>
-      <c r="F83" s="3">
-        <v>143000</v>
-      </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I83" s="3">
         <v>143800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>135000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>123600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>126300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>129300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>350300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>333500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>331400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>326600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>317400</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>313100</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>307300</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>294600</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>260000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>257100</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>248300</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>266500</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>251200</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>232700</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>219300</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>204100</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AD83" s="3">
         <v>199800</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AE83" s="3">
         <v>206800</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AF83" s="3">
         <v>188000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AG83" s="3">
         <v>193300</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AH83" s="3">
         <v>190100</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AI83" s="3">
         <v>180300</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AJ83" s="3">
         <v>174900</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AK83" s="3">
         <v>176400</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AL83" s="3">
         <v>181400</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AM83" s="3">
         <v>191300</v>
       </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8012,8 +8416,14 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8119,8 +8529,14 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8226,8 +8642,14 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8333,8 +8755,14 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8440,115 +8868,127 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
+      <c r="D89" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-1022400</v>
+      </c>
+      <c r="F89" s="3">
         <v>344100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>986700</v>
       </c>
-      <c r="F89" s="3">
-        <v>791400</v>
-      </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I89" s="3">
         <v>543300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>364200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>453800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>649800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>244400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>74000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>2084300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>398700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>1462500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>606300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>1560600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>447600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>601400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>1962900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>771400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>317100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>431600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>538300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>1381600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>-141600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>-478100</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>1547600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>67100</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>336000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>-753500</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>210900</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AI89" s="3">
         <v>363600</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AJ89" s="3">
         <v>-577400</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AK89" s="3">
         <v>207600</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AL89" s="3">
         <v>345500</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AM89" s="3">
         <v>1558700</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8586,115 +9026,123 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
+      <c r="D91" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-185400</v>
+      </c>
+      <c r="F91" s="3">
         <v>-174300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-152200</v>
       </c>
-      <c r="F91" s="3">
-        <v>-154500</v>
-      </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I91" s="3">
         <v>-204400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-158900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-191600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-174800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-278900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-383400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-383400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-386200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-364500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-361800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-278500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-279300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-111400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-71600</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-69600</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-50200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-68600</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-71900</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-75000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-31200</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-76200</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-86400</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-34900</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AF91" s="3">
         <v>-37200</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AG91" s="3">
         <v>-61300</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AH91" s="3">
         <v>-55300</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AI91" s="3">
         <v>-44600</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AJ91" s="3">
         <v>-56700</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AK91" s="3">
         <v>-177300</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AL91" s="3">
         <v>-181700</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AM91" s="3">
         <v>-154700</v>
       </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8800,8 +9248,14 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8907,115 +9361,127 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
+      <c r="D94" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-196300</v>
+      </c>
+      <c r="F94" s="3">
         <v>-335200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-204900</v>
       </c>
-      <c r="F94" s="3">
-        <v>-319800</v>
-      </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I94" s="3">
         <v>-250300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-364400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-468700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-200000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-314000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-407200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-806000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-387800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-574100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-389300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-343400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-191600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-279600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-197000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-214300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-285100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-237800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-215400</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-200400</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-303400</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-181500</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-217100</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-103700</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>-197400</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>-173500</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AH94" s="3">
         <v>-103200</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AI94" s="3">
         <v>-92900</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AJ94" s="3">
         <v>-743900</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AK94" s="3">
         <v>-1323900</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AL94" s="3">
         <v>93100</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AM94" s="3">
         <v>-200800</v>
       </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9053,115 +9519,123 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
+      <c r="D96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E96" s="3">
+        <v>0</v>
+      </c>
+      <c r="F96" s="3">
         <v>134000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>474300</v>
       </c>
-      <c r="F96" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
+      <c r="H96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I96" s="3">
+        <v>0</v>
+      </c>
+      <c r="J96" s="3">
         <v>124500</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>458800</v>
       </c>
-      <c r="J96" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3">
+      <c r="L96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3">
         <v>-123400</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
       <c r="O96" s="3">
         <v>0</v>
       </c>
       <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3">
         <v>-119800</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
-      <c r="R96" s="3">
-        <v>0</v>
-      </c>
       <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+      <c r="U96" s="3">
         <v>100</v>
       </c>
-      <c r="T96" s="3">
+      <c r="V96" s="3">
         <v>-102000</v>
       </c>
-      <c r="U96" s="3">
-        <v>0</v>
-      </c>
-      <c r="V96" s="3">
-        <v>0</v>
-      </c>
       <c r="W96" s="3">
         <v>0</v>
       </c>
       <c r="X96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-96400</v>
       </c>
-      <c r="Y96" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z96" s="3">
-        <v>0</v>
-      </c>
       <c r="AA96" s="3">
         <v>0</v>
       </c>
       <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-91400</v>
       </c>
-      <c r="AC96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD96" s="3">
-        <v>0</v>
-      </c>
       <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG96" s="3">
         <v>3300</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AH96" s="3">
         <v>-92300</v>
       </c>
-      <c r="AG96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH96" s="3">
-        <v>0</v>
-      </c>
       <c r="AI96" s="3">
         <v>0</v>
       </c>
       <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL96" s="3">
         <v>-85100</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AM96" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9267,8 +9741,14 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9374,8 +9854,14 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9481,325 +9967,349 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
+      <c r="D100" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E100" s="3">
+        <v>1963300</v>
+      </c>
+      <c r="F100" s="3">
         <v>-99100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-627000</v>
       </c>
-      <c r="F100" s="3">
-        <v>-47200</v>
-      </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I100" s="3">
         <v>-154500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-323400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-574900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-283400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-729100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-301500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>625300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-8500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-750100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-110400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-717100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-179800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-1224700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-1524500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-387900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-91100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-69000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>-157600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>-524100</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>512300</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-86000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>-165100</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>-317800</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>691600</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>1071600</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AH100" s="3">
         <v>395000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AI100" s="3">
         <v>-525700</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AJ100" s="3">
         <v>-66500</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AK100" s="3">
         <v>1318500</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AL100" s="3">
         <v>-117800</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AM100" s="3">
         <v>-1014900</v>
       </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
+      <c r="D101" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-44800</v>
+      </c>
+      <c r="F101" s="3">
         <v>52800</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-28000</v>
       </c>
-      <c r="F101" s="3">
-        <v>-61600</v>
-      </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I101" s="3">
         <v>29900</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>86200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-124300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-144700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>35600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>86200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>-124300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>-144700</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>35600</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>2400</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>-28500</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>31100</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>-68900</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>100100</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>33800</v>
       </c>
-      <c r="V101" s="3">
+      <c r="X101" s="3">
         <v>3700</v>
       </c>
-      <c r="W101" s="3">
+      <c r="Y101" s="3">
         <v>-94800</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Z101" s="3">
         <v>44700</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="AA101" s="3">
         <v>-63500</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AB101" s="3">
         <v>-12800</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AC101" s="3">
         <v>8500</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AD101" s="3">
         <v>22000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AE101" s="3">
         <v>-46200</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AF101" s="3">
         <v>-65000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AG101" s="3">
         <v>43000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AH101" s="3">
         <v>13700</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AI101" s="3">
         <v>11400</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AJ101" s="3">
         <v>20600</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AK101" s="3">
         <v>29300</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AL101" s="3">
         <v>-50800</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AM101" s="3">
         <v>3900</v>
       </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
+        <v>793700</v>
+      </c>
+      <c r="F102" s="3">
         <v>-244500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>267800</v>
       </c>
-      <c r="F102" s="3">
-        <v>351300</v>
-      </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3">
         <v>93700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-270800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-617800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>104700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-768800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-548500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>1779300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-142200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>173800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>109000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>471700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>107400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-971800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>341500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>203000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-55400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>30100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>210000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>593500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>54600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>-737000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>1187300</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>-400600</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>765100</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>187700</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>516500</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AI102" s="3">
         <v>-243600</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AJ102" s="3">
         <v>-1367100</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AK102" s="3">
         <v>231600</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AL102" s="3">
         <v>270000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AM102" s="3">
         <v>346900</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/LNVGY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LNVGY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="92">
   <si>
     <t>LNVGY</t>
   </si>
@@ -656,166 +656,173 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AM102"/>
+  <dimension ref="A5:AO102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43921</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43830</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43738</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43646</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43555</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43465</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>43373</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>43281</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>43190</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AJ7" s="2">
         <v>43100</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AK7" s="2">
         <v>43008</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AL7" s="2">
         <v>42916</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AM7" s="2">
         <v>42825</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AN7" s="2">
         <v>42735</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AO7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -849,86 +856,92 @@
       <c r="M8" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N8" s="3">
+      <c r="N8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P8" s="3">
         <v>15266600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>17089500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>16955600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>16693800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>20126500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>17868700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>16929200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>15630100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>17245400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>14518900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>13347900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>10579400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>14102800</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>13522000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>12512200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>11710300</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>14035100</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>13379800</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>11912700</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AI8" s="3">
         <v>10638300</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AJ8" s="3">
         <v>12938500</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AK8" s="3">
         <v>11760900</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AL8" s="3">
         <v>10012200</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AM8" s="3">
         <v>9578700</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AN8" s="3">
         <v>12168700</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AO8" s="3">
         <v>11231200</v>
       </c>
     </row>
-    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -962,86 +975,92 @@
       <c r="M9" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N9" s="3">
+      <c r="N9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="O9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P9" s="3">
         <v>12654400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>14213000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>14086700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>13829500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>16771300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>14862900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>14105500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>12942200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>14459300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>12266400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>11306500</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>8717600</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>11838200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>11339400</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>10463800</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>9815100</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>11985500</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>11585700</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AH9" s="3">
         <v>10281100</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AI9" s="3">
         <v>9094300</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AJ9" s="3">
         <v>11187500</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AK9" s="3">
         <v>10148400</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AL9" s="3">
         <v>8647600</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AM9" s="3">
         <v>8210200</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AN9" s="3">
         <v>10573500</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AO9" s="3">
         <v>9624000</v>
       </c>
     </row>
-    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -1075,86 +1094,92 @@
       <c r="M10" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N10" s="3">
+      <c r="N10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="O10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P10" s="3">
         <v>2612200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>2876500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>2868900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>2864300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>3355200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>3005800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>2823700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>2687900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>2786100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>2252500</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>2041400</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>1861800</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>2264600</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>2182600</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>2048400</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>1895200</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>2049600</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>1794100</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>1631600</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AI10" s="3">
         <v>1544000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AJ10" s="3">
         <v>1751000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AK10" s="3">
         <v>1612500</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AL10" s="3">
         <v>1364600</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AM10" s="3">
         <v>1368500</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AN10" s="3">
         <v>1595200</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AO10" s="3">
         <v>1607200</v>
       </c>
     </row>
-    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1194,8 +1219,10 @@
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
+      <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
     </row>
-    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1229,86 +1256,92 @@
       <c r="M12" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N12" s="3">
+      <c r="N12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="O12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P12" s="3">
         <v>578600</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>555700</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>511400</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>575800</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>549200</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>482000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>466500</v>
       </c>
-      <c r="U12" s="3">
+      <c r="W12" s="3">
         <v>416700</v>
       </c>
-      <c r="V12" s="3">
+      <c r="X12" s="3">
         <v>398100</v>
       </c>
-      <c r="W12" s="3">
+      <c r="Y12" s="3">
         <v>306500</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Z12" s="3">
         <v>332600</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="AA12" s="3">
         <v>347200</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AB12" s="3">
         <v>341200</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AC12" s="3">
         <v>318000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AD12" s="3">
         <v>329300</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AE12" s="3">
         <v>371300</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AF12" s="3">
         <v>272800</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AG12" s="3">
         <v>312300</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AH12" s="3">
         <v>309900</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AI12" s="3">
         <v>326800</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AJ12" s="3">
         <v>344400</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AK12" s="3">
         <v>310900</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AL12" s="3">
         <v>291600</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AM12" s="3">
         <v>338700</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AN12" s="3">
         <v>318400</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AO12" s="3">
         <v>348800</v>
       </c>
     </row>
-    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1420,8 +1453,14 @@
       <c r="AM13" s="3">
         <v>0</v>
       </c>
+      <c r="AN13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1464,11 +1503,11 @@
       <c r="P14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
-      <c r="R14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="S14" s="3">
         <v>0</v>
@@ -1506,35 +1545,41 @@
       <c r="AD14" s="3">
         <v>0</v>
       </c>
-      <c r="AE14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AF14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AG14" s="3">
-        <v>0</v>
+      <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AH14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AI14" s="3" t="s">
-        <v>10</v>
+      <c r="AI14" s="3">
+        <v>0</v>
       </c>
       <c r="AJ14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AK14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL14" s="3">
+      <c r="AK14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AL14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AM14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN14" s="3">
         <v>1000</v>
       </c>
-      <c r="AM14" s="3" t="s">
+      <c r="AO14" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1568,11 +1613,11 @@
       <c r="M15" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N15" s="3">
-        <v>0</v>
-      </c>
-      <c r="O15" s="3">
-        <v>0</v>
+      <c r="N15" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="O15" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="P15" s="3">
         <v>0</v>
@@ -1646,8 +1691,14 @@
       <c r="AM15" s="3">
         <v>0</v>
       </c>
+      <c r="AN15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1684,8 +1735,10 @@
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
+      <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
     </row>
-    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1719,86 +1772,92 @@
       <c r="M17" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N17" s="3">
+      <c r="N17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="O17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P17" s="3">
         <v>14516700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>16238600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>16178400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>16105000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>19194100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>17052100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>16186500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>15151300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>16544200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>13954400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>12912000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>10413300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>13614700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>13080200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>12169500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>11436800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>13600700</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>13090300</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>11732400</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AI17" s="3">
         <v>10537600</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AJ17" s="3">
         <v>12734100</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AK17" s="3">
         <v>11673200</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AL17" s="3">
         <v>10018300</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AM17" s="3">
         <v>9504800</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AN17" s="3">
         <v>12030700</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AO17" s="3">
         <v>11015800</v>
       </c>
     </row>
-    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1832,86 +1891,92 @@
       <c r="M18" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N18" s="3">
+      <c r="N18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="O18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P18" s="3">
         <v>750000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>850900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>777200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>588800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>932400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>816600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>742700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>478800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>701200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>564500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>435900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>166100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>488100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>441800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>342700</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>273500</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>434400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>289500</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>180300</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AI18" s="3">
         <v>100700</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AJ18" s="3">
         <v>204400</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AK18" s="3">
         <v>87700</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AL18" s="3">
         <v>-6100</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AM18" s="3">
         <v>73900</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AN18" s="3">
         <v>138000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AO18" s="3">
         <v>215400</v>
       </c>
     </row>
-    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1951,8 +2016,10 @@
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
+      <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
     </row>
-    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1986,86 +2053,92 @@
       <c r="M20" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N20" s="3">
+      <c r="N20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="O20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P20" s="3">
         <v>-59800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>-46500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>-24600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>-8100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>-12100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>-6700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>-27400</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>-30100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>-36300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>-33100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>-39700</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>-26100</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>-34700</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>-66000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>-32500</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>-26200</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>-23500</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AG20" s="3">
         <v>-22100</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AH20" s="3">
         <v>-12000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AI20" s="3">
         <v>-14100</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AJ20" s="3">
         <v>-12500</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AK20" s="3">
         <v>-9300</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AL20" s="3">
         <v>-10200</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AM20" s="3">
         <v>-2500</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AN20" s="3">
         <v>10300</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AO20" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -2099,86 +2172,92 @@
       <c r="M21" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N21" s="3">
+      <c r="N21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="O21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P21" s="3">
         <v>1040400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>1137900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>1084000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>907400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>1237700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>1123000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>1022700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>743300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>924900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>788500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>644500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>406600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>704700</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>608500</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>529500</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>451400</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>610700</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>474200</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>356300</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AI21" s="3">
         <v>279800</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AJ21" s="3">
         <v>382000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AK21" s="3">
         <v>258700</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AL21" s="3">
         <v>158500</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AM21" s="3">
         <v>247700</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AN21" s="3">
         <v>329700</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AO21" s="3">
         <v>406500</v>
       </c>
     </row>
-    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2212,86 +2291,92 @@
       <c r="M22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N22" s="3">
+      <c r="N22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="O22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P22" s="3">
         <v>85100</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>94300</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>62100</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>60600</v>
-      </c>
-      <c r="R22" s="3">
-        <v>65100</v>
-      </c>
-      <c r="S22" s="3">
-        <v>67700</v>
       </c>
       <c r="T22" s="3">
         <v>65100</v>
       </c>
       <c r="U22" s="3">
+        <v>67700</v>
+      </c>
+      <c r="V22" s="3">
+        <v>65100</v>
+      </c>
+      <c r="W22" s="3">
         <v>68500</v>
       </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>73400</v>
       </c>
-      <c r="W22" s="3">
+      <c r="Y22" s="3">
         <v>61000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Z22" s="3">
         <v>64100</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="AA22" s="3">
         <v>62800</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AB22" s="3">
         <v>63200</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AC22" s="3">
         <v>65700</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AD22" s="3">
         <v>70100</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AE22" s="3">
         <v>67100</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AF22" s="3">
         <v>60600</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AG22" s="3">
         <v>54200</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AH22" s="3">
         <v>55500</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AI22" s="3">
         <v>49700</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AJ22" s="3">
         <v>41600</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AK22" s="3">
         <v>43100</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AL22" s="3">
         <v>52900</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AM22" s="3">
         <v>56100</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AN22" s="3">
         <v>46900</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AO22" s="3">
         <v>47400</v>
       </c>
     </row>
-    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2325,86 +2410,92 @@
       <c r="M23" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N23" s="3">
+      <c r="N23" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="O23" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P23" s="3">
         <v>605000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>710100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>690500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>520200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>855200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>742100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>650200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>380300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>591500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>470400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>332100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>77300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>390200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>310100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>240100</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>180200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>350300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>213300</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>112800</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AI23" s="3">
         <v>36800</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AJ23" s="3">
         <v>150300</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AK23" s="3">
         <v>35300</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AL23" s="3">
         <v>-69300</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AM23" s="3">
         <v>15200</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AN23" s="3">
         <v>101300</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AO23" s="3">
         <v>167800</v>
       </c>
     </row>
-    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2438,86 +2529,92 @@
       <c r="M24" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N24" s="3">
+      <c r="N24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="O24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P24" s="3">
         <v>123100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>156200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>151000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>98800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>173500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>185100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>165100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>95100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>160000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>120800</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>85300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>13900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>84700</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>66400</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>48200</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>46700</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>85500</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>39800</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AH24" s="3">
         <v>27500</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AI24" s="3">
         <v>-11600</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AJ24" s="3">
         <v>424800</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AK24" s="3">
         <v>-117800</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AL24" s="3">
         <v>-15400</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AM24" s="3">
         <v>-88500</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AN24" s="3">
         <v>-5700</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AO24" s="3">
         <v>15800</v>
       </c>
     </row>
-    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2629,8 +2726,14 @@
       <c r="AM25" s="3">
         <v>0</v>
       </c>
+      <c r="AN25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2664,86 +2767,92 @@
       <c r="M26" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N26" s="3">
+      <c r="N26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="O26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P26" s="3">
         <v>481900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>553800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>539500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>421400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>681700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>557100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>485200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>285200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>431400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>349600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>246800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>63400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>305500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>243600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>191900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>133600</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>264800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>173500</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>85300</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AI26" s="3">
         <v>48400</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AJ26" s="3">
         <v>-274500</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AK26" s="3">
         <v>153200</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AL26" s="3">
         <v>-53900</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AM26" s="3">
         <v>103700</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AN26" s="3">
         <v>107100</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AO26" s="3">
         <v>152000</v>
       </c>
     </row>
-    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2777,86 +2886,92 @@
       <c r="M27" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N27" s="3">
+      <c r="N27" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="O27" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P27" s="3">
         <v>437200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>541200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>515700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>412200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>639600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>512000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>466100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>260200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>395100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>310200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>212800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>42600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>258100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>202200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>162200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>118100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>232800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>168400</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>77000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AI27" s="3">
         <v>32700</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AJ27" s="3">
         <v>-288800</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AK27" s="3">
         <v>139000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AL27" s="3">
         <v>-72300</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AM27" s="3">
         <v>106900</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AN27" s="3">
         <v>98400</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AO27" s="3">
         <v>156800</v>
       </c>
     </row>
-    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2968,8 +3083,14 @@
       <c r="AM28" s="3">
         <v>0</v>
       </c>
+      <c r="AN28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3003,11 +3124,11 @@
       <c r="M29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N29" s="3">
-        <v>0</v>
-      </c>
-      <c r="O29" s="3">
-        <v>0</v>
+      <c r="N29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="O29" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="P29" s="3">
         <v>0</v>
@@ -3081,8 +3202,14 @@
       <c r="AM29" s="3">
         <v>0</v>
       </c>
+      <c r="AN29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3194,8 +3321,14 @@
       <c r="AM30" s="3">
         <v>0</v>
       </c>
+      <c r="AN30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3307,8 +3440,14 @@
       <c r="AM31" s="3">
         <v>0</v>
       </c>
+      <c r="AN31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3342,86 +3481,92 @@
       <c r="M32" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N32" s="3">
+      <c r="N32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="O32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P32" s="3">
         <v>59800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>46500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>24600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>8100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>12100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>6700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>27400</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>30100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>36300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>33100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>39700</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>26100</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>34700</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>66000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>32500</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>26200</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>23500</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>22100</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AH32" s="3">
         <v>12000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AI32" s="3">
         <v>14100</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AJ32" s="3">
         <v>12500</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AK32" s="3">
         <v>9300</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AL32" s="3">
         <v>10200</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AM32" s="3">
         <v>2500</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AN32" s="3">
         <v>-10300</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AO32" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -3455,86 +3600,92 @@
       <c r="M33" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N33" s="3">
+      <c r="N33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="O33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P33" s="3">
         <v>437200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>541200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>515700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>412200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>639600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>512000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>466100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>260200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>395100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>310200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>212800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>42600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>258100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>202200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>162200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>118100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>232800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>168400</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>77000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AI33" s="3">
         <v>32700</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AJ33" s="3">
         <v>-288800</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AK33" s="3">
         <v>139000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AL33" s="3">
         <v>-72300</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AM33" s="3">
         <v>106900</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AN33" s="3">
         <v>98400</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AO33" s="3">
         <v>156800</v>
       </c>
     </row>
-    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3646,8 +3797,14 @@
       <c r="AM34" s="3">
         <v>0</v>
       </c>
+      <c r="AN34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3681,204 +3838,216 @@
       <c r="M35" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N35" s="3">
+      <c r="N35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="O35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P35" s="3">
         <v>437200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>541200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>515700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>412200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>639600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>512000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>466100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>260200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>395100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>310200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>212800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>42600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>258100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>202200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>162200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>118100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>232800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>168400</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>77000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AI35" s="3">
         <v>32700</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AJ35" s="3">
         <v>-288800</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AK35" s="3">
         <v>139000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AL35" s="3">
         <v>-72300</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AM35" s="3">
         <v>106900</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AN35" s="3">
         <v>98400</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AO35" s="3">
         <v>156800</v>
       </c>
     </row>
-    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43921</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43830</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43738</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43646</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43555</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43465</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>43373</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>43281</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>43190</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AJ38" s="2">
         <v>43100</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AK38" s="2">
         <v>43008</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AL38" s="2">
         <v>42916</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AM38" s="2">
         <v>42825</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AN38" s="2">
         <v>42735</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AO38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3918,8 +4087,10 @@
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
+      <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
     </row>
-    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3959,1025 +4130,1081 @@
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
+      <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
     </row>
-    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D41" s="3" t="s">
-        <v>10</v>
+      <c r="D41" s="3">
+        <v>5221400</v>
       </c>
       <c r="E41" s="3">
+        <v>5112100</v>
+      </c>
+      <c r="F41" s="3">
+        <v>4504400</v>
+      </c>
+      <c r="G41" s="3">
         <v>4728100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>3934400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>4178900</v>
       </c>
-      <c r="H41" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
+        <v>3911100</v>
+      </c>
+      <c r="K41" s="3">
         <v>3559800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>3466200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>3737000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>4354800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>4250100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>5018900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>5567400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>3788100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>3930300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>3756500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>3647500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>3175800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>3068400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>4040100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>3698700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>3495600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>3551000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>3520900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>3310900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>2717400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>2662900</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>3399900</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>2212500</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>2613100</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AI41" s="3">
         <v>1848000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AJ41" s="3">
         <v>1660300</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AK41" s="3">
         <v>1143800</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AL41" s="3">
         <v>1387500</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AM41" s="3">
         <v>2754600</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AN41" s="3">
         <v>2523000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AO41" s="3">
         <v>2253100</v>
       </c>
     </row>
-    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>153000</v>
       </c>
       <c r="E42" s="3">
+        <v>131600</v>
+      </c>
+      <c r="F42" s="3">
+        <v>5310800</v>
+      </c>
+      <c r="G42" s="3">
         <v>58200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>189200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>114500</v>
       </c>
-      <c r="H42" s="3">
-        <v>0</v>
-      </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
+        <v>113600</v>
+      </c>
+      <c r="K42" s="3">
         <v>60400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>100800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>118000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>249900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>198000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>61800</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>60400</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>57600</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>92500</v>
       </c>
-      <c r="R42" s="3">
+      <c r="T42" s="3">
         <v>72500</v>
       </c>
-      <c r="S42" s="3">
+      <c r="U42" s="3">
         <v>83500</v>
       </c>
-      <c r="T42" s="3">
+      <c r="V42" s="3">
         <v>82800</v>
       </c>
-      <c r="U42" s="3">
+      <c r="W42" s="3">
         <v>59400</v>
       </c>
-      <c r="V42" s="3">
+      <c r="X42" s="3">
         <v>51100</v>
       </c>
-      <c r="W42" s="3">
+      <c r="Y42" s="3">
         <v>54000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Z42" s="3">
         <v>50700</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="AA42" s="3">
         <v>66500</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AB42" s="3">
         <v>65100</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AC42" s="3">
         <v>65200</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AD42" s="3">
         <v>70600</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AE42" s="3">
         <v>70200</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AF42" s="3">
         <v>108600</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AG42" s="3">
         <v>112300</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AH42" s="3">
         <v>75900</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AI42" s="3">
         <v>84300</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AJ42" s="3">
         <v>86500</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AK42" s="3">
         <v>118200</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AL42" s="3">
         <v>153600</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AM42" s="3">
         <v>196700</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AN42" s="3">
         <v>162200</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AO42" s="3">
         <v>196600</v>
       </c>
     </row>
-    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3" t="s">
-        <v>10</v>
+      <c r="D43" s="3">
+        <v>19416600</v>
       </c>
       <c r="E43" s="3">
+        <v>17970300</v>
+      </c>
+      <c r="F43" s="3">
+        <v>11159700</v>
+      </c>
+      <c r="G43" s="3">
         <v>13760700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>13809500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>13431900</v>
       </c>
-      <c r="H43" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
+        <v>11384500</v>
+      </c>
+      <c r="K43" s="3">
         <v>10936700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>12059400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>11595000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>10125900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>10236200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>11854000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>12346700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>14797200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>15244900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>16798400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>13698200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>13029500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>12518900</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>13537100</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>11207200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>10257700</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>8850900</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>12562500</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>11648000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>11474800</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>9481000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>10010500</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>10509900</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AH43" s="3">
         <v>10307200</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AI43" s="3">
         <v>8557600</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AJ43" s="3">
         <v>9712800</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AK43" s="3">
         <v>9751000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AL43" s="3">
         <v>8075700</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AM43" s="3">
         <v>8062800</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AN43" s="3">
         <v>8914800</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AO43" s="3">
         <v>8875200</v>
       </c>
     </row>
-    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3" t="s">
-        <v>10</v>
+      <c r="D44" s="3">
+        <v>9076600</v>
       </c>
       <c r="E44" s="3">
+        <v>8617400</v>
+      </c>
+      <c r="F44" s="3">
+        <v>8742600</v>
+      </c>
+      <c r="G44" s="3">
         <v>7923800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>9147700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>9118800</v>
       </c>
-      <c r="H44" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
+        <v>7777600</v>
+      </c>
+      <c r="K44" s="3">
         <v>6702700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>6218900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>6169600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>5907200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>6371900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>7502100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>8417900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>8867700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>8300700</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>8441600</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>8727800</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>7825800</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>6380600</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>5785800</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>5242300</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>5126700</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>4946900</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>3998400</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>3816900</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>3573000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>3434700</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AF44" s="3">
         <v>3792300</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AG44" s="3">
         <v>4280900</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AH44" s="3">
         <v>4125100</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AI44" s="3">
         <v>3791700</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AJ44" s="3">
         <v>3983300</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AK44" s="3">
         <v>3600000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AL44" s="3">
         <v>3177500</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AM44" s="3">
         <v>2794000</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AN44" s="3">
         <v>2833600</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AO44" s="3">
         <v>2882800</v>
       </c>
     </row>
-    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>10</v>
+      <c r="D45" s="3">
+        <v>49600</v>
       </c>
       <c r="E45" s="3">
+        <v>55500</v>
+      </c>
+      <c r="F45" s="3">
+        <v>43400</v>
+      </c>
+      <c r="G45" s="3">
         <v>110800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>185600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>29900</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
+        <v>94400</v>
+      </c>
+      <c r="K45" s="3">
         <v>127600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>15400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>107200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>98900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>97800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>1695300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>1725700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>1594500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>1428500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>1413800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>1414700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>1396500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>1308100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>1036400</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>1102900</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>1116900</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>1318200</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>1299100</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>1275600</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>1172300</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>1237500</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>1168400</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>1211800</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AH45" s="3">
         <v>1524900</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AI45" s="3">
         <v>1381800</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AJ45" s="3">
         <v>1502200</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AK45" s="3">
         <v>1419700</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AL45" s="3">
         <v>1354900</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AM45" s="3">
         <v>1060200</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AN45" s="3">
         <v>980200</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AO45" s="3">
         <v>930100</v>
       </c>
     </row>
-    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D46" s="3" t="s">
-        <v>10</v>
+      <c r="D46" s="3">
+        <v>35437800</v>
       </c>
       <c r="E46" s="3">
+        <v>33216700</v>
+      </c>
+      <c r="F46" s="3">
+        <v>29760900</v>
+      </c>
+      <c r="G46" s="3">
         <v>27904100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>28574500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>28206500</v>
       </c>
-      <c r="H46" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
+        <v>24557300</v>
+      </c>
+      <c r="K46" s="3">
         <v>22687200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>23227800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>23409200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>22274500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>22940900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>26132000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>28118100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>29105000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>28996900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>30482800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>27571700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>25510300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>23335400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>24450500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>21305000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>20047600</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>18733400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>21446000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>20116800</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>19008100</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>16886200</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>18479800</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>18327500</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>18646200</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AI46" s="3">
         <v>15663300</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AJ46" s="3">
         <v>16945200</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AK46" s="3">
         <v>16032700</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AL46" s="3">
         <v>14149300</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AM46" s="3">
         <v>14868400</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AN46" s="3">
         <v>15413900</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AO46" s="3">
         <v>15137700</v>
       </c>
     </row>
-    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>10</v>
+      <c r="D47" s="3">
+        <v>2210900</v>
       </c>
       <c r="E47" s="3">
+        <v>1925600</v>
+      </c>
+      <c r="F47" s="3">
+        <v>1856100</v>
+      </c>
+      <c r="G47" s="3">
         <v>1825500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>1757000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>1843100</v>
       </c>
-      <c r="H47" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
+        <v>1772500</v>
+      </c>
+      <c r="K47" s="3">
         <v>1768400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>1718700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>1719600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>1637400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>1738400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>1673800</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>1554800</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>1543800</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>1508500</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>1293600</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>1193400</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>1120400</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>955300</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>939200</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>844200</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>701700</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AA47" s="3">
         <v>611300</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AB47" s="3">
         <v>618200</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AC47" s="3">
         <v>556300</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AD47" s="3">
         <v>554700</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AE47" s="3">
         <v>599900</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AF47" s="3">
         <v>559700</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AG47" s="3">
         <v>506600</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AH47" s="3">
         <v>431900</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AI47" s="3">
         <v>408700</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AJ47" s="3">
         <v>392900</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AK47" s="3">
         <v>366600</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AL47" s="3">
         <v>304700</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AM47" s="3">
         <v>288500</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AN47" s="3">
         <v>236300</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AO47" s="3">
         <v>215000</v>
       </c>
     </row>
-    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3" t="s">
-        <v>10</v>
+      <c r="D48" s="3">
+        <v>3320200</v>
       </c>
       <c r="E48" s="3">
+        <v>3042000</v>
+      </c>
+      <c r="F48" s="3">
+        <v>2938300</v>
+      </c>
+      <c r="G48" s="3">
         <v>2900900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>2754300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>2893100</v>
       </c>
-      <c r="H48" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
+        <v>2831000</v>
+      </c>
+      <c r="K48" s="3">
         <v>2919100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>2999300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>3157900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>3123800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>3303900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>3174200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>2788700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>2846700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>2986100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>2834000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>2711600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>2657000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>2674900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>2565700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>2555100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>2472500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>2017100</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>2016100</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>1937900</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>1936400</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>1662900</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>1568900</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>1514700</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AH48" s="3">
         <v>1636000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AI48" s="3">
         <v>1687600</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AJ48" s="3">
         <v>1663500</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AK48" s="3">
         <v>1706600</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AL48" s="3">
         <v>1716100</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AM48" s="3">
         <v>1649400</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AN48" s="3">
         <v>1588100</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AO48" s="3">
         <v>1593000</v>
       </c>
     </row>
-    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="3" t="s">
-        <v>10</v>
+      <c r="D49" s="3">
+        <v>7921700</v>
       </c>
       <c r="E49" s="3">
+        <v>8256300</v>
+      </c>
+      <c r="F49" s="3">
+        <v>8328700</v>
+      </c>
+      <c r="G49" s="3">
         <v>8233000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>8026400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>8257700</v>
       </c>
-      <c r="H49" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
+        <v>8198800</v>
+      </c>
+      <c r="K49" s="3">
         <v>8345400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>8519200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>8174800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>8190500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>8267100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>8184600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>8048700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>7849700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>8066800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>8138300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>8238900</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>8447600</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>8405000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>8152100</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>7980100</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>7991500</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>7984600</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>8230900</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>8196700</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>8391500</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>8324600</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AF49" s="3">
         <v>8296700</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AG49" s="3">
         <v>8286300</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AH49" s="3">
         <v>8426900</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AI49" s="3">
         <v>8514500</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AJ49" s="3">
         <v>8416300</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AK49" s="3">
         <v>8448400</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AL49" s="3">
         <v>8317200</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AM49" s="3">
         <v>8349100</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AN49" s="3">
         <v>8313800</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AO49" s="3">
         <v>8560500</v>
       </c>
     </row>
-    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5089,8 +5316,14 @@
       <c r="AM50" s="3">
         <v>0</v>
       </c>
+      <c r="AN50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5202,121 +5435,133 @@
       <c r="AM51" s="3">
         <v>0</v>
       </c>
+      <c r="AN51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>10</v>
+      <c r="D52" s="3">
+        <v>333200</v>
       </c>
       <c r="E52" s="3">
+        <v>310300</v>
+      </c>
+      <c r="F52" s="3">
+        <v>335100</v>
+      </c>
+      <c r="G52" s="3">
         <v>311400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>417500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>467300</v>
       </c>
-      <c r="H52" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
+        <v>420100</v>
+      </c>
+      <c r="K52" s="3">
         <v>397500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>408000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>284700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>210200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>202500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>2584100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>2783200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>2903300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>2952200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>2897500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>2859000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>2725300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>2620100</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>2537600</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>2399800</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>2281700</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>2781800</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>2715100</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>2581700</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>2520900</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>2514900</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>2373500</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AG52" s="3">
         <v>2252300</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AH52" s="3">
         <v>2170400</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AI52" s="3">
         <v>2220000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AJ52" s="3">
         <v>2081500</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AK52" s="3">
         <v>2369200</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AL52" s="3">
         <v>2139600</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AM52" s="3">
         <v>2030600</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AN52" s="3">
         <v>1651600</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AO52" s="3">
         <v>1578300</v>
       </c>
     </row>
-    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5428,121 +5673,133 @@
       <c r="AM53" s="3">
         <v>0</v>
       </c>
+      <c r="AN53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D54" s="3" t="s">
-        <v>10</v>
+      <c r="D54" s="3">
+        <v>52632400</v>
       </c>
       <c r="E54" s="3">
+        <v>49831200</v>
+      </c>
+      <c r="F54" s="3">
+        <v>46323200</v>
+      </c>
+      <c r="G54" s="3">
         <v>44230800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>44722300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>44464300</v>
       </c>
-      <c r="H54" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
+        <v>40484700</v>
+      </c>
+      <c r="K54" s="3">
         <v>38751000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>39504300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>39256700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>37924400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>38920100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>41748600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>43293500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>44248500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>44510400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>45646200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>42574700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>40460600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>37990600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>38645100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>35084200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>33495000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>32128200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>35026300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>33389400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>32411600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>29988500</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>31278600</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>30887400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>31311400</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AI54" s="3">
         <v>28494200</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AJ54" s="3">
         <v>29499400</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AK54" s="3">
         <v>28923600</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AL54" s="3">
         <v>26626800</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AM54" s="3">
         <v>27186000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AN54" s="3">
         <v>27203800</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AO54" s="3">
         <v>27084500</v>
       </c>
     </row>
-    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5582,8 +5839,10 @@
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
+      <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
     </row>
-    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5623,686 +5882,724 @@
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
+      <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
     </row>
-    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3" t="s">
-        <v>10</v>
+      <c r="D57" s="3">
+        <v>16727000</v>
       </c>
       <c r="E57" s="3">
+        <v>16132400</v>
+      </c>
+      <c r="F57" s="3">
+        <v>14187800</v>
+      </c>
+      <c r="G57" s="3">
         <v>11978900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>13883800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>14229400</v>
       </c>
-      <c r="H57" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
+        <v>11924600</v>
+      </c>
+      <c r="K57" s="3">
         <v>10505400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>10258500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>10872300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>9284200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>9772900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>10837300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>12348700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>13609600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>11035900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>12516700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>11492000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>11198200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>10220800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>9968000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>8525700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>7806100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>7509700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>8665800</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>7857700</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>6736700</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>6429800</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>7339800</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>7281900</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>7919600</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AI57" s="3">
         <v>6450800</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AJ57" s="3">
         <v>7498200</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AK57" s="3">
         <v>7240100</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AL57" s="3">
         <v>6209100</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AM57" s="3">
         <v>5649900</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AN57" s="3">
         <v>6162700</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AO57" s="3">
         <v>5758900</v>
       </c>
     </row>
-    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3" t="s">
-        <v>10</v>
+      <c r="D58" s="3">
+        <v>299300</v>
       </c>
       <c r="E58" s="3">
+        <v>146100</v>
+      </c>
+      <c r="F58" s="3">
+        <v>159700</v>
+      </c>
+      <c r="G58" s="3">
         <v>1125300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>1147100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>1120100</v>
       </c>
-      <c r="H58" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
+        <v>1100500</v>
+      </c>
+      <c r="K58" s="3">
         <v>152000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>176100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>414300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>398800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>395300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>736500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>753100</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>963300</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>3081900</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>1637700</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>1856900</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>1853800</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>1717600</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>1987100</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>3508300</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>3895400</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>4845600</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>3966000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>3901700</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>4094900</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>3225900</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AF58" s="3">
         <v>3675300</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AG58" s="3">
         <v>3259700</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AH58" s="3">
         <v>3470000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AI58" s="3">
         <v>1968700</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AJ58" s="3">
         <v>1004200</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AK58" s="3">
         <v>1045200</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AL58" s="3">
         <v>1055400</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AM58" s="3">
         <v>905600</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AN58" s="3">
         <v>700600</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AO58" s="3">
         <v>708200</v>
       </c>
     </row>
-    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>10</v>
+      <c r="D59" s="3">
+        <v>15386300</v>
       </c>
       <c r="E59" s="3">
+        <v>14171100</v>
+      </c>
+      <c r="F59" s="3">
+        <v>13102900</v>
+      </c>
+      <c r="G59" s="3">
         <v>12498600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>13630400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>13446700</v>
       </c>
-      <c r="H59" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
+        <v>12443900</v>
+      </c>
+      <c r="K59" s="3">
         <v>12074400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>13078100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>12621300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>12570400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>12361500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>17343400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>17673600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>18396800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>18640900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>19546000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>17995800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>16166600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>15433300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>15165700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>12541100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>11673600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>10902800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>12601600</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>12280300</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>12013500</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>10834600</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>11768900</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>12050400</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>11625600</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AI59" s="3">
         <v>11040300</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AJ59" s="3">
         <v>12086600</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AK59" s="3">
         <v>12009800</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AL59" s="3">
         <v>10788000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AM59" s="3">
         <v>11778300</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AN59" s="3">
         <v>12984600</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AO59" s="3">
         <v>11364000</v>
       </c>
     </row>
-    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D60" s="3" t="s">
-        <v>10</v>
+      <c r="D60" s="3">
+        <v>36890400</v>
       </c>
       <c r="E60" s="3">
+        <v>34516000</v>
+      </c>
+      <c r="F60" s="3">
+        <v>31285100</v>
+      </c>
+      <c r="G60" s="3">
         <v>29994100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>32904100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>32682100</v>
       </c>
-      <c r="H60" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
+        <v>28839000</v>
+      </c>
+      <c r="K60" s="3">
         <v>26059200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>26700700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>27055700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>25378000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>26093400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>28917200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>30775300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>32969700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>32758700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>33700300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>31344700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>29218600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>27371600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>27120700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>24575100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>23375100</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>23258100</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>25233500</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>24039700</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>22845100</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>20490300</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>22784100</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>22592000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>23015300</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AI60" s="3">
         <v>19459700</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AJ60" s="3">
         <v>20589000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AK60" s="3">
         <v>20295000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AL60" s="3">
         <v>18052500</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AM60" s="3">
         <v>18333800</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AN60" s="3">
         <v>19848000</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AO60" s="3">
         <v>17831000</v>
       </c>
     </row>
-    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>4753100</v>
       </c>
       <c r="E61" s="3">
+        <v>4693000</v>
+      </c>
+      <c r="F61" s="3">
+        <v>4663400</v>
+      </c>
+      <c r="G61" s="3">
         <v>4607600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>2834200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>2830700</v>
       </c>
-      <c r="H61" s="3">
-        <v>0</v>
-      </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
+        <v>2833100</v>
+      </c>
+      <c r="K61" s="3">
         <v>3809700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>3826700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>3907300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>3972800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>3964000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>4180700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>4185100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>2890000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>2896300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>3619300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>3627000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>3622000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>3632800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>4246500</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>2873000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>2867400</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>1911400</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>2498400</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>2452800</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>2462800</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>2426800</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AF61" s="3">
         <v>1821200</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AG61" s="3">
         <v>1820100</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AH61" s="3">
         <v>1842200</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AI61" s="3">
         <v>2648700</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AJ61" s="3">
         <v>2617700</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AK61" s="3">
         <v>2591300</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AL61" s="3">
         <v>2579200</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AM61" s="3">
         <v>2966700</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AN61" s="3">
         <v>2465200</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AO61" s="3">
         <v>2487500</v>
       </c>
     </row>
-    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3" t="s">
-        <v>10</v>
+      <c r="D62" s="3">
+        <v>595700</v>
       </c>
       <c r="E62" s="3">
+        <v>743600</v>
+      </c>
+      <c r="F62" s="3">
+        <v>619100</v>
+      </c>
+      <c r="G62" s="3">
         <v>750800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>471000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>520500</v>
       </c>
-      <c r="H62" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
+        <v>504600</v>
+      </c>
+      <c r="K62" s="3">
         <v>574400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>616000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>584800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>591500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>642700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>2847200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>2706100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>2803700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>3460800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>3534700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>3464100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>3460000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>3375600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>3367000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>3179700</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>3022200</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>2899300</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>2999200</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>2882400</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>2846900</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>2974300</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>2803400</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>2521900</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AH62" s="3">
         <v>2115800</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AI62" s="3">
         <v>1839700</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AJ62" s="3">
         <v>1916700</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AK62" s="3">
         <v>1848900</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AL62" s="3">
         <v>1817100</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AM62" s="3">
         <v>1790200</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AN62" s="3">
         <v>1856000</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AO62" s="3">
         <v>3583200</v>
       </c>
     </row>
-    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6414,8 +6711,14 @@
       <c r="AM63" s="3">
         <v>0</v>
       </c>
+      <c r="AN63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6527,8 +6830,14 @@
       <c r="AM64" s="3">
         <v>0</v>
       </c>
+      <c r="AN64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6640,121 +6949,133 @@
       <c r="AM65" s="3">
         <v>0</v>
       </c>
+      <c r="AN65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D66" s="3" t="s">
-        <v>10</v>
+      <c r="D66" s="3">
+        <v>44786300</v>
       </c>
       <c r="E66" s="3">
+        <v>42342300</v>
+      </c>
+      <c r="F66" s="3">
+        <v>38882300</v>
+      </c>
+      <c r="G66" s="3">
         <v>37570900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>38581400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>38372800</v>
       </c>
-      <c r="H66" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
+        <v>34419300</v>
+      </c>
+      <c r="K66" s="3">
         <v>32669800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>33391300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>33678200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>32067400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>32873000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>36424100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>38109200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>39068600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>39519800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>41162200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>38571700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>36400300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>34431600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>34758400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>30568500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>29159200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>27937000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>30588700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>29147100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>27899500</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>25598400</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>27099800</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>26872400</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>26971200</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AI66" s="3">
         <v>23981900</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AJ66" s="3">
         <v>25154000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AK66" s="3">
         <v>24769900</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AL66" s="3">
         <v>22489200</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AM66" s="3">
         <v>23118700</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AN66" s="3">
         <v>24201600</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AO66" s="3">
         <v>23923100</v>
       </c>
     </row>
-    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6794,8 +7115,10 @@
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
+      <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
     </row>
-    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6907,8 +7230,14 @@
       <c r="AM68" s="3">
         <v>0</v>
       </c>
+      <c r="AN68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7020,8 +7349,14 @@
       <c r="AM69" s="3">
         <v>0</v>
       </c>
+      <c r="AN69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7133,8 +7468,14 @@
       <c r="AM70" s="3">
         <v>0</v>
       </c>
+      <c r="AN70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7246,121 +7587,133 @@
       <c r="AM71" s="3">
         <v>0</v>
       </c>
+      <c r="AN71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3" t="s">
-        <v>10</v>
+      <c r="D72" s="3">
+        <v>6715200</v>
       </c>
       <c r="E72" s="3">
+        <v>6318200</v>
+      </c>
+      <c r="F72" s="3">
+        <v>6457400</v>
+      </c>
+      <c r="G72" s="3">
         <v>5971600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>5875400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>5319200</v>
       </c>
-      <c r="H72" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
+        <v>5435400</v>
+      </c>
+      <c r="K72" s="3">
         <v>5207100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>4969500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>4753600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>4963400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>4805900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>4590200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>4209700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>4064400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>3841000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>3460100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>2951300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>2796200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>2334600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>2056000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>1803600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>1825700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>1614800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>1603800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>1453200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>1586700</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>1424000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>1249300</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>1110200</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>1242900</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AI72" s="3">
         <v>1160100</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AJ72" s="3">
         <v>1143900</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AK72" s="3">
         <v>1531400</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AL72" s="3">
         <v>1684100</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AM72" s="3">
         <v>1756400</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AN72" s="3">
         <v>1610600</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AO72" s="3">
         <v>1616600</v>
       </c>
     </row>
-    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7472,8 +7825,14 @@
       <c r="AM73" s="3">
         <v>0</v>
       </c>
+      <c r="AN73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7585,8 +7944,14 @@
       <c r="AM74" s="3">
         <v>0</v>
       </c>
+      <c r="AN74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7698,121 +8063,133 @@
       <c r="AM75" s="3">
         <v>0</v>
       </c>
+      <c r="AN75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D76" s="3" t="s">
-        <v>10</v>
+      <c r="D76" s="3">
+        <v>6524200</v>
       </c>
       <c r="E76" s="3">
+        <v>6294600</v>
+      </c>
+      <c r="F76" s="3">
+        <v>6259600</v>
+      </c>
+      <c r="G76" s="3">
         <v>5521600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>5028700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>4930000</v>
       </c>
-      <c r="H76" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
+        <v>5015200</v>
+      </c>
+      <c r="K76" s="3">
         <v>5035200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>5053100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>4579800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>4861800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>5040200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>5324600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>5184300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>5179900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>4990600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>4484000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>4003000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>4060400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>3559000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>3886800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>4515700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>4335800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>4191200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>4437600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>4242300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>4512100</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>4390100</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>4178800</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>4015000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>4340200</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AI76" s="3">
         <v>4512300</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AJ76" s="3">
         <v>4345400</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AK76" s="3">
         <v>4153700</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AL76" s="3">
         <v>4137600</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AM76" s="3">
         <v>4067300</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AN76" s="3">
         <v>3002200</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AO76" s="3">
         <v>3161400</v>
       </c>
     </row>
-    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7924,126 +8301,138 @@
       <c r="AM77" s="3">
         <v>0</v>
       </c>
+      <c r="AN77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43921</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43830</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43738</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43646</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43555</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43465</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>43373</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>43281</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>43190</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AJ80" s="2">
         <v>43100</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AK80" s="2">
         <v>43008</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AL80" s="2">
         <v>42916</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AM80" s="2">
         <v>42825</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AN80" s="2">
         <v>42735</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AO80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -8077,86 +8466,92 @@
       <c r="M81" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N81" s="3">
+      <c r="N81" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="O81" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P81" s="3">
         <v>437200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>541200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>515700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>412200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>639600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>512000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>466100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>260200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>395100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>310200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>212800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>42600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>258100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>202200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>162200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>118100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>232800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>168400</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>77000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AI81" s="3">
         <v>32700</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AJ81" s="3">
         <v>-288800</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AK81" s="3">
         <v>139000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AL81" s="3">
         <v>-72300</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AM81" s="3">
         <v>106900</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AN81" s="3">
         <v>98400</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AO81" s="3">
         <v>156800</v>
       </c>
     </row>
-    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8196,121 +8591,129 @@
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
+      <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
     </row>
-    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>10</v>
+      <c r="D83" s="3">
+        <v>148400</v>
       </c>
       <c r="E83" s="3">
+        <v>141600</v>
+      </c>
+      <c r="F83" s="3">
+        <v>136200</v>
+      </c>
+      <c r="G83" s="3">
         <v>155800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>141000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>140600</v>
       </c>
-      <c r="H83" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>143800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
+        <v>143800</v>
+      </c>
+      <c r="L83" s="3">
         <v>135000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>123600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>126300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>129300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>350300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>333500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>331400</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>326600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>317400</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>313100</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>307300</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>294600</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>260000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>257100</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>248300</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>266500</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>251200</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>232700</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AD83" s="3">
         <v>219300</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AE83" s="3">
         <v>204100</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AF83" s="3">
         <v>199800</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AG83" s="3">
         <v>206800</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AH83" s="3">
         <v>188000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AI83" s="3">
         <v>193300</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AJ83" s="3">
         <v>190100</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AK83" s="3">
         <v>180300</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AL83" s="3">
         <v>174900</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AM83" s="3">
         <v>176400</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AN83" s="3">
         <v>181400</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AO83" s="3">
         <v>191300</v>
       </c>
     </row>
-    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8422,8 +8825,14 @@
       <c r="AM84" s="3">
         <v>0</v>
       </c>
+      <c r="AN84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8535,8 +8944,14 @@
       <c r="AM85" s="3">
         <v>0</v>
       </c>
+      <c r="AN85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8648,8 +9063,14 @@
       <c r="AM86" s="3">
         <v>0</v>
       </c>
+      <c r="AN86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8761,8 +9182,14 @@
       <c r="AM87" s="3">
         <v>0</v>
       </c>
+      <c r="AN87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8874,121 +9301,133 @@
       <c r="AM88" s="3">
         <v>0</v>
       </c>
+      <c r="AN88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>10</v>
+      <c r="D89" s="3">
+        <v>951800</v>
       </c>
       <c r="E89" s="3">
+        <v>1543000</v>
+      </c>
+      <c r="F89" s="3">
+        <v>1219100</v>
+      </c>
+      <c r="G89" s="3">
         <v>-1022400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>344100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>986700</v>
       </c>
-      <c r="H89" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
+        <v>791400</v>
+      </c>
+      <c r="K89" s="3">
         <v>543300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>364200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>453800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>649800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>244400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>74000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>2084300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>398700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>1462500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>606300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>1560600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>447600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>601400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>1962900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>771400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>317100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>431600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>538300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>1381600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>-141600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>-478100</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>1547600</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>67100</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>336000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AI89" s="3">
         <v>-753500</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AJ89" s="3">
         <v>210900</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AK89" s="3">
         <v>363600</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AL89" s="3">
         <v>-577400</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AM89" s="3">
         <v>207600</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AN89" s="3">
         <v>345500</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AO89" s="3">
         <v>1558700</v>
       </c>
     </row>
-    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9028,121 +9467,129 @@
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
+      <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
     </row>
-    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>10</v>
+      <c r="D91" s="3">
+        <v>-404800</v>
       </c>
       <c r="E91" s="3">
+        <v>-286200</v>
+      </c>
+      <c r="F91" s="3">
+        <v>-177000</v>
+      </c>
+      <c r="G91" s="3">
         <v>-185400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-174300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-152200</v>
       </c>
-      <c r="H91" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
+        <v>-154500</v>
+      </c>
+      <c r="K91" s="3">
         <v>-204400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-158900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-191600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-174800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-278900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-383400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-383400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-386200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-364500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-361800</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-278500</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-279300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-111400</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-71600</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-69600</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-50200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-68600</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-71900</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-75000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-31200</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-76200</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AF91" s="3">
         <v>-86400</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AG91" s="3">
         <v>-34900</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AH91" s="3">
         <v>-37200</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AI91" s="3">
         <v>-61300</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AJ91" s="3">
         <v>-55300</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AK91" s="3">
         <v>-44600</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AL91" s="3">
         <v>-56700</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AM91" s="3">
         <v>-177300</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AN91" s="3">
         <v>-181700</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AO91" s="3">
         <v>-154700</v>
       </c>
     </row>
-    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9254,8 +9701,14 @@
       <c r="AM92" s="3">
         <v>0</v>
       </c>
+      <c r="AN92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9367,121 +9820,133 @@
       <c r="AM93" s="3">
         <v>0</v>
       </c>
+      <c r="AN93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>10</v>
+      <c r="D94" s="3">
+        <v>-590900</v>
       </c>
       <c r="E94" s="3">
+        <v>-358100</v>
+      </c>
+      <c r="F94" s="3">
+        <v>-420800</v>
+      </c>
+      <c r="G94" s="3">
         <v>-196300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-335200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-204900</v>
       </c>
-      <c r="H94" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
+        <v>-319800</v>
+      </c>
+      <c r="K94" s="3">
         <v>-250300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-364400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-468700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-200000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-314000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-407200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-806000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-387800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-574100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-389300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-343400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-191600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-279600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-197000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-214300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-285100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-237800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-215400</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-200400</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-303400</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-181500</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>-217100</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>-103700</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AH94" s="3">
         <v>-197400</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AI94" s="3">
         <v>-173500</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AJ94" s="3">
         <v>-103200</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AK94" s="3">
         <v>-92900</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AL94" s="3">
         <v>-743900</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AM94" s="3">
         <v>-1323900</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AN94" s="3">
         <v>93100</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AO94" s="3">
         <v>-200800</v>
       </c>
     </row>
-    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9521,121 +9986,129 @@
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
+      <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
     </row>
-    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3" t="s">
-        <v>10</v>
+      <c r="D96" s="3">
+        <v>134100</v>
       </c>
       <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
+        <v>478400</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G96" s="3">
+        <v>0</v>
+      </c>
+      <c r="H96" s="3">
         <v>134000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>474300</v>
       </c>
-      <c r="H96" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
+      <c r="J96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3">
         <v>124500</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>458800</v>
       </c>
-      <c r="L96" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
-      <c r="N96" s="3">
+      <c r="N96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
         <v>-123400</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
       <c r="Q96" s="3">
         <v>0</v>
       </c>
       <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
         <v>-119800</v>
       </c>
-      <c r="S96" s="3">
-        <v>0</v>
-      </c>
-      <c r="T96" s="3">
-        <v>0</v>
-      </c>
       <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+      <c r="W96" s="3">
         <v>100</v>
       </c>
-      <c r="V96" s="3">
+      <c r="X96" s="3">
         <v>-102000</v>
       </c>
-      <c r="W96" s="3">
-        <v>0</v>
-      </c>
-      <c r="X96" s="3">
-        <v>0</v>
-      </c>
       <c r="Y96" s="3">
         <v>0</v>
       </c>
       <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-96400</v>
       </c>
-      <c r="AA96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB96" s="3">
-        <v>0</v>
-      </c>
       <c r="AC96" s="3">
         <v>0</v>
       </c>
       <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-91400</v>
       </c>
-      <c r="AE96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF96" s="3">
-        <v>0</v>
-      </c>
       <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI96" s="3">
         <v>3300</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AJ96" s="3">
         <v>-92300</v>
       </c>
-      <c r="AI96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ96" s="3">
-        <v>0</v>
-      </c>
       <c r="AK96" s="3">
         <v>0</v>
       </c>
       <c r="AL96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN96" s="3">
         <v>-85100</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AO96" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9747,8 +10220,14 @@
       <c r="AM97" s="3">
         <v>0</v>
       </c>
+      <c r="AN97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9860,8 +10339,14 @@
       <c r="AM98" s="3">
         <v>0</v>
       </c>
+      <c r="AN98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9973,343 +10458,367 @@
       <c r="AM99" s="3">
         <v>0</v>
       </c>
+      <c r="AN99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>10</v>
+      <c r="D100" s="3">
+        <v>-237400</v>
       </c>
       <c r="E100" s="3">
+        <v>-562300</v>
+      </c>
+      <c r="F100" s="3">
+        <v>-1087200</v>
+      </c>
+      <c r="G100" s="3">
         <v>1963300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-99100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-627000</v>
       </c>
-      <c r="H100" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
+        <v>-47200</v>
+      </c>
+      <c r="K100" s="3">
         <v>-154500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-323400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-574900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-283400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-729100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-301500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>625300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-8500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-750100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-110400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-717100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-179800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-1224700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-1524500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-387900</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>-91100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>-69000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>-157600</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-524100</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>512300</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>-86000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>-165100</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>-317800</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AH100" s="3">
         <v>691600</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AI100" s="3">
         <v>1071600</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AJ100" s="3">
         <v>395000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AK100" s="3">
         <v>-525700</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AL100" s="3">
         <v>-66500</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AM100" s="3">
         <v>1318500</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AN100" s="3">
         <v>-117800</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AO100" s="3">
         <v>-1014900</v>
       </c>
     </row>
-    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>10</v>
+      <c r="D101" s="3">
+        <v>-154200</v>
       </c>
       <c r="E101" s="3">
+        <v>113100</v>
+      </c>
+      <c r="F101" s="3">
+        <v>-73100</v>
+      </c>
+      <c r="G101" s="3">
         <v>-44800</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>52800</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-28000</v>
       </c>
-      <c r="H101" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>29900</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
+        <v>29900</v>
+      </c>
+      <c r="L101" s="3">
         <v>86200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-124300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>-144700</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>35600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>86200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>-124300</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>-144700</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>35600</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>2400</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>-28500</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>31100</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>-68900</v>
       </c>
-      <c r="V101" s="3">
+      <c r="X101" s="3">
         <v>100100</v>
       </c>
-      <c r="W101" s="3">
+      <c r="Y101" s="3">
         <v>33800</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Z101" s="3">
         <v>3700</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="AA101" s="3">
         <v>-94800</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AB101" s="3">
         <v>44700</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AC101" s="3">
         <v>-63500</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AD101" s="3">
         <v>-12800</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AE101" s="3">
         <v>8500</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AF101" s="3">
         <v>22000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AG101" s="3">
         <v>-46200</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AH101" s="3">
         <v>-65000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AI101" s="3">
         <v>43000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AJ101" s="3">
         <v>13700</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AK101" s="3">
         <v>11400</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AL101" s="3">
         <v>20600</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AM101" s="3">
         <v>29300</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AN101" s="3">
         <v>-50800</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AO101" s="3">
         <v>3900</v>
       </c>
     </row>
-    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>0</v>
+        <v>109300</v>
       </c>
       <c r="E102" s="3">
+        <v>607700</v>
+      </c>
+      <c r="F102" s="3">
+        <v>-223700</v>
+      </c>
+      <c r="G102" s="3">
         <v>793700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-244500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>267800</v>
       </c>
-      <c r="H102" s="3">
-        <v>0</v>
-      </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
+        <v>351300</v>
+      </c>
+      <c r="K102" s="3">
         <v>93700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-270800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-617800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>104700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-768800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-548500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>1779300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-142200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>173800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>109000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>471700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>107400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>-971800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>341500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>203000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>-55400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>30100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>210000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>593500</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>54600</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>-737000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>1187300</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>-400600</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>765100</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AI102" s="3">
         <v>187700</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AJ102" s="3">
         <v>516500</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AK102" s="3">
         <v>-243600</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AL102" s="3">
         <v>-1367100</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AM102" s="3">
         <v>231600</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AN102" s="3">
         <v>270000</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AO102" s="3">
         <v>346900</v>
       </c>
     </row>
